--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="999">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">Not set yet: golive.cutover_date (Settings sheet of the configuration workbook, or Master &gt; Configuration)</t>
+    <t xml:space="preserve">2026-10-04 (setting golive.cutover_date)</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill in</t>
@@ -346,7 +346,7 @@
     <t xml:space="preserve">Numbering</t>
   </si>
   <si>
-    <t xml:space="preserve">Next Number is the next sequence number of the current period (last number of the old system + 1) and cannot go backwards. It must be above every migrated number of the same format (checked by both workbooks).</t>
+    <t xml:space="preserve">Next Number is the next sequence number of the current period (last number of the old system + 1); it cannot go below a number already issued. It is kept on the series as the start of the period, so the transaction reset after the smoke test restarts the series there (no need to load the sheet again). It must be above every migrated number of the same format (checked by both workbooks).</t>
   </si>
   <si>
     <t xml:space="preserve">Settings</t>
@@ -1561,7 +1561,7 @@
     <t xml:space="preserve">Numbering: Next Number</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. Next sequence number of the current period: the last number used in the old system plus one. It cannot go backwards</t>
+    <t xml:space="preserve">Optional. Next sequence number of the current period: the last number used in the old system plus one. It cannot go below a number already issued; the transaction reset restarts the series here</t>
   </si>
   <si>
     <t xml:space="preserve">Numbering: Active</t>
@@ -1675,283 +1675,304 @@
     <t xml:space="preserve">system-admin</t>
   </si>
   <si>
+    <t xml:space="preserve">ARC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quotation_discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inactive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inactive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">renewal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium_tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prorate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fiscal_yearly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sales</t>
+  </si>
+  <si>
     <t xml:space="preserve">FPG</t>
   </si>
   <si>
-    <t xml:space="preserve">BOND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quotation_discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">broker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inactive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-current Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inactive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">renewal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">premium_tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per_unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prorate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fiscal_yearly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sales</t>
+    <t xml:space="preserve">BURGLARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy_issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non_package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return_premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrift Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">never</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claim_settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lgt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claims</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">policy_issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non_package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processing</t>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting</t>
   </si>
   <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">return_premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thrift Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Deposit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">never</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operations</t>
+    <t xml:space="preserve">EAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">journal_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casualty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
-    <t xml:space="preserve">CGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claim_settlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trust Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lgt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claims</t>
+    <t xml:space="preserve">EB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">write_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commission_payout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">petty_cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting</t>
+    <t xml:space="preserve">HOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remittance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Tax</t>
   </si>
   <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">EAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casualty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting-manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">write_off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commission_payout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating Expenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">petty_cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Expenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remittance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income Tax</t>
-  </si>
-  <si>
     <t xml:space="preserve">HULL</t>
   </si>
   <si>
     <t xml:space="preserve">remittance_settlement</t>
   </si>
   <si>
+    <t xml:space="preserve">TALA</t>
+  </si>
+  <si>
     <t xml:space="preserve">IAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIS</t>
   </si>
   <si>
     <t xml:space="preserve">MARINE</t>
@@ -5984,16 +6005,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -6001,16 +6022,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6040,22 +6061,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>508</v>
@@ -6063,22 +6084,22 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -6114,40 +6135,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>508</v>
@@ -6155,24 +6176,24 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -6217,34 +6238,34 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>508</v>
@@ -6252,31 +6273,31 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>553</v>
@@ -6310,25 +6331,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>508</v>
@@ -6336,25 +6357,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -6388,55 +6409,55 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>509</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>510</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>511</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>508</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>602</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>535</v>
@@ -6501,46 +6522,46 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>797</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>691</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>799</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>508</v>
@@ -6548,37 +6569,37 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>546</v>
@@ -6626,58 +6647,58 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>508</v>
@@ -6685,58 +6706,58 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>547</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="O2" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="P2" s="9" t="s">
-        <v>827</v>
-      </c>
       <c r="Q2" s="9" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -6768,19 +6789,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>508</v>
@@ -6788,16 +6809,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -6835,43 +6856,43 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>508</v>
@@ -6879,36 +6900,36 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>570</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -7387,12 +7408,14 @@
       <c r="M8" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="N8" s="11"/>
+      <c r="N8" s="11" t="s">
+        <v>620</v>
+      </c>
       <c r="O8" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -7402,7 +7425,7 @@
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9">
@@ -7410,7 +7433,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -7421,12 +7444,14 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
+      <c r="N9" s="11" t="s">
+        <v>625</v>
+      </c>
       <c r="O9" s="11" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -7442,7 +7467,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -7453,12 +7478,14 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
+      <c r="N10" s="11" t="s">
+        <v>629</v>
+      </c>
       <c r="O10" s="11" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -7474,7 +7501,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -7485,12 +7512,14 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+      <c r="N11" s="11" t="s">
+        <v>633</v>
+      </c>
       <c r="O11" s="11" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -7506,7 +7535,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -7517,12 +7546,14 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+      <c r="N12" s="11" t="s">
+        <v>637</v>
+      </c>
       <c r="O12" s="11" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -7547,9 +7578,11 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="N13" s="11" t="s">
+        <v>640</v>
+      </c>
       <c r="O13" s="11" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -7575,9 +7608,11 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
+      <c r="N14" s="11" t="s">
+        <v>642</v>
+      </c>
       <c r="O14" s="11" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -7605,7 +7640,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -7633,7 +7668,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -7661,7 +7696,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -7689,7 +7724,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -7717,7 +7752,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -7745,7 +7780,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -7777,19 +7812,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>508</v>
@@ -7797,19 +7832,19 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -7851,58 +7886,58 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>508</v>
@@ -7910,51 +7945,51 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="R2" s="9" t="s">
         <v>549</v>
@@ -7987,13 +8022,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>508</v>
@@ -8001,13 +8036,13 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -8038,25 +8073,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>508</v>
@@ -8064,16 +8099,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>550</v>
@@ -8117,16 +8152,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -8134,16 +8169,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8171,16 +8206,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -8188,13 +8223,13 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -8223,7 +8258,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>508</v>
@@ -8231,7 +8266,7 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -8257,10 +8292,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>508</v>
@@ -8268,10 +8303,10 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -8299,16 +8334,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -8316,16 +8351,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8356,25 +8391,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>935</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>936</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>937</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>939</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>928</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>508</v>
@@ -8382,25 +8417,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -8443,61 +8478,61 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="T1" s="8" t="s">
         <v>508</v>
@@ -8505,49 +8540,49 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
@@ -8583,62 +8618,62 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>532</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
         <v>537</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
         <v>531</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$7</formula1>
+      <formula1>Lists!$N$2:$N$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
       <formula1>Lists!$O$2:$O$20</formula1>
@@ -8679,60 +8714,60 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>517</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>532</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>612</v>
@@ -8742,7 +8777,7 @@
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -8754,7 +8789,7 @@
         <v>531</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -8796,49 +8831,49 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>971</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>950</v>
-      </c>
       <c r="F1" s="8" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>532</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
@@ -8869,30 +8904,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>613</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -8925,25 +8960,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>518</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>532</v>
@@ -8951,25 +8986,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>541</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>531</v>
@@ -9000,24 +9035,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -9039,16 +9074,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -9056,16 +9091,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9093,16 +9128,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>683</v>
-      </c>
       <c r="D1" s="8" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -9110,16 +9145,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9148,19 +9183,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>508</v>
@@ -9168,19 +9203,19 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -9217,43 +9252,43 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>697</v>
-      </c>
       <c r="K1" s="8" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>508</v>
@@ -9261,38 +9296,38 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -9321,16 +9356,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>508</v>
@@ -9338,16 +9373,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -10,41 +10,43 @@
     <sheet name="Company" sheetId="3" r:id="rId3"/>
     <sheet name="Settings" sheetId="4" r:id="rId4"/>
     <sheet name="Countries" sheetId="5" r:id="rId5"/>
-    <sheet name="States" sheetId="6" r:id="rId6"/>
-    <sheet name="Cities" sheetId="7" r:id="rId7"/>
-    <sheet name="Branches" sheetId="8" r:id="rId8"/>
-    <sheet name="Departments" sheetId="9" r:id="rId9"/>
-    <sheet name="Hierarchy" sheetId="10" r:id="rId10"/>
-    <sheet name="Designations" sheetId="11" r:id="rId11"/>
-    <sheet name="Users" sheetId="12" r:id="rId12"/>
-    <sheet name="Currencies" sheetId="13" r:id="rId13"/>
-    <sheet name="Exchange Rates" sheetId="14" r:id="rId14"/>
-    <sheet name="Chart of Accounts" sheetId="15" r:id="rId15"/>
-    <sheet name="Banks" sheetId="16" r:id="rId16"/>
-    <sheet name="Bank Accounts" sheetId="17" r:id="rId17"/>
-    <sheet name="Signatories" sheetId="18" r:id="rId18"/>
-    <sheet name="Transaction Codes" sheetId="19" r:id="rId19"/>
-    <sheet name="Write-off Reasons" sheetId="20" r:id="rId20"/>
-    <sheet name="Insurers" sheetId="21" r:id="rId21"/>
-    <sheet name="Lines of Business" sheetId="22" r:id="rId22"/>
-    <sheet name="Products" sheetId="23" r:id="rId23"/>
-    <sheet name="Policy Types" sheetId="24" r:id="rId24"/>
-    <sheet name="Covers" sheetId="25" r:id="rId25"/>
-    <sheet name="Vehicle Brands" sheetId="26" r:id="rId26"/>
-    <sheet name="Vehicle Models" sheetId="27" r:id="rId27"/>
-    <sheet name="Vehicle Variants" sheetId="28" r:id="rId28"/>
-    <sheet name="Vehicles" sheetId="29" r:id="rId29"/>
-    <sheet name="Commission Rates" sheetId="30" r:id="rId30"/>
-    <sheet name="Premium Taxes" sheetId="31" r:id="rId31"/>
-    <sheet name="LGU Rates" sheetId="32" r:id="rId32"/>
-    <sheet name="Authority Limits" sheetId="33" r:id="rId33"/>
-    <sheet name="Numbering" sheetId="34" r:id="rId34"/>
+    <sheet name="Regions" sheetId="6" r:id="rId6"/>
+    <sheet name="Provinces" sheetId="7" r:id="rId7"/>
+    <sheet name="Cities and Municipalities" sheetId="8" r:id="rId8"/>
+    <sheet name="Barangays" sheetId="9" r:id="rId9"/>
+    <sheet name="Branches" sheetId="10" r:id="rId10"/>
+    <sheet name="Departments" sheetId="11" r:id="rId11"/>
+    <sheet name="Hierarchy" sheetId="12" r:id="rId12"/>
+    <sheet name="Designations" sheetId="13" r:id="rId13"/>
+    <sheet name="Users" sheetId="14" r:id="rId14"/>
+    <sheet name="Currencies" sheetId="15" r:id="rId15"/>
+    <sheet name="Exchange Rates" sheetId="16" r:id="rId16"/>
+    <sheet name="Chart of Accounts" sheetId="17" r:id="rId17"/>
+    <sheet name="Banks" sheetId="18" r:id="rId18"/>
+    <sheet name="Bank Accounts" sheetId="19" r:id="rId19"/>
+    <sheet name="Signatories" sheetId="20" r:id="rId20"/>
+    <sheet name="Transaction Codes" sheetId="21" r:id="rId21"/>
+    <sheet name="Write-off Reasons" sheetId="22" r:id="rId22"/>
+    <sheet name="Insurers" sheetId="23" r:id="rId23"/>
+    <sheet name="Lines of Business" sheetId="24" r:id="rId24"/>
+    <sheet name="Products" sheetId="25" r:id="rId25"/>
+    <sheet name="Policy Types" sheetId="26" r:id="rId26"/>
+    <sheet name="Covers" sheetId="27" r:id="rId27"/>
+    <sheet name="Vehicle Brands" sheetId="28" r:id="rId28"/>
+    <sheet name="Vehicle Models" sheetId="29" r:id="rId29"/>
+    <sheet name="Vehicle Variants" sheetId="30" r:id="rId30"/>
+    <sheet name="Vehicles" sheetId="31" r:id="rId31"/>
+    <sheet name="Commission Rates" sheetId="32" r:id="rId32"/>
+    <sheet name="Premium Taxes" sheetId="33" r:id="rId33"/>
+    <sheet name="LGU Rates" sheetId="34" r:id="rId34"/>
+    <sheet name="Authority Limits" sheetId="35" r:id="rId35"/>
+    <sheet name="Numbering" sheetId="36" r:id="rId36"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1062">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -70,7 +72,7 @@
     <t xml:space="preserve">Cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 (setting golive.cutover_date)</t>
+    <t xml:space="preserve">Not set yet: golive.cutover_date (Settings sheet of the configuration workbook, or Master &gt; Configuration)</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill in</t>
@@ -127,175 +129,187 @@
     <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Country. Key: Country Name</t>
   </si>
   <si>
-    <t xml:space="preserve">4. States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; State. Key: Country + State Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Cities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City. Key: State + City Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Branches</t>
+    <t xml:space="preserve">4. Regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Province (regions are shown with their provinces; no Region screen of its own). Key: Country + Region Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Provinces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Province. Key: Country + Province Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Cities and Municipalities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City / Municipality. Key: Province + City / Municipality Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Barangays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City / Municipality (barangays are picked on the address forms; no Barangay screen of its own). Key: City / Municipality + Barangay Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Branches</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Organization &gt; Branch. Key: Branch Code</t>
   </si>
   <si>
-    <t xml:space="preserve">7. Departments</t>
+    <t xml:space="preserve">9. Departments</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Department (opened from Master &gt; Generals &gt; Organization &gt; Branch). Key: Department Code</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Hierarchy</t>
+    <t xml:space="preserve">10. Hierarchy</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Employee Management &gt; Hierarchy. Key: Rank Code</t>
   </si>
   <si>
-    <t xml:space="preserve">9. Designations</t>
+    <t xml:space="preserve">11. Designations</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Employee Management &gt; Designation. Key: Designation Code</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Users</t>
+    <t xml:space="preserve">12. Users</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; User. Key: Username</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Currencies</t>
+    <t xml:space="preserve">13. Currencies</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Currency. Key: Currency Code</t>
   </si>
   <si>
-    <t xml:space="preserve">12. Exchange Rates</t>
+    <t xml:space="preserve">14. Exchange Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Exchange Rate. Key: Currency Code + To Currency Code + Effective From</t>
   </si>
   <si>
-    <t xml:space="preserve">13. Chart of Accounts</t>
+    <t xml:space="preserve">15. Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Main Account / Sub Account. Key: Account Code</t>
   </si>
   <si>
-    <t xml:space="preserve">14. Banks</t>
+    <t xml:space="preserve">16. Banks</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Bank. Key: Bank Code</t>
   </si>
   <si>
-    <t xml:space="preserve">15. Bank Accounts</t>
+    <t xml:space="preserve">17. Bank Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Bank (choose Bank accounts in the Upload dialog). Key: Account Code</t>
   </si>
   <si>
-    <t xml:space="preserve">16. Signatories</t>
+    <t xml:space="preserve">18. Signatories</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Signatories. Key: Signatory Code</t>
   </si>
   <si>
-    <t xml:space="preserve">17. Transaction Codes</t>
+    <t xml:space="preserve">19. Transaction Codes</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Transaction Code. Key: Transaction Code</t>
   </si>
   <si>
-    <t xml:space="preserve">18. Write-off Reasons</t>
+    <t xml:space="preserve">20. Write-off Reasons</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Account Determination (write-off reasons). Key: Reason Code</t>
   </si>
   <si>
-    <t xml:space="preserve">19. Insurers</t>
+    <t xml:space="preserve">21. Insurers</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Insurance Company. Key: Insurance Company Code</t>
   </si>
   <si>
-    <t xml:space="preserve">20. Lines of Business</t>
+    <t xml:space="preserve">22. Lines of Business</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Line of Business. Key: Line of Business Code</t>
   </si>
   <si>
-    <t xml:space="preserve">21. Products</t>
+    <t xml:space="preserve">23. Products</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Product. Key: Product Code</t>
   </si>
   <si>
-    <t xml:space="preserve">22. Policy Types</t>
+    <t xml:space="preserve">24. Policy Types</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Product (policy types). Key: Policy Type Code</t>
   </si>
   <si>
-    <t xml:space="preserve">23. Covers</t>
+    <t xml:space="preserve">25. Covers</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Cover. Key: Cover Code</t>
   </si>
   <si>
-    <t xml:space="preserve">24. Vehicle Brands</t>
+    <t xml:space="preserve">26. Vehicle Brands</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle brands in the Upload dialog). Key: Brand</t>
   </si>
   <si>
-    <t xml:space="preserve">25. Vehicle Models</t>
+    <t xml:space="preserve">27. Vehicle Models</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle models in the Upload dialog). Key: Brand + Model</t>
   </si>
   <si>
-    <t xml:space="preserve">26. Vehicle Variants</t>
+    <t xml:space="preserve">28. Vehicle Variants</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle variants in the Upload dialog). Key: Model + Variant</t>
   </si>
   <si>
-    <t xml:space="preserve">27. Vehicles</t>
+    <t xml:space="preserve">29. Vehicles</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle. Key: Vehicle Code</t>
   </si>
   <si>
-    <t xml:space="preserve">28. Commission Rates</t>
+    <t xml:space="preserve">30. Commission Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Commission Rate Matrix. Key: Insurer + Product + Line of Business + Policy Type + Effective From</t>
   </si>
   <si>
-    <t xml:space="preserve">29. Premium Taxes</t>
+    <t xml:space="preserve">31. Premium Taxes</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (Taxes &amp; Charges). Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">30. LGU Rates</t>
+    <t xml:space="preserve">32. LGU Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (LGU Tax Rates). Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">31. Authority Limits</t>
+    <t xml:space="preserve">33. Authority Limits</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; Authority Matrix. Key: Transaction Type + Role</t>
   </si>
   <si>
-    <t xml:space="preserve">32. Numbering</t>
+    <t xml:space="preserve">34. Numbering</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code</t>
@@ -523,13 +537,13 @@
     <t xml:space="preserve">Company: Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Company: Pin Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company: City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company: State</t>
+    <t xml:space="preserve">Company: ZIP Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company: Province</t>
   </si>
   <si>
     <t xml:space="preserve">Company: Country</t>
@@ -586,43 +600,115 @@
     <t xml:space="preserve">Countries: Status</t>
   </si>
   <si>
-    <t xml:space="preserve">States: State Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States: State Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States: Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">States: Country</t>
+    <t xml:space="preserve">Regions: Region Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions: Region Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions: Designation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions: PSGC Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions: Country</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Name or code of an existing country record</t>
   </si>
   <si>
-    <t xml:space="preserve">States: Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cities: City Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cities: City Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cities: Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cities: State</t>
+    <t xml:space="preserve">Regions: Sort Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Whole number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Province Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Province Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Name or code of an existing region record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. One of the allowed values. Values: Lists sheet, Province Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: PSGC Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: City / Municipality Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: City / Municipality Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: Province</t>
   </si>
   <si>
     <t xml:space="preserve">Required. Name or code of an existing state record</t>
   </si>
   <si>
-    <t xml:space="preserve">Cities: Postal Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cities: Status</t>
+    <t xml:space="preserve">Cities and Municipalities: Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. One of the allowed values. Values: Lists sheet, City / Municipality Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: ZIP Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: Metro Manila District</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: PSGC Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cities and Municipalities: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangays: Barangay Code (PSGC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangays: Barangay Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangays: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Name or code of an existing city record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangays: ZIP Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangays: Status</t>
   </si>
   <si>
     <t xml:space="preserve">Branches: Branch Code</t>
@@ -652,10 +738,10 @@
     <t xml:space="preserve">Branches: Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Branches: City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branches: State</t>
+    <t xml:space="preserve">Branches: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branches: Province</t>
   </si>
   <si>
     <t xml:space="preserve">Branches: Country</t>
@@ -718,9 +804,6 @@
     <t xml:space="preserve">Designations: Level</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. Whole number</t>
-  </si>
-  <si>
     <t xml:space="preserve">Designations: Reporting to Level</t>
   </si>
   <si>
@@ -928,7 +1011,7 @@
     <t xml:space="preserve">Banks: Bank Branch</t>
   </si>
   <si>
-    <t xml:space="preserve">Banks: IFSC / SWIFT Code</t>
+    <t xml:space="preserve">Banks: SWIFT Code</t>
   </si>
   <si>
     <t xml:space="preserve">Required. SWIFT / BIC code of the branch</t>
@@ -943,10 +1026,10 @@
     <t xml:space="preserve">Banks: Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Banks: City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banks: State</t>
+    <t xml:space="preserve">Banks: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banks: Province</t>
   </si>
   <si>
     <t xml:space="preserve">Banks: Country</t>
@@ -1153,10 +1236,10 @@
     <t xml:space="preserve">Insurers: Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurers: City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurers: State</t>
+    <t xml:space="preserve">Insurers: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurers: Province</t>
   </si>
   <si>
     <t xml:space="preserve">Insurers: Country</t>
@@ -1195,6 +1278,18 @@
     <t xml:space="preserve">Optional. One of the allowed values. Values: Lists sheet, Insurance Company Default Billing Mode</t>
   </si>
   <si>
+    <t xml:space="preserve">Insurers: IC Certificate of Authority No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurers: Certificate of Authority Valid Until</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurers: IC Licence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. One of the allowed values. Values: Lists sheet, Insurance Company IC Licence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Insurers: Status</t>
   </si>
   <si>
@@ -1474,16 +1569,19 @@
     <t xml:space="preserve">LGU Rates: Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Required. City or municipality</t>
+    <t xml:space="preserve">Required. City or municipality (the local government unit levying the tax)</t>
   </si>
   <si>
     <t xml:space="preserve">LGU Rates: Province</t>
   </si>
   <si>
-    <t xml:space="preserve">LGU Rates: City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optional. Name of a city of the City master (optional link)</t>
+    <t xml:space="preserve">Optional. Province of the Province master (Metro Manila for NCR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LGU Rates: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Name or PSGC code of a city / municipality of the City / Municipality master (optional link)</t>
   </si>
   <si>
     <t xml:space="preserve">LGU Rates: Rate</t>
@@ -1615,6 +1713,12 @@
     <t xml:space="preserve">Transaction Types</t>
   </si>
   <si>
+    <t xml:space="preserve">Province Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality Class</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bank Category</t>
   </si>
   <si>
@@ -1627,6 +1731,9 @@
     <t xml:space="preserve">Insurance Company Default Billing Mode</t>
   </si>
   <si>
+    <t xml:space="preserve">Insurance Company IC Licence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Product Business Type</t>
   </si>
   <si>
@@ -1675,7 +1782,7 @@
     <t xml:space="preserve">system-admin</t>
   </si>
   <si>
-    <t xml:space="preserve">ARC</t>
+    <t xml:space="preserve">APEX</t>
   </si>
   <si>
     <t xml:space="preserve">BOND</t>
@@ -1684,6 +1791,12 @@
     <t xml:space="preserve">quotation_discount</t>
   </si>
   <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highly Urbanized City</t>
+  </si>
+  <si>
     <t xml:space="preserve">Universal Bank</t>
   </si>
   <si>
@@ -1696,6 +1809,9 @@
     <t xml:space="preserve">broker</t>
   </si>
   <si>
+    <t xml:space="preserve">Non-life</t>
+  </si>
+  <si>
     <t xml:space="preserve">package</t>
   </si>
   <si>
@@ -1741,66 +1857,81 @@
     <t xml:space="preserve">sales</t>
   </si>
   <si>
+    <t xml:space="preserve">EVERSAFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURGLARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy_issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitan area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non_package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processing</t>
+  </si>
+  <si>
     <t xml:space="preserve">FPG</t>
   </si>
   <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">policy_issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non_package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">CAR</t>
   </si>
   <si>
     <t xml:space="preserve">return_premium</t>
   </si>
   <si>
+    <t xml:space="preserve">Special Geographic Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component City</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thrift Bank</t>
   </si>
   <si>
@@ -1810,6 +1941,9 @@
     <t xml:space="preserve">Both</t>
   </si>
   <si>
+    <t xml:space="preserve">Composite</t>
+  </si>
+  <si>
     <t xml:space="preserve">both</t>
   </si>
   <si>
@@ -1834,7 +1968,7 @@
     <t xml:space="preserve">operations</t>
   </si>
   <si>
-    <t xml:space="preserve">LUZ</t>
+    <t xml:space="preserve">GOLDENHORIZON</t>
   </si>
   <si>
     <t xml:space="preserve">CGL</t>
@@ -1843,6 +1977,12 @@
     <t xml:space="preserve">claim_settlement</t>
   </si>
   <si>
+    <t xml:space="preserve">Province / state outside the Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipality</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rural Bank</t>
   </si>
   <si>
@@ -1864,78 +2004,78 @@
     <t xml:space="preserve">claims</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEGRITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIBERTYSHIELD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">journal_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casualty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting-manager</t>
+  </si>
+  <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting</t>
+    <t xml:space="preserve">EB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">write_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Services</t>
   </si>
   <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
-    <t xml:space="preserve">EAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casualty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting-manager</t>
+    <t xml:space="preserve">FIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commission_payout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">write_off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commission_payout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating Expenses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCIC</t>
-  </si>
-  <si>
     <t xml:space="preserve">GPA</t>
   </si>
   <si>
@@ -1957,24 +2097,24 @@
     <t xml:space="preserve">Income Tax</t>
   </si>
   <si>
+    <t xml:space="preserve">SECUREGUARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remittance_settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENTINEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">HULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remittance_settlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TALA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIS</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARINE</t>
   </si>
   <si>
@@ -2032,13 +2172,10 @@
     <t xml:space="preserve">Address Line 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pin Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State</t>
+    <t xml:space="preserve">ZIP Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality</t>
   </si>
   <si>
     <t xml:space="preserve">Country</t>
@@ -2083,7 +2220,7 @@
     <t xml:space="preserve">1226</t>
   </si>
   <si>
-    <t xml:space="preserve">Makati</t>
+    <t xml:space="preserve">Makati City</t>
   </si>
   <si>
     <t xml:space="preserve">Metro Manila</t>
@@ -2134,49 +2271,109 @@
     <t xml:space="preserve">+62</t>
   </si>
   <si>
-    <t xml:space="preserve">State Code *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State Name *</t>
+    <t xml:space="preserve">Region Code *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region Name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSGC Code</t>
   </si>
   <si>
     <t xml:space="preserve">Country *</t>
   </si>
   <si>
-    <t xml:space="preserve">SAMPLE QUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quezon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province of Quezon, CALABARZON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City Code *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City Name *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postal Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMPLE CBY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabuyao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">City of Cabuyao, Laguna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laguna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4025</t>
+    <t xml:space="preserve">Sort Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE MY-PEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peninsular Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaysia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province Code *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province Name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE MY-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selangor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State of Selangor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality Code *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality Name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro Manila District</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE MY-10-SHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shah Alam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City of Shah Alam, Selangor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MY-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangay Code (PSGC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barangay Name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City / Municipality *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE 0730600041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lahug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0730600000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6000</t>
   </si>
   <si>
     <t xml:space="preserve">Branch Code *</t>
@@ -2188,9 +2385,6 @@
     <t xml:space="preserve">Email ID *</t>
   </si>
   <si>
-    <t xml:space="preserve">City *</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAMPLE ILO</t>
   </si>
   <si>
@@ -2269,9 +2463,6 @@
     <t xml:space="preserve">Designation Name *</t>
   </si>
   <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reporting to Level</t>
   </si>
   <si>
@@ -2317,9 +2508,6 @@
     <t xml:space="preserve">Department</t>
   </si>
   <si>
-    <t xml:space="preserve">Designation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reporting To</t>
   </si>
   <si>
@@ -2461,34 +2649,34 @@
     <t xml:space="preserve">Bank Branch *</t>
   </si>
   <si>
-    <t xml:space="preserve">IFSC / SWIFT Code *</t>
+    <t xml:space="preserve">SWIFT Code *</t>
   </si>
   <si>
     <t xml:space="preserve">Phone *</t>
   </si>
   <si>
-    <t xml:space="preserve">SAMPLE UBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Union Bank of the Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ortigas Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBPHPHMM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnionBank Plaza, Meralco Ave.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+63 2 8841 8600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customer.service@unionbank.example.ph</t>
+    <t xml:space="preserve">SAMPLE CITI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citibank, N.A. (Philippine Branch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonifacio Global City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CITIPHMX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Bonifacio High Street, 5th Ave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taguig City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+63 2 8995 9999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer.service@citi.example.ph</t>
   </si>
   <si>
     <t xml:space="preserve">Bank Name</t>
@@ -2542,7 +2730,7 @@
     <t xml:space="preserve">BDO</t>
   </si>
   <si>
-    <t xml:space="preserve">Banco de Oro</t>
+    <t xml:space="preserve">BDO Unibank, Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">0012-3456-7890</t>
@@ -2707,6 +2895,15 @@
     <t xml:space="preserve">Default Billing Mode</t>
   </si>
   <si>
+    <t xml:space="preserve">IC Certificate of Authority No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificate of Authority Valid Until</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC Licence</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAMPLE CHARTER</t>
   </si>
   <si>
@@ -2965,9 +3162,6 @@
     <t xml:space="preserve">Minimum Amount</t>
   </si>
   <si>
-    <t xml:space="preserve">Sort Order</t>
-  </si>
-  <si>
     <t xml:space="preserve">Effective From</t>
   </si>
   <si>
@@ -2980,13 +3174,10 @@
     <t xml:space="preserve">150</t>
   </si>
   <si>
-    <t xml:space="preserve">Province</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAMPLE VAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Valenzuela</t>
+    <t xml:space="preserve">Valenzuela City</t>
   </si>
   <si>
     <t xml:space="preserve">0.2</t>
@@ -3169,7 +3360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3523,26 +3714,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="10"/>
+      <c r="B45" s="4" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" s="4" t="s">
+      <c r="A47" s="10" t="s">
         <v>89</v>
       </c>
+      <c r="B47" s="10"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -3561,26 +3752,26 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="B50" s="10"/>
+      <c r="B50" s="4" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" s="4" t="s">
+      <c r="A52" s="10" t="s">
         <v>98</v>
       </c>
+      <c r="B52" s="10"/>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
@@ -3607,26 +3798,26 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="10"/>
+      <c r="B56" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" s="4" t="s">
+      <c r="A58" s="10" t="s">
         <v>109</v>
       </c>
+      <c r="B58" s="10"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
@@ -3757,54 +3948,54 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="B75" s="10"/>
+      <c r="B75" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="A77" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B77" s="10"/>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>151</v>
@@ -3812,10 +4003,10 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="83">
@@ -3823,103 +4014,103 @@
         <v>154</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96">
@@ -3951,439 +4142,439 @@
         <v>175</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>144</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>224</v>
+        <v>151</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>224</v>
+        <v>148</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>228</v>
+        <v>148</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>230</v>
+        <v>151</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>235</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>239</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154">
@@ -4391,7 +4582,7 @@
         <v>240</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
     </row>
     <row r="155">
@@ -4399,119 +4590,119 @@
         <v>241</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>242</v>
+        <v>148</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>244</v>
+        <v>148</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>246</v>
+        <v>151</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="B169" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="170">
@@ -4519,55 +4710,55 @@
         <v>260</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="B171" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>144</v>
+        <v>259</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>144</v>
+        <v>259</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="B174" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>147</v>
+        <v>259</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="B176" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="177">
@@ -4575,39 +4766,39 @@
         <v>270</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>168</v>
+        <v>271</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>144</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>275</v>
+        <v>148</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>277</v>
+        <v>148</v>
       </c>
     </row>
     <row r="182">
@@ -4615,191 +4806,191 @@
         <v>278</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>279</v>
+        <v>148</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>284</v>
+        <v>151</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>290</v>
+        <v>151</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>144</v>
+        <v>288</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>147</v>
+        <v>294</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>144</v>
+        <v>299</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>197</v>
+        <v>302</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="B205" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="206">
@@ -4807,575 +4998,575 @@
         <v>310</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>144</v>
+        <v>311</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>147</v>
+        <v>313</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>144</v>
+        <v>315</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>147</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>263</v>
+        <v>151</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>325</v>
+        <v>148</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>327</v>
+        <v>148</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>329</v>
+        <v>151</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>168</v>
+        <v>225</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>144</v>
+        <v>333</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>144</v>
+        <v>341</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>341</v>
+        <v>151</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>147</v>
+        <v>352</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>168</v>
+        <v>356</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>356</v>
+        <v>148</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>358</v>
+        <v>148</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>147</v>
+        <v>368</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>376</v>
+        <v>172</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>378</v>
+        <v>148</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>380</v>
+        <v>148</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>168</v>
+        <v>385</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>393</v>
+        <v>151</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>395</v>
+        <v>151</v>
       </c>
     </row>
     <row r="278">
@@ -5383,63 +5574,63 @@
         <v>396</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>144</v>
+        <v>225</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>403</v>
+        <v>151</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>168</v>
+        <v>403</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B285" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="286">
@@ -5447,79 +5638,79 @@
         <v>406</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>144</v>
+        <v>407</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>144</v>
+        <v>409</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>409</v>
+        <v>151</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>168</v>
+        <v>290</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>144</v>
+        <v>413</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>414</v>
+        <v>148</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>418</v>
+        <v>172</v>
       </c>
     </row>
     <row r="296">
@@ -5527,7 +5718,7 @@
         <v>419</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="297">
@@ -5535,7 +5726,7 @@
         <v>420</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="298">
@@ -5543,7 +5734,7 @@
         <v>421</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>224</v>
+        <v>148</v>
       </c>
     </row>
     <row r="299">
@@ -5551,7 +5742,7 @@
         <v>422</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="300">
@@ -5559,95 +5750,95 @@
         <v>423</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>144</v>
+        <v>424</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>144</v>
+        <v>426</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>144</v>
+        <v>428</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>168</v>
+        <v>434</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>432</v>
+        <v>172</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>434</v>
+        <v>148</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>436</v>
+        <v>148</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>438</v>
+        <v>148</v>
       </c>
     </row>
     <row r="312">
@@ -5663,7 +5854,7 @@
         <v>441</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>261</v>
+        <v>172</v>
       </c>
     </row>
     <row r="314">
@@ -5671,319 +5862,511 @@
         <v>442</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>443</v>
+        <v>148</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>445</v>
+        <v>172</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>232</v>
+        <v>445</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>448</v>
+        <v>148</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>450</v>
+        <v>172</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>454</v>
+        <v>148</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>456</v>
+        <v>151</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>458</v>
+        <v>191</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>460</v>
+        <v>172</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>462</v>
+        <v>148</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>464</v>
+        <v>148</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>466</v>
+        <v>148</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>445</v>
+        <v>245</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>232</v>
+        <v>463</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>232</v>
+        <v>469</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>481</v>
+        <v>288</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>232</v>
+        <v>474</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>232</v>
+        <v>476</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>232</v>
+        <v>479</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>232</v>
+        <v>487</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>232</v>
+        <v>491</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>503</v>
+        <v>259</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>505</v>
+        <v>259</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="s">
+        <v>502</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="B353" s="4" t="s">
-        <v>286</v>
+      <c r="B358" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0" t="s">
+        <v>524</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="0" t="s">
+        <v>527</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -5992,6 +6375,173 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="18" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="17" style="11" customWidth="1"/>
+    <col min="6" max="6" width="20" style="11" customWidth="1"/>
+    <col min="7" max="7" width="20" style="11" customWidth="1"/>
+    <col min="8" max="8" width="20" style="11" customWidth="1"/>
+    <col min="9" max="9" width="25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="14" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="18" style="11" customWidth="1"/>
+    <col min="13" max="13" width="14" style="11" customWidth="1"/>
+    <col min="14" max="14" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21" style="11" customWidth="1"/>
+    <col min="2" max="2" width="21" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17" style="11" customWidth="1"/>
+    <col min="4" max="4" width="17" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6005,33 +6555,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>732</v>
+        <v>796</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>733</v>
+        <v>797</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>734</v>
+        <v>798</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>735</v>
+        <v>799</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>736</v>
+        <v>800</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>737</v>
+        <v>801</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>738</v>
+        <v>802</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6045,7 +6595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6061,45 +6611,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>739</v>
+        <v>803</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>740</v>
+        <v>804</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>725</v>
+        <v>789</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>742</v>
+        <v>805</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>743</v>
+        <v>806</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>744</v>
+        <v>807</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>745</v>
+        <v>808</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>746</v>
+        <v>809</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>747</v>
+        <v>810</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>748</v>
+        <v>811</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -6113,7 +6663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6135,74 +6685,74 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>749</v>
+        <v>812</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>750</v>
+        <v>813</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>751</v>
+        <v>814</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>752</v>
+        <v>815</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>753</v>
+        <v>816</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>754</v>
+        <v>817</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>755</v>
+        <v>818</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>727</v>
+        <v>791</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>756</v>
+        <v>819</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>758</v>
+        <v>820</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>759</v>
+        <v>821</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>760</v>
+        <v>822</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>761</v>
+        <v>823</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>762</v>
+        <v>824</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>763</v>
+        <v>825</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>764</v>
+        <v>826</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>731</v>
+        <v>795</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>613</v>
+        <v>659</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>536</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -6218,7 +6768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6238,69 +6788,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>766</v>
+        <v>828</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>767</v>
+        <v>829</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>768</v>
+        <v>830</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>769</v>
+        <v>831</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>770</v>
+        <v>832</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>771</v>
+        <v>833</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>772</v>
+        <v>834</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>773</v>
+        <v>835</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>774</v>
+        <v>836</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>775</v>
+        <v>837</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>776</v>
+        <v>838</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>777</v>
+        <v>839</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>778</v>
+        <v>840</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>778</v>
+        <v>840</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>779</v>
+        <v>841</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>748</v>
+        <v>811</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>780</v>
+        <v>842</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>553</v>
+        <v>591</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -6314,7 +6864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6331,51 +6881,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>781</v>
+        <v>843</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>782</v>
+        <v>844</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>783</v>
+        <v>845</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>784</v>
+        <v>846</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>785</v>
+        <v>847</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>786</v>
+        <v>848</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>787</v>
+        <v>849</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>788</v>
+        <v>850</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>789</v>
+        <v>851</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>790</v>
+        <v>852</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>791</v>
+        <v>853</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>792</v>
+        <v>854</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>793</v>
+        <v>855</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -6389,7 +6939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6409,67 +6959,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>794</v>
+        <v>856</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>795</v>
+        <v>857</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>796</v>
+        <v>858</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>797</v>
+        <v>859</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>798</v>
+        <v>860</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>799</v>
+        <v>861</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>800</v>
+        <v>862</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>801</v>
+        <v>863</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>602</v>
+        <v>648</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>628</v>
+        <v>674</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>628</v>
+        <v>674</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>535</v>
+        <v>570</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>553</v>
+        <v>591</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>536</v>
+        <v>571</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -6498,7 +7048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6506,11 +7056,11 @@
     <col min="1" max="1" width="15" style="11" customWidth="1"/>
     <col min="2" max="2" width="15" style="11" customWidth="1"/>
     <col min="3" max="3" width="17" style="11" customWidth="1"/>
-    <col min="4" max="4" width="23" style="11" customWidth="1"/>
+    <col min="4" max="4" width="16" style="11" customWidth="1"/>
     <col min="5" max="5" width="20" style="11" customWidth="1"/>
     <col min="6" max="6" width="20" style="11" customWidth="1"/>
     <col min="7" max="7" width="20" style="11" customWidth="1"/>
-    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="25" style="11" customWidth="1"/>
     <col min="9" max="9" width="14" style="11" customWidth="1"/>
     <col min="10" max="10" width="14" style="11" customWidth="1"/>
     <col min="11" max="11" width="14" style="11" customWidth="1"/>
@@ -6522,94 +7072,94 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>802</v>
+        <v>864</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>803</v>
+        <v>865</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>804</v>
+        <v>866</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>805</v>
+        <v>867</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>714</v>
+        <v>771</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>704</v>
+        <v>761</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>698</v>
+        <v>745</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>806</v>
+        <v>868</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>667</v>
+        <v>712</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>713</v>
+        <v>778</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>797</v>
+        <v>859</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>807</v>
+        <v>869</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>808</v>
+        <v>870</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>809</v>
+        <v>871</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>810</v>
+        <v>872</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>811</v>
+        <v>873</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>812</v>
+        <v>874</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>681</v>
+        <v>726</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>813</v>
+        <v>875</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>814</v>
+        <v>876</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>546</v>
+        <v>608</v>
       </c>
       <c r="O2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
-      <formula1>Lists!$Q$2:$Q$6</formula1>
+      <formula1>Lists!$S$2:$S$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="O2:O5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -6619,7 +7169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6647,124 +7197,124 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>794</v>
+        <v>856</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>795</v>
+        <v>857</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>802</v>
+        <v>864</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>815</v>
+        <v>877</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>816</v>
+        <v>878</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>817</v>
+        <v>879</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>818</v>
+        <v>880</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>819</v>
+        <v>881</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>820</v>
+        <v>882</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>727</v>
+        <v>791</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>821</v>
+        <v>883</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>822</v>
+        <v>884</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>823</v>
+        <v>885</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>824</v>
+        <v>886</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>825</v>
+        <v>887</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>826</v>
+        <v>888</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>827</v>
+        <v>889</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>828</v>
+        <v>890</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>829</v>
+        <v>891</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>830</v>
+        <v>892</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>831</v>
+        <v>893</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>832</v>
+        <v>894</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>833</v>
+        <v>895</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>790</v>
+        <v>852</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>834</v>
+        <v>896</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>835</v>
+        <v>897</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>836</v>
+        <v>898</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>837</v>
+        <v>899</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>838</v>
+        <v>900</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>839</v>
+        <v>901</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>840</v>
+        <v>902</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>841</v>
+        <v>903</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>834</v>
+        <v>896</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>842</v>
+        <v>904</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>838</v>
+        <v>900</v>
       </c>
       <c r="S2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
-      <formula1>Lists!$R$2:$R$5</formula1>
+      <formula1>Lists!$T$2:$T$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="S2:S5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -6774,7 +7324,948 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AA20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="16" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18" style="11" customWidth="1"/>
+    <col min="7" max="7" width="15" style="11" customWidth="1"/>
+    <col min="8" max="8" width="26" style="11" customWidth="1"/>
+    <col min="9" max="9" width="15" style="11" customWidth="1"/>
+    <col min="10" max="10" width="17" style="11" customWidth="1"/>
+    <col min="11" max="11" width="17" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14" style="11" customWidth="1"/>
+    <col min="13" max="13" width="14" style="11" customWidth="1"/>
+    <col min="14" max="14" width="14" style="11" customWidth="1"/>
+    <col min="15" max="15" width="14" style="11" customWidth="1"/>
+    <col min="16" max="16" width="21" style="11" customWidth="1"/>
+    <col min="17" max="17" width="18" style="11" customWidth="1"/>
+    <col min="18" max="18" width="29" style="11" customWidth="1"/>
+    <col min="19" max="19" width="17" style="11" customWidth="1"/>
+    <col min="20" max="20" width="29" style="11" customWidth="1"/>
+    <col min="21" max="21" width="38" style="11" customWidth="1"/>
+    <col min="22" max="22" width="42" style="11" customWidth="1"/>
+    <col min="23" max="23" width="32" style="11" customWidth="1"/>
+    <col min="24" max="24" width="25" style="11" customWidth="1"/>
+    <col min="25" max="25" width="28" style="11" customWidth="1"/>
+    <col min="26" max="26" width="30" style="11" customWidth="1"/>
+    <col min="27" max="27" width="47" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>589</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>685</v>
+      </c>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11" t="s">
+        <v>690</v>
+      </c>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6789,36 +8280,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>843</v>
+        <v>905</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>844</v>
+        <v>906</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>845</v>
+        <v>907</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>846</v>
+        <v>908</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>847</v>
+        <v>909</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>848</v>
+        <v>910</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>849</v>
+        <v>911</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>850</v>
+        <v>912</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -6833,7 +8324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6856,80 +8347,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>851</v>
+        <v>913</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>852</v>
+        <v>914</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>853</v>
+        <v>915</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>854</v>
+        <v>916</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>855</v>
+        <v>917</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>856</v>
+        <v>918</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>857</v>
+        <v>919</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>727</v>
+        <v>791</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>858</v>
+        <v>920</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>859</v>
+        <v>921</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>860</v>
+        <v>922</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>861</v>
+        <v>923</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>862</v>
+        <v>924</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>863</v>
+        <v>925</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>864</v>
+        <v>926</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>865</v>
+        <v>927</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>866</v>
+        <v>928</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>731</v>
+        <v>795</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>867</v>
+        <v>929</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>868</v>
+        <v>930</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>869</v>
+        <v>931</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -6937,7 +8428,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="D2:D5000">
-      <formula1>Lists!$S$2:$S$4</formula1>
+      <formula1>Lists!$U$2:$U$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -6947,857 +8438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14" style="11" customWidth="1"/>
-    <col min="3" max="3" width="16" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19" style="11" customWidth="1"/>
-    <col min="5" max="5" width="18" style="11" customWidth="1"/>
-    <col min="6" max="6" width="18" style="11" customWidth="1"/>
-    <col min="7" max="7" width="15" style="11" customWidth="1"/>
-    <col min="8" max="8" width="26" style="11" customWidth="1"/>
-    <col min="9" max="9" width="15" style="11" customWidth="1"/>
-    <col min="10" max="10" width="17" style="11" customWidth="1"/>
-    <col min="11" max="11" width="17" style="11" customWidth="1"/>
-    <col min="12" max="12" width="14" style="11" customWidth="1"/>
-    <col min="13" max="13" width="14" style="11" customWidth="1"/>
-    <col min="14" max="14" width="14" style="11" customWidth="1"/>
-    <col min="15" max="15" width="14" style="11" customWidth="1"/>
-    <col min="16" max="16" width="21" style="11" customWidth="1"/>
-    <col min="17" max="17" width="17" style="11" customWidth="1"/>
-    <col min="18" max="18" width="29" style="11" customWidth="1"/>
-    <col min="19" max="19" width="38" style="11" customWidth="1"/>
-    <col min="20" max="20" width="42" style="11" customWidth="1"/>
-    <col min="21" max="21" width="25" style="11" customWidth="1"/>
-    <col min="22" max="22" width="28" style="11" customWidth="1"/>
-    <col min="23" max="23" width="30" style="11" customWidth="1"/>
-    <col min="24" max="24" width="47" style="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:24" ht="20" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>533</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>535</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>542</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="s">
-        <v>553</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>556</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>559</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>568</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>572</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>573</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>576</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11" t="s">
-        <v>577</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11" t="s">
-        <v>580</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>581</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>583</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>589</v>
-      </c>
-      <c r="X4" s="11" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11" t="s">
-        <v>591</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11" t="s">
-        <v>593</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>595</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>596</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>603</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11" t="s">
-        <v>605</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>606</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q6" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
-        <v>611</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>615</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
-        <v>618</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>620</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>622</v>
-      </c>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11" t="s">
-        <v>624</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11" t="s">
-        <v>625</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>626</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>627</v>
-      </c>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11" t="s">
-        <v>629</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>630</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11" t="s">
-        <v>632</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>635</v>
-      </c>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>638</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11" t="s">
-        <v>640</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>641</v>
-      </c>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>643</v>
-      </c>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11" t="s">
-        <v>645</v>
-      </c>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11" t="s">
-        <v>648</v>
-      </c>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11" t="s">
-        <v>649</v>
-      </c>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7812,39 +8453,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>870</v>
+        <v>932</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>871</v>
+        <v>933</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>872</v>
+        <v>934</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>873</v>
+        <v>935</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>874</v>
+        <v>936</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>875</v>
+        <v>937</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>876</v>
+        <v>938</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>877</v>
+        <v>939</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>878</v>
+        <v>940</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -7858,9 +8499,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" style="11" customWidth="1"/>
@@ -7871,7 +8512,7 @@
     <col min="6" max="6" width="20" style="11" customWidth="1"/>
     <col min="7" max="7" width="20" style="11" customWidth="1"/>
     <col min="8" max="8" width="20" style="11" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+    <col min="9" max="9" width="25" style="11" customWidth="1"/>
     <col min="10" max="10" width="14" style="11" customWidth="1"/>
     <col min="11" max="11" width="14" style="11" customWidth="1"/>
     <col min="12" max="12" width="14" style="11" customWidth="1"/>
@@ -7881,127 +8522,145 @@
     <col min="16" max="16" width="37" style="11" customWidth="1"/>
     <col min="17" max="17" width="40" style="11" customWidth="1"/>
     <col min="18" max="18" width="26" style="11" customWidth="1"/>
-    <col min="19" max="19" width="14" style="11" customWidth="1"/>
+    <col min="19" max="19" width="37" style="11" customWidth="1"/>
+    <col min="20" max="20" width="40" style="11" customWidth="1"/>
+    <col min="21" max="21" width="16" style="11" customWidth="1"/>
+    <col min="22" max="22" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20" customHeight="1">
+    <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>879</v>
+        <v>941</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>880</v>
+        <v>942</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>881</v>
+        <v>943</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>653</v>
+        <v>699</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>714</v>
+        <v>771</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>704</v>
+        <v>761</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>698</v>
+        <v>745</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>713</v>
+        <v>778</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>882</v>
+        <v>944</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>823</v>
+        <v>885</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>883</v>
+        <v>945</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>884</v>
+        <v>946</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>885</v>
+        <v>947</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>886</v>
+        <v>948</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>508</v>
+        <v>949</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>887</v>
+        <v>952</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>888</v>
+        <v>953</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>889</v>
+        <v>954</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>890</v>
+        <v>955</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>891</v>
+        <v>956</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>892</v>
+        <v>957</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>679</v>
+        <v>724</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>681</v>
+        <v>726</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>893</v>
+        <v>958</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>894</v>
+        <v>959</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>895</v>
+        <v>960</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>896</v>
+        <v>961</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>897</v>
+        <v>962</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>898</v>
+        <v>963</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="R2:R5000">
-      <formula1>Lists!$T$2:$T$3</formula1>
+      <formula1>Lists!$V$2:$V$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="S2:S5000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="U2:U5000">
+      <formula1>Lists!$W$2:$W$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="V2:V5000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -8009,7 +8668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8022,27 +8681,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>899</v>
+        <v>964</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>900</v>
+        <v>965</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>901</v>
+        <v>966</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>902</v>
+        <v>967</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>903</v>
+        <v>968</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>904</v>
+        <v>969</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -8056,7 +8715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8073,48 +8732,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>905</v>
+        <v>970</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>906</v>
+        <v>971</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>907</v>
+        <v>972</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>908</v>
+        <v>973</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>909</v>
+        <v>974</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>910</v>
+        <v>975</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>911</v>
+        <v>976</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>912</v>
+        <v>977</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>913</v>
+        <v>978</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>914</v>
+        <v>979</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>915</v>
+        <v>980</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>550</v>
+        <v>588</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>551</v>
+        <v>589</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -8122,13 +8781,13 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
-      <formula1>Lists!$U$2:$U$3</formula1>
+      <formula1>Lists!$X$2:$X$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
-      <formula1>Lists!$V$2:$V$4</formula1>
+      <formula1>Lists!$Y$2:$Y$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G2:G5000">
-      <formula1>Lists!$W$2:$W$4</formula1>
+      <formula1>Lists!$Z$2:$Z$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -8138,7 +8797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8152,33 +8811,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>916</v>
+        <v>981</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>917</v>
+        <v>982</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>918</v>
+        <v>983</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>919</v>
+        <v>984</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>920</v>
+        <v>985</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>921</v>
+        <v>986</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8192,7 +8851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8206,30 +8865,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>922</v>
+        <v>987</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>923</v>
+        <v>988</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>924</v>
+        <v>989</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>925</v>
+        <v>990</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>926</v>
+        <v>991</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>927</v>
+        <v>992</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>928</v>
+        <v>993</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -8237,7 +8896,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="D2:D5000">
-      <formula1>Lists!$X$2:$X$8</formula1>
+      <formula1>Lists!$AA$2:$AA$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -8247,7 +8906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8258,15 +8917,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>929</v>
+        <v>994</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>930</v>
+        <v>995</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -8280,7 +8939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8292,156 +8951,27 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>929</v>
+        <v>994</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>931</v>
+        <v>996</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>932</v>
+        <v>997</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>933</v>
+        <v>998</v>
       </c>
       <c r="C2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="C2:C5000">
-      <formula1>Lists!$B$2:$B$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14" style="11" customWidth="1"/>
-    <col min="3" max="3" width="15" style="11" customWidth="1"/>
-    <col min="4" max="4" width="14" style="11" customWidth="1"/>
-    <col min="5" max="5" width="14" style="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="20" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>935</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>936</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>940</v>
-      </c>
-      <c r="E2" s="9"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
-      <formula1>Lists!$B$2:$B$3</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18" style="11" customWidth="1"/>
-    <col min="2" max="2" width="18" style="11" customWidth="1"/>
-    <col min="3" max="3" width="21" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19" style="11" customWidth="1"/>
-    <col min="5" max="5" width="19" style="11" customWidth="1"/>
-    <col min="6" max="6" width="22" style="11" customWidth="1"/>
-    <col min="7" max="7" width="15" style="11" customWidth="1"/>
-    <col min="8" max="8" width="14" style="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="20" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>941</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>943</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>944</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>945</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>946</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>935</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>947</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>948</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>949</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>933</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>950</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>951</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="H2" s="9"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -8467,7 +8997,7 @@
     <col min="11" max="11" width="20" style="11" customWidth="1"/>
     <col min="12" max="12" width="20" style="11" customWidth="1"/>
     <col min="13" max="13" width="14" style="11" customWidth="1"/>
-    <col min="14" max="14" width="14" style="11" customWidth="1"/>
+    <col min="14" max="14" width="25" style="11" customWidth="1"/>
     <col min="15" max="15" width="14" style="11" customWidth="1"/>
     <col min="16" max="16" width="14" style="11" customWidth="1"/>
     <col min="17" max="17" width="18" style="11" customWidth="1"/>
@@ -8478,115 +9008,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>653</v>
+        <v>699</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>654</v>
+        <v>700</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>655</v>
+        <v>701</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>656</v>
+        <v>702</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>657</v>
+        <v>703</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>662</v>
+        <v>708</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>663</v>
+        <v>709</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>664</v>
+        <v>581</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>665</v>
+        <v>710</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>666</v>
+        <v>711</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>667</v>
+        <v>712</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>668</v>
+        <v>713</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>669</v>
+        <v>714</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>670</v>
+        <v>715</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>671</v>
+        <v>716</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>672</v>
+        <v>717</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>673</v>
+        <v>718</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>674</v>
+        <v>719</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>676</v>
+        <v>721</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>677</v>
+        <v>722</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>678</v>
+        <v>723</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>679</v>
+        <v>724</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>681</v>
+        <v>726</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>682</v>
+        <v>727</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>553</v>
+        <v>591</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -8601,6 +9131,135 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="21" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19" style="11" customWidth="1"/>
+    <col min="6" max="6" width="22" style="11" customWidth="1"/>
+    <col min="7" max="7" width="15" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>998</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8618,56 +9277,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>953</v>
+        <v>1018</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>954</v>
+        <v>1019</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>955</v>
+        <v>1020</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>956</v>
+        <v>1021</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>957</v>
+        <v>1022</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>781</v>
+        <v>843</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>782</v>
+        <v>844</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>958</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>959</v>
+        <v>1024</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>537</v>
+        <v>572</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>960</v>
+        <v>1025</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>961</v>
+        <v>1026</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>962</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
@@ -8689,7 +9348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8714,70 +9373,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>963</v>
+        <v>1028</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>964</v>
+        <v>1029</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>965</v>
+        <v>1030</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>966</v>
+        <v>1031</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>967</v>
+        <v>1032</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>968</v>
+        <v>1033</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>969</v>
+        <v>1034</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>970</v>
+        <v>1035</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>971</v>
+        <v>1036</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>972</v>
+        <v>1037</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>973</v>
+        <v>746</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>974</v>
+        <v>1038</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>782</v>
+        <v>844</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>958</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>975</v>
+        <v>1039</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>976</v>
+        <v>1040</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>612</v>
+        <v>658</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>579</v>
+        <v>620</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>977</v>
+        <v>1041</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -8786,10 +9445,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>961</v>
+        <v>1026</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -8813,7 +9472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8821,7 +9480,7 @@
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
     <col min="2" max="2" width="14" style="11" customWidth="1"/>
     <col min="3" max="3" width="14" style="11" customWidth="1"/>
-    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="14" style="11" customWidth="1"/>
     <col min="6" max="6" width="20" style="11" customWidth="1"/>
     <col min="7" max="7" width="18" style="11" customWidth="1"/>
@@ -8831,53 +9490,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>963</v>
+        <v>1028</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>964</v>
+        <v>1029</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>978</v>
+        <v>581</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>663</v>
+        <v>709</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>957</v>
+        <v>1022</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>974</v>
+        <v>1038</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>782</v>
+        <v>844</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>958</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>979</v>
+        <v>1042</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>980</v>
+        <v>1043</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="D2" s="9"/>
+        <v>725</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1043</v>
+      </c>
       <c r="E2" s="9" t="s">
-        <v>981</v>
+        <v>1044</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>961</v>
+        <v>1026</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -8891,7 +9552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8904,30 +9565,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>982</v>
+        <v>1045</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>983</v>
+        <v>1046</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>984</v>
+        <v>1047</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>958</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>985</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>613</v>
+        <v>659</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>986</v>
+        <v>1049</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>987</v>
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
@@ -8943,7 +9604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8960,54 +9621,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>988</v>
+        <v>1051</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>989</v>
+        <v>1052</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1053</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>991</v>
+        <v>1054</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>992</v>
+        <v>1055</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>993</v>
+        <v>1056</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>532</v>
+        <v>567</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>994</v>
+        <v>1057</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>995</v>
+        <v>1058</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>996</v>
+        <v>1059</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>997</v>
+        <v>1060</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>940</v>
+        <v>1005</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>541</v>
+        <v>576</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>998</v>
+        <v>1061</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>531</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -9035,24 +9696,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>683</v>
+        <v>728</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>684</v>
+        <v>729</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>685</v>
+        <v>730</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>686</v>
+        <v>731</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>687</v>
+        <v>732</v>
       </c>
     </row>
   </sheetData>
@@ -9074,33 +9735,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>688</v>
+        <v>733</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>689</v>
+        <v>734</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>691</v>
+        <v>736</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>692</v>
+        <v>737</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>693</v>
+        <v>738</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>694</v>
+        <v>739</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>695</v>
+        <v>740</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9116,51 +9777,63 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" style="11" customWidth="1"/>
-    <col min="2" max="2" width="16" style="11" customWidth="1"/>
+    <col min="1" max="1" width="17" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
     <col min="3" max="3" width="17" style="11" customWidth="1"/>
-    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="15" style="11" customWidth="1"/>
     <col min="5" max="5" width="14" style="11" customWidth="1"/>
+    <col min="6" max="6" width="16" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20" customHeight="1">
+    <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>696</v>
+        <v>741</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>697</v>
+        <v>742</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>690</v>
+        <v>743</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>698</v>
+        <v>744</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>508</v>
+        <v>745</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>699</v>
+        <v>747</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>700</v>
+        <v>748</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="E2" s="9"/>
+        <v>749</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="G2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G2:G5000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -9170,58 +9843,73 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15" style="11" customWidth="1"/>
-    <col min="2" max="2" width="15" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" customWidth="1"/>
     <col min="3" max="3" width="17" style="11" customWidth="1"/>
     <col min="4" max="4" width="14" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
     <col min="6" max="6" width="14" style="11" customWidth="1"/>
+    <col min="7" max="7" width="15" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20" customHeight="1">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>702</v>
+        <v>752</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>703</v>
+        <v>753</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>704</v>
+        <v>754</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>705</v>
+        <v>745</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>508</v>
+        <v>755</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>706</v>
+        <v>756</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>707</v>
+        <v>757</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>708</v>
+        <v>758</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>709</v>
+        <v>748</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="F2" s="9"/>
+        <v>750</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
+      <formula1>Lists!$Q$2:$Q$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -9231,110 +9919,81 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" style="11" customWidth="1"/>
-    <col min="2" max="2" width="17" style="11" customWidth="1"/>
-    <col min="3" max="3" width="18" style="11" customWidth="1"/>
+    <col min="1" max="1" width="30" style="11" customWidth="1"/>
+    <col min="2" max="2" width="30" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17" style="11" customWidth="1"/>
     <col min="4" max="4" width="14" style="11" customWidth="1"/>
-    <col min="5" max="5" width="17" style="11" customWidth="1"/>
-    <col min="6" max="6" width="20" style="11" customWidth="1"/>
-    <col min="7" max="7" width="20" style="11" customWidth="1"/>
-    <col min="8" max="8" width="20" style="11" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="27" style="11" customWidth="1"/>
+    <col min="9" max="9" width="15" style="11" customWidth="1"/>
     <col min="10" max="10" width="14" style="11" customWidth="1"/>
-    <col min="11" max="11" width="14" style="11" customWidth="1"/>
-    <col min="12" max="12" width="18" style="11" customWidth="1"/>
-    <col min="13" max="13" width="14" style="11" customWidth="1"/>
-    <col min="14" max="14" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20" customHeight="1">
+    <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>651</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>713</v>
+        <v>761</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>658</v>
+        <v>754</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>659</v>
+        <v>762</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>661</v>
+        <v>763</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>714</v>
+        <v>744</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>715</v>
+        <v>764</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>716</v>
+        <v>765</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>717</v>
+        <v>766</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>720</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
+      <formula1>Lists!$R$2:$R$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="J2:J5000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -9347,42 +10006,42 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21" style="11" customWidth="1"/>
-    <col min="2" max="2" width="21" style="11" customWidth="1"/>
-    <col min="3" max="3" width="17" style="11" customWidth="1"/>
-    <col min="4" max="4" width="17" style="11" customWidth="1"/>
+    <col min="1" max="1" width="26" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" customWidth="1"/>
+    <col min="3" max="3" width="25" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
     <col min="5" max="5" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>725</v>
+        <v>769</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>726</v>
+        <v>770</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>658</v>
+        <v>771</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>728</v>
+        <v>772</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>729</v>
+        <v>773</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>730</v>
+        <v>774</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>731</v>
+        <v>775</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -36,17 +36,23 @@
     <sheet name="Vehicle Models" sheetId="29" r:id="rId29"/>
     <sheet name="Vehicle Variants" sheetId="30" r:id="rId30"/>
     <sheet name="Vehicles" sheetId="31" r:id="rId31"/>
-    <sheet name="Commission Rates" sheetId="32" r:id="rId32"/>
-    <sheet name="Premium Taxes" sheetId="33" r:id="rId33"/>
-    <sheet name="LGU Rates" sheetId="34" r:id="rId34"/>
-    <sheet name="Authority Limits" sheetId="35" r:id="rId35"/>
-    <sheet name="Numbering" sheetId="36" r:id="rId36"/>
+    <sheet name="Suppliers" sheetId="32" r:id="rId32"/>
+    <sheet name="Asset Classes" sheetId="33" r:id="rId33"/>
+    <sheet name="Short-Period Rates" sheetId="34" r:id="rId34"/>
+    <sheet name="Cancellation Reasons" sheetId="35" r:id="rId35"/>
+    <sheet name="Claim Document Checklist" sheetId="36" r:id="rId36"/>
+    <sheet name="Repair Shops" sheetId="37" r:id="rId37"/>
+    <sheet name="Commission Rates" sheetId="38" r:id="rId38"/>
+    <sheet name="Premium Taxes" sheetId="39" r:id="rId39"/>
+    <sheet name="LGU Rates" sheetId="40" r:id="rId40"/>
+    <sheet name="Authority Limits" sheetId="41" r:id="rId41"/>
+    <sheet name="Numbering" sheetId="42" r:id="rId42"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="1218">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -285,31 +291,67 @@
     <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle. Key: Vehicle Code</t>
   </si>
   <si>
-    <t xml:space="preserve">30. Commission Rates</t>
+    <t xml:space="preserve">30. Suppliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accounts &gt; Payables &gt; Suppliers. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. Asset Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Finance &gt; Asset Classes. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32. Short-Period Rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Short-Period Rates. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33. Cancellation Reasons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Cancellation Reasons. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34. Claim Document Checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Claim Document Checklist. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35. Repair Shops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Repair Shops. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36. Commission Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Commission Rate Matrix. Key: Insurer + Product + Line of Business + Policy Type + Effective From</t>
   </si>
   <si>
-    <t xml:space="preserve">31. Premium Taxes</t>
+    <t xml:space="preserve">37. Premium Taxes</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (Taxes &amp; Charges). Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">32. LGU Rates</t>
+    <t xml:space="preserve">38. LGU Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (LGU Tax Rates). Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">33. Authority Limits</t>
+    <t xml:space="preserve">39. Authority Limits</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; Authority Matrix. Key: Transaction Type + Role</t>
   </si>
   <si>
-    <t xml:space="preserve">34. Numbering</t>
+    <t xml:space="preserve">40. Numbering</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code</t>
@@ -1434,6 +1476,222 @@
     <t xml:space="preserve">Vehicles: Status</t>
   </si>
   <si>
+    <t xml:space="preserve">Suppliers: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: TIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Registered Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: VAT Registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: EWT Tax Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. EWT tax code of Master &gt; Finance &gt; Taxation withheld from the supplier, e.g. WC158 (goods), WC160 (services), WC100 (rentals); empty = none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Payment Terms (days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Days from the invoice date to the due date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Default Expense Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. GL expense account proposed on new invoice lines, e.g. 4401008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Contact Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: E-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Bank Account No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppliers: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Asset Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Useful Life (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Straight-line useful life in months, e.g. 36 for computers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Salvage Value (% of cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Salvage value as a percent of cost (0 when none)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Asset Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. GL asset account, e.g. 1401003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Accumulated Depreciation Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. GL accumulated depreciation account, e.g. 1402003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Depreciation Expense Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. GL depreciation expense account, e.g. 4406001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Classes: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short-Period Rates: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short-Period Rates: Cover Up To (days in force)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Upper limit of the band in days in force, e.g. 31 for not exceeding 1 month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short-Period Rates: Premium Retained (% of annual premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Percent of the annual premium kept by the insurer, e.g. 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short-Period Rates: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short-Period Rates: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reasons: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reasons: Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reasons: Initiated By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. insured (short-period scale) or insurer (pro-rata). Values: Lists sheet, Cancellation Reason Initiated By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reasons: Return Premium Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. auto (from who initiates), pro-rata, short-period or flat (whole premium returned). Values: Lists sheet, Cancellation Reason Return Premium Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reasons: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reasons: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Line of Business (* = all)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Line of business code as on the policy (MOTOR, FIRE ...) or * for every line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Claim Type (* = all)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Claim type as on the claim (Own Damage, Theft, Third Party ...) or * for every type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Yes when the claim cannot go to the insurer without it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Sort Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Document Checklist: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Repair Shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Contact Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: E-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: TIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Accredited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Yes when the insurers accredit the shop (only accredited shops take estimates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Accredited By (insurers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Insurers that accredit the shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Labour Rate per Hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Labour rate per hour agreed with the insurers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shops: Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">Commission Rates: Insurer</t>
   </si>
   <si>
@@ -1746,6 +2004,12 @@
     <t xml:space="preserve">Cover Lines of business (blank: every line)</t>
   </si>
   <si>
+    <t xml:space="preserve">Cancellation Reason Initiated By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancellation Reason Return Premium Method</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
@@ -1821,6 +2085,12 @@
     <t xml:space="preserve">motor</t>
   </si>
   <si>
+    <t xml:space="preserve">insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
@@ -1896,6 +2166,12 @@
     <t xml:space="preserve">fire</t>
   </si>
   <si>
+    <t xml:space="preserve">insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pro-rata</t>
+  </si>
+  <si>
     <t xml:space="preserve">equity</t>
   </si>
   <si>
@@ -1953,6 +2229,9 @@
     <t xml:space="preserve">accident</t>
   </si>
   <si>
+    <t xml:space="preserve">short-period</t>
+  </si>
+  <si>
     <t xml:space="preserve">income</t>
   </si>
   <si>
@@ -2061,6 +2340,9 @@
     <t xml:space="preserve">Cost of Services</t>
   </si>
   <si>
+    <t xml:space="preserve">own-book</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
@@ -3102,6 +3384,201 @@
     <t xml:space="preserve">MPV</t>
   </si>
   <si>
+    <t xml:space="preserve">Code *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registered Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAT Registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EWT Tax Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment Terms (days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default Expense Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Account No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE SUP-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metro Courier Services Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">009-876-543-000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Shaw Blvd., Mandaluyong City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WC160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4401007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billing Officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">billing@metrocourier.example.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+63 2 8700 1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0012-3456-7899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Class *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Useful Life (months) *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salvage Value (% of cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Account *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accumulated Depreciation Account *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation Expense Account *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE OFFICE-FITOUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office fit-out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1401005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1402005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4406002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cover Up To (days in force) *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium Retained (% of annual premium) *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE SP13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not exceeding 15 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiated By *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Premium Method *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE TOTAL_LOSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total loss of the insured property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cover ends with a total loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line of Business (* = all) *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Type (* = all) *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE PA-MEDCERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical certificate and hospital bills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair Shop *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accredited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accredited By (insurers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labour Rate per Hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE RS-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality Auto Repair Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88 E. Rodriguez Jr. Ave.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quezon City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Advisor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+63 2 8911 2233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service@qualityauto.example.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010-222-333-000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malayan, Pioneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">650</t>
+  </si>
+  <si>
     <t xml:space="preserve">Insurer</t>
   </si>
   <si>
@@ -3130,9 +3607,6 @@
   </si>
   <si>
     <t xml:space="preserve">Agreement 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code *</t>
   </si>
   <si>
     <t xml:space="preserve">Name *</t>
@@ -3241,7 +3715,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3268,8 +3742,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3297,6 +3785,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3328,7 +3834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3351,6 +3857,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3360,7 +3871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B437"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3730,142 +4241,142 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="10"/>
+      <c r="B47" s="4" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B52" s="10"/>
+      <c r="A52" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>100</v>
-      </c>
+      <c r="A53" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="10"/>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B58" s="10"/>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="B64" s="4" t="s">
+      <c r="A64" s="10" t="s">
         <v>121</v>
       </c>
+      <c r="B64" s="10"/>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
@@ -3964,2097 +4475,2097 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="B77" s="10"/>
+      <c r="B77" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>155</v>
-      </c>
+      <c r="A83" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B83" s="10"/>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>148</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>148</v>
+        <v>222</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>148</v>
+        <v>237</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>245</v>
+        <v>163</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>257</v>
+        <v>163</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>259</v>
+        <v>203</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>148</v>
+        <v>278</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>148</v>
+        <v>271</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>148</v>
+        <v>281</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>148</v>
+        <v>283</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>148</v>
+        <v>285</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>151</v>
+        <v>287</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>288</v>
+        <v>163</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>290</v>
+        <v>160</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>148</v>
+        <v>257</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>294</v>
+        <v>182</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>151</v>
+        <v>300</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>172</v>
+        <v>302</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>299</v>
+        <v>160</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>304</v>
+        <v>163</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>306</v>
+        <v>163</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>311</v>
+        <v>160</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>148</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>148</v>
+        <v>323</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>151</v>
+        <v>327</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>151</v>
+        <v>329</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>148</v>
+        <v>334</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>225</v>
+        <v>163</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>333</v>
+        <v>160</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>148</v>
+        <v>345</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>341</v>
+        <v>184</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>290</v>
+        <v>353</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>352</v>
+        <v>163</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>354</v>
+        <v>163</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>356</v>
+        <v>302</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>148</v>
+        <v>364</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>151</v>
+        <v>366</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>151</v>
+        <v>368</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>368</v>
+        <v>163</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>151</v>
+        <v>380</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>378</v>
+        <v>163</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>383</v>
+        <v>163</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>385</v>
+        <v>163</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>151</v>
+        <v>390</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>151</v>
+        <v>395</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>151</v>
+        <v>397</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>225</v>
+        <v>163</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>403</v>
+        <v>160</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>405</v>
+        <v>160</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>407</v>
+        <v>160</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>409</v>
+        <v>237</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>290</v>
+        <v>163</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>172</v>
+        <v>417</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>148</v>
+        <v>419</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>148</v>
+        <v>421</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>172</v>
+        <v>302</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>148</v>
+        <v>425</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>424</v>
+        <v>160</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>426</v>
+        <v>184</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>428</v>
+        <v>160</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>151</v>
+        <v>436</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>172</v>
+        <v>440</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>440</v>
+        <v>163</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>172</v>
+        <v>446</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>445</v>
+        <v>160</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>172</v>
+        <v>452</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>449</v>
+        <v>184</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>191</v>
+        <v>457</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>148</v>
+        <v>461</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>245</v>
+        <v>184</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>463</v>
+        <v>160</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>465</v>
+        <v>160</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>467</v>
+        <v>160</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>469</v>
+        <v>257</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>471</v>
+        <v>163</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>288</v>
+        <v>184</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>474</v>
+        <v>160</v>
       </c>
     </row>
     <row r="339">
@@ -6062,311 +6573,791 @@
         <v>475</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>476</v>
+        <v>160</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>259</v>
+        <v>163</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>479</v>
+        <v>163</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>481</v>
+        <v>182</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>489</v>
+        <v>163</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>491</v>
+        <v>167</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>493</v>
+        <v>163</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>495</v>
+        <v>163</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>497</v>
+        <v>163</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>476</v>
+        <v>160</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>259</v>
+        <v>494</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>259</v>
+        <v>496</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>259</v>
+        <v>498</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>509</v>
+        <v>163</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>511</v>
+        <v>184</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>513</v>
+        <v>160</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>259</v>
+        <v>507</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>259</v>
+        <v>509</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>313</v>
+        <v>163</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>519</v>
+        <v>160</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>521</v>
+        <v>160</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>259</v>
+        <v>517</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>526</v>
+        <v>163</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>529</v>
+        <v>160</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>535</v>
+        <v>160</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
+        <v>528</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="s">
+        <v>529</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="s">
+        <v>533</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="s">
         <v>538</v>
       </c>
-      <c r="B377" s="4" t="s">
-        <v>313</v>
+      <c r="B387" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0" t="s">
+        <v>541</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0" t="s">
+        <v>543</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="s">
+        <v>548</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0" t="s">
+        <v>554</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0" t="s">
+        <v>557</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0" t="s">
+        <v>580</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="0" t="s">
+        <v>582</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0" t="s">
+        <v>583</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="B415" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0" t="s">
+        <v>599</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="0" t="s">
+        <v>600</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0" t="s">
+        <v>601</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="0" t="s">
+        <v>622</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -6397,82 +7388,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>776</v>
+        <v>868</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>777</v>
+        <v>869</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>697</v>
+        <v>789</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>778</v>
+        <v>870</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>705</v>
+        <v>797</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>706</v>
+        <v>798</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>707</v>
+        <v>799</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>771</v>
+        <v>863</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>761</v>
+        <v>853</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>711</v>
+        <v>803</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>712</v>
+        <v>804</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>779</v>
+        <v>871</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>780</v>
+        <v>872</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>781</v>
+        <v>873</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>782</v>
+        <v>874</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>783</v>
+        <v>875</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>784</v>
+        <v>876</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>785</v>
+        <v>877</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>786</v>
+        <v>878</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>787</v>
+        <v>879</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>726</v>
+        <v>818</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>788</v>
+        <v>880</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -6501,33 +7492,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>789</v>
+        <v>881</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>790</v>
+        <v>882</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>791</v>
+        <v>883</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>792</v>
+        <v>884</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>793</v>
+        <v>885</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>794</v>
+        <v>886</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>795</v>
+        <v>887</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6555,33 +7546,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>704</v>
-      </c>
       <c r="D1" s="8" t="s">
-        <v>798</v>
+        <v>890</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>799</v>
+        <v>891</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>800</v>
+        <v>892</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>801</v>
+        <v>893</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>802</v>
+        <v>894</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6611,45 +7602,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>803</v>
+        <v>895</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>804</v>
+        <v>896</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>789</v>
+        <v>881</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>755</v>
+        <v>847</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>805</v>
+        <v>897</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>806</v>
+        <v>898</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>807</v>
+        <v>899</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>808</v>
+        <v>900</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>809</v>
+        <v>901</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>810</v>
+        <v>902</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>811</v>
+        <v>903</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -6685,80 +7676,80 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>812</v>
+        <v>904</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>813</v>
+        <v>905</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>814</v>
+        <v>906</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>815</v>
+        <v>907</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>816</v>
+        <v>908</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>817</v>
+        <v>909</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>818</v>
+        <v>910</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>791</v>
+        <v>883</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>819</v>
+        <v>911</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>743</v>
+        <v>835</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>820</v>
+        <v>912</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>821</v>
+        <v>913</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>822</v>
+        <v>914</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>823</v>
+        <v>915</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>824</v>
+        <v>916</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>825</v>
+        <v>917</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>826</v>
+        <v>918</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>795</v>
+        <v>887</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>659</v>
+        <v>750</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>571</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="L2:L5000">
-      <formula1>Lists!$M$2:$M$8</formula1>
+      <formula1>Lists!$M$2:$M$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
       <formula1>Lists!$G$2:$G$3</formula1>
@@ -6788,69 +7779,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>827</v>
+        <v>919</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>828</v>
+        <v>920</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>829</v>
+        <v>921</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>830</v>
+        <v>922</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>831</v>
+        <v>923</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>832</v>
+        <v>924</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>833</v>
+        <v>925</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>834</v>
+        <v>926</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>835</v>
+        <v>927</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>836</v>
+        <v>928</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>837</v>
+        <v>929</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>838</v>
+        <v>930</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>839</v>
+        <v>931</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>840</v>
+        <v>932</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>840</v>
+        <v>932</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>841</v>
+        <v>933</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>811</v>
+        <v>903</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>842</v>
+        <v>934</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>591</v>
+        <v>679</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -6881,51 +7872,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>843</v>
+        <v>935</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>844</v>
+        <v>936</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>827</v>
+        <v>919</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>845</v>
+        <v>937</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>846</v>
+        <v>938</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>847</v>
+        <v>939</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>848</v>
+        <v>940</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>849</v>
+        <v>941</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>850</v>
+        <v>942</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>851</v>
+        <v>943</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>852</v>
+        <v>944</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>853</v>
+        <v>945</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>854</v>
+        <v>946</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>855</v>
+        <v>947</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -6959,67 +7950,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>856</v>
+        <v>948</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>857</v>
+        <v>949</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>625</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>858</v>
+        <v>950</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>542</v>
+        <v>626</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>859</v>
+        <v>951</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>543</v>
+        <v>627</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>860</v>
+        <v>952</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>861</v>
+        <v>953</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>862</v>
+        <v>954</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>863</v>
+        <v>955</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>648</v>
+        <v>739</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>674</v>
+        <v>766</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>674</v>
+        <v>766</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>570</v>
+        <v>656</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>591</v>
+        <v>679</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>571</v>
+        <v>657</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -7072,87 +8063,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>864</v>
+        <v>956</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>865</v>
+        <v>957</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>866</v>
+        <v>958</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>867</v>
+        <v>959</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>705</v>
+        <v>797</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>706</v>
+        <v>798</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>707</v>
+        <v>799</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>771</v>
+        <v>863</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>761</v>
+        <v>853</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>868</v>
+        <v>960</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>712</v>
+        <v>804</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>778</v>
+        <v>870</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>859</v>
+        <v>951</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>869</v>
+        <v>961</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>870</v>
+        <v>962</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>871</v>
+        <v>963</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>872</v>
+        <v>964</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>873</v>
+        <v>965</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>874</v>
+        <v>966</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>725</v>
+        <v>817</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>726</v>
+        <v>818</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>875</v>
+        <v>967</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>876</v>
+        <v>968</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>608</v>
+        <v>696</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -7197,117 +8188,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>856</v>
+        <v>948</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>857</v>
+        <v>949</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>864</v>
+        <v>956</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>877</v>
+        <v>969</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>878</v>
+        <v>970</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>879</v>
+        <v>971</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>880</v>
+        <v>972</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>881</v>
+        <v>973</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>882</v>
+        <v>974</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>791</v>
+        <v>883</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>883</v>
+        <v>975</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>884</v>
+        <v>976</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>885</v>
+        <v>977</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>886</v>
+        <v>978</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>887</v>
+        <v>979</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>888</v>
+        <v>980</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>889</v>
+        <v>981</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>890</v>
+        <v>982</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>891</v>
+        <v>983</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>892</v>
+        <v>984</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>893</v>
+        <v>985</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>894</v>
+        <v>986</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>895</v>
+        <v>987</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>584</v>
+        <v>670</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>852</v>
+        <v>944</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>896</v>
+        <v>988</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>897</v>
+        <v>989</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>898</v>
+        <v>990</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>899</v>
+        <v>991</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>900</v>
+        <v>992</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>901</v>
+        <v>993</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>902</v>
+        <v>994</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>903</v>
+        <v>995</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>896</v>
+        <v>988</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>904</v>
+        <v>996</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>900</v>
+        <v>992</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -7326,7 +8317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
@@ -7356,368 +8347,392 @@
     <col min="25" max="25" width="28" style="11" customWidth="1"/>
     <col min="26" max="26" width="30" style="11" customWidth="1"/>
     <col min="27" max="27" width="47" style="11" customWidth="1"/>
+    <col min="28" max="28" width="36" style="11" customWidth="1"/>
+    <col min="29" max="29" width="45" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="20" customHeight="1">
+    <row r="1" spans="1:29" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>539</v>
+        <v>623</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>625</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>542</v>
+        <v>626</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>543</v>
+        <v>627</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>544</v>
+        <v>628</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>545</v>
+        <v>629</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>546</v>
+        <v>630</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>547</v>
+        <v>631</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>548</v>
+        <v>632</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>549</v>
+        <v>633</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>550</v>
+        <v>634</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>551</v>
+        <v>635</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>552</v>
+        <v>636</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>553</v>
+        <v>637</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>554</v>
+        <v>638</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>555</v>
+        <v>639</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>556</v>
+        <v>640</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>557</v>
+        <v>641</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>558</v>
+        <v>642</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>559</v>
+        <v>643</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>560</v>
+        <v>644</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>561</v>
+        <v>645</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>562</v>
+        <v>646</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>563</v>
+        <v>647</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>564</v>
+        <v>648</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>565</v>
+        <v>649</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>568</v>
+        <v>654</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>569</v>
+        <v>655</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>570</v>
+        <v>656</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>571</v>
+        <v>657</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>571</v>
+        <v>657</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>572</v>
+        <v>658</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>573</v>
+        <v>659</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>574</v>
+        <v>660</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>575</v>
+        <v>661</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>576</v>
+        <v>662</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>577</v>
+        <v>663</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>578</v>
+        <v>664</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>579</v>
+        <v>665</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>580</v>
+        <v>666</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>581</v>
+        <v>667</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>582</v>
+        <v>668</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>583</v>
+        <v>669</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>584</v>
+        <v>670</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>585</v>
+        <v>671</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>586</v>
+        <v>672</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>587</v>
+        <v>673</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>588</v>
+        <v>674</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>589</v>
+        <v>675</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>573</v>
+        <v>659</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>590</v>
+        <v>676</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>591</v>
+        <v>679</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>592</v>
+        <v>680</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>593</v>
+        <v>681</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>594</v>
+        <v>682</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>595</v>
+        <v>683</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>596</v>
+        <v>684</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>596</v>
+        <v>684</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>597</v>
+        <v>685</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>598</v>
+        <v>686</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>599</v>
+        <v>687</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>600</v>
+        <v>688</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>601</v>
+        <v>689</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>602</v>
+        <v>690</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>603</v>
+        <v>691</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>604</v>
+        <v>692</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>605</v>
+        <v>693</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>606</v>
+        <v>694</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>607</v>
+        <v>695</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>608</v>
+        <v>696</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>609</v>
+        <v>697</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>610</v>
+        <v>698</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>611</v>
+        <v>699</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>612</v>
+        <v>700</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>613</v>
+        <v>701</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>614</v>
+        <v>702</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>598</v>
+        <v>686</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>615</v>
+        <v>703</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="AC3" s="11" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>616</v>
+        <v>706</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>617</v>
+        <v>707</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>618</v>
+        <v>708</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>619</v>
+        <v>709</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>620</v>
+        <v>710</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>621</v>
+        <v>711</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>622</v>
+        <v>712</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>623</v>
+        <v>713</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>624</v>
+        <v>714</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>625</v>
+        <v>715</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>626</v>
+        <v>716</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>627</v>
+        <v>717</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>628</v>
+        <v>718</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>629</v>
+        <v>719</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>630</v>
+        <v>720</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>631</v>
+        <v>721</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>632</v>
+        <v>722</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>633</v>
+        <v>723</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>634</v>
+        <v>724</v>
+      </c>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>635</v>
+        <v>726</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>636</v>
+        <v>727</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>637</v>
+        <v>728</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>638</v>
+        <v>729</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>639</v>
+        <v>730</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>640</v>
+        <v>731</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>641</v>
+        <v>732</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>642</v>
+        <v>733</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>643</v>
+        <v>734</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>644</v>
+        <v>735</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>645</v>
+        <v>736</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>646</v>
+        <v>737</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -7726,44 +8741,48 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>647</v>
+        <v>738</v>
+      </c>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>648</v>
+        <v>739</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>649</v>
+        <v>740</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>650</v>
+        <v>741</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>651</v>
+        <v>742</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>652</v>
+        <v>743</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>653</v>
+        <v>744</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>654</v>
+        <v>745</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>655</v>
+        <v>746</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -7773,37 +8792,39 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>656</v>
-      </c>
+        <v>747</v>
+      </c>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>657</v>
+        <v>748</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>658</v>
+        <v>749</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>659</v>
+        <v>750</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>660</v>
+        <v>751</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>661</v>
+        <v>752</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>662</v>
+        <v>753</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -7816,15 +8837,17 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>663</v>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>664</v>
+        <v>755</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -7835,16 +8858,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>665</v>
+        <v>756</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>666</v>
+        <v>757</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>667</v>
+        <v>758</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>668</v>
+        <v>759</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -7857,15 +8880,17 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>669</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>670</v>
+        <v>761</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -7875,15 +8900,17 @@
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
+      <c r="M9" s="11" t="s">
+        <v>762</v>
+      </c>
       <c r="N9" s="11" t="s">
-        <v>671</v>
+        <v>763</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>672</v>
+        <v>764</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>673</v>
+        <v>765</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -7896,13 +8923,15 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>674</v>
+        <v>766</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -7914,13 +8943,13 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11" t="s">
-        <v>675</v>
+        <v>767</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>676</v>
+        <v>768</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>677</v>
+        <v>769</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -7933,13 +8962,15 @@
       <c r="Y10" s="11"/>
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>678</v>
+        <v>770</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -7951,13 +8982,13 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>679</v>
+        <v>771</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>680</v>
+        <v>772</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>681</v>
+        <v>773</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -7970,13 +9001,15 @@
       <c r="Y11" s="11"/>
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>682</v>
+        <v>774</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -7988,13 +9021,13 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>683</v>
+        <v>775</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>684</v>
+        <v>776</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>685</v>
+        <v>777</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -8007,6 +9040,8 @@
       <c r="Y12" s="11"/>
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -8023,10 +9058,10 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
-        <v>686</v>
+        <v>778</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>687</v>
+        <v>779</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -8040,6 +9075,8 @@
       <c r="Y13" s="11"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -8056,10 +9093,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
-        <v>688</v>
+        <v>780</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>689</v>
+        <v>781</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -8073,6 +9110,8 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11"/>
       <c r="AA14" s="11"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -8090,7 +9129,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>690</v>
+        <v>782</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -8104,6 +9143,8 @@
       <c r="Y15" s="11"/>
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -8121,7 +9162,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>691</v>
+        <v>783</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -8135,6 +9176,8 @@
       <c r="Y16" s="11"/>
       <c r="Z16" s="11"/>
       <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
+      <c r="AC16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -8152,7 +9195,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>692</v>
+        <v>784</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -8166,6 +9209,8 @@
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
+      <c r="AC17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -8183,7 +9228,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>693</v>
+        <v>785</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -8197,6 +9242,8 @@
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
       <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
+      <c r="AC18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -8214,7 +9261,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>694</v>
+        <v>786</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -8228,6 +9275,8 @@
       <c r="Y19" s="11"/>
       <c r="Z19" s="11"/>
       <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -8245,7 +9294,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>695</v>
+        <v>787</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -8259,6 +9308,8 @@
       <c r="Y20" s="11"/>
       <c r="Z20" s="11"/>
       <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8280,36 +9331,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>905</v>
+        <v>997</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>906</v>
+        <v>998</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>907</v>
+        <v>999</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>743</v>
+        <v>835</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>908</v>
+        <v>1000</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>909</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>910</v>
+        <v>1002</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>911</v>
+        <v>1003</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>912</v>
+        <v>1004</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -8347,80 +9398,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>913</v>
+        <v>1005</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>914</v>
+        <v>1006</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>735</v>
+        <v>827</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>915</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>916</v>
+        <v>1008</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>917</v>
+        <v>1009</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>918</v>
+        <v>1010</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>919</v>
+        <v>1011</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>791</v>
+        <v>883</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>920</v>
+        <v>1012</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>921</v>
+        <v>1013</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>922</v>
+        <v>1014</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>923</v>
+        <v>1015</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>924</v>
+        <v>1016</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>925</v>
+        <v>1017</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>926</v>
+        <v>1018</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>610</v>
+        <v>698</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>927</v>
+        <v>1019</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>928</v>
+        <v>1020</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>795</v>
+        <v>887</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>929</v>
+        <v>1021</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>930</v>
+        <v>1022</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>931</v>
+        <v>1023</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -8453,39 +9504,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>932</v>
+        <v>1024</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>933</v>
+        <v>1025</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>934</v>
+        <v>1026</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>935</v>
+        <v>1027</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>936</v>
+        <v>1028</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>937</v>
+        <v>1029</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>938</v>
+        <v>1030</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>939</v>
+        <v>1031</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>940</v>
+        <v>1032</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -8530,122 +9581,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>941</v>
+        <v>1033</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>942</v>
+        <v>1034</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>943</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>699</v>
+        <v>791</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>705</v>
+        <v>797</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>706</v>
+        <v>798</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>707</v>
+        <v>799</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>771</v>
+        <v>863</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>761</v>
+        <v>853</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>778</v>
+        <v>870</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>944</v>
+        <v>1036</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>885</v>
+        <v>977</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>945</v>
+        <v>1037</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>946</v>
+        <v>1038</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>947</v>
+        <v>1039</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>948</v>
+        <v>1040</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>949</v>
+        <v>1041</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>950</v>
+        <v>1042</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>951</v>
+        <v>1043</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>952</v>
+        <v>1044</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>953</v>
+        <v>1045</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>954</v>
+        <v>1046</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>955</v>
+        <v>1047</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>956</v>
+        <v>1048</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>957</v>
+        <v>1049</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>724</v>
+        <v>816</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>725</v>
+        <v>817</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>726</v>
+        <v>818</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>958</v>
+        <v>1050</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>959</v>
+        <v>1051</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>960</v>
+        <v>1052</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>961</v>
+        <v>1053</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>962</v>
+        <v>1054</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>963</v>
+        <v>1055</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>586</v>
+        <v>672</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -8681,27 +9732,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>964</v>
+        <v>1056</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>965</v>
+        <v>1057</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>966</v>
+        <v>1058</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>967</v>
+        <v>1059</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>968</v>
+        <v>1060</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>969</v>
+        <v>1061</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -8732,48 +9783,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>970</v>
+        <v>1062</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>971</v>
+        <v>1063</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>972</v>
+        <v>1064</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>973</v>
+        <v>1065</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>974</v>
+        <v>1066</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>975</v>
+        <v>1067</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>976</v>
+        <v>1068</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>977</v>
+        <v>1069</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>978</v>
+        <v>1070</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>979</v>
+        <v>1071</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>980</v>
+        <v>1072</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>588</v>
+        <v>674</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>589</v>
+        <v>675</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -8811,33 +9862,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>981</v>
+        <v>1073</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>982</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>983</v>
+        <v>1075</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>984</v>
+        <v>1076</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>985</v>
+        <v>1077</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>986</v>
+        <v>1078</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>693</v>
+        <v>785</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8865,30 +9916,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>987</v>
+        <v>1079</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>988</v>
+        <v>1080</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>989</v>
+        <v>1081</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>990</v>
+        <v>1082</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>991</v>
+        <v>1083</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>992</v>
+        <v>1084</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>993</v>
+        <v>1085</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -8917,15 +9968,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>994</v>
+        <v>1086</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>995</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -8951,21 +10002,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>994</v>
+        <v>1086</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>996</v>
+        <v>1088</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>997</v>
+        <v>1089</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>998</v>
+        <v>1090</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -9008,115 +10059,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>696</v>
+        <v>788</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>697</v>
+        <v>789</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>698</v>
+        <v>790</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>699</v>
+        <v>791</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>700</v>
+        <v>792</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>701</v>
+        <v>793</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>702</v>
+        <v>794</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>703</v>
+        <v>795</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>705</v>
+        <v>797</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>706</v>
+        <v>798</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>707</v>
+        <v>799</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>708</v>
+        <v>800</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>709</v>
+        <v>801</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>581</v>
+        <v>667</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>710</v>
+        <v>802</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>711</v>
+        <v>803</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>712</v>
+        <v>804</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>713</v>
+        <v>805</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>714</v>
+        <v>806</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>715</v>
+        <v>807</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>716</v>
+        <v>808</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>717</v>
+        <v>809</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>718</v>
+        <v>810</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>719</v>
+        <v>811</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>720</v>
+        <v>812</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>721</v>
+        <v>813</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>722</v>
+        <v>814</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>723</v>
+        <v>815</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>724</v>
+        <v>816</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>725</v>
+        <v>817</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>726</v>
+        <v>818</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>727</v>
+        <v>819</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>591</v>
+        <v>679</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -9144,33 +10195,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>996</v>
+        <v>1088</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>999</v>
+        <v>1091</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1000</v>
+        <v>1092</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1001</v>
+        <v>1093</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1002</v>
+        <v>1094</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1003</v>
+        <v>1095</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1004</v>
+        <v>1096</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1005</v>
+        <v>1097</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9201,51 +10252,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1006</v>
+        <v>1098</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1007</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1008</v>
+        <v>1100</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1009</v>
+        <v>1101</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1010</v>
+        <v>1102</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1011</v>
+        <v>1103</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1000</v>
+        <v>1092</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1012</v>
+        <v>1104</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1013</v>
+        <v>1105</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1014</v>
+        <v>1106</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>998</v>
+        <v>1090</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1015</v>
+        <v>1107</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1016</v>
+        <v>1108</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1017</v>
+        <v>1109</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -9260,6 +10311,500 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="24" style="11" customWidth="1"/>
+    <col min="5" max="5" width="20" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18" style="11" customWidth="1"/>
+    <col min="7" max="7" width="26" style="11" customWidth="1"/>
+    <col min="8" max="8" width="29" style="11" customWidth="1"/>
+    <col min="9" max="9" width="20" style="11" customWidth="1"/>
+    <col min="10" max="10" width="14" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14" style="11" customWidth="1"/>
+    <col min="13" max="13" width="22" style="11" customWidth="1"/>
+    <col min="14" max="14" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>1118</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>986</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>1128</v>
+      </c>
+      <c r="N2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="N2:N5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="26" style="11" customWidth="1"/>
+    <col min="4" max="4" width="31" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19" style="11" customWidth="1"/>
+    <col min="6" max="6" width="38" style="11" customWidth="1"/>
+    <col min="7" max="7" width="34" style="11" customWidth="1"/>
+    <col min="8" max="8" width="17" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="I2:I5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="33" style="11" customWidth="1"/>
+    <col min="3" max="3" width="40" style="11" customWidth="1"/>
+    <col min="4" max="4" width="17" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="18" style="11" customWidth="1"/>
+    <col min="4" max="4" width="27" style="11" customWidth="1"/>
+    <col min="5" max="5" width="17" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="C2:C5000">
+      <formula1>Lists!$AB$2:$AB$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="D2:D5000">
+      <formula1>Lists!$AC$2:$AC$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="32" style="11" customWidth="1"/>
+    <col min="3" max="3" width="26" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+    <col min="6" max="6" width="16" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="25" style="11" customWidth="1"/>
+    <col min="5" max="5" width="20" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+    <col min="9" max="9" width="16" style="11" customWidth="1"/>
+    <col min="10" max="10" width="30" style="11" customWidth="1"/>
+    <col min="11" max="11" width="26" style="11" customWidth="1"/>
+    <col min="12" max="12" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>1162</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="L2:L5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9277,56 +10822,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1018</v>
+        <v>1175</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1019</v>
+        <v>1176</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1020</v>
+        <v>1177</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1021</v>
+        <v>1178</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1022</v>
+        <v>1179</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>843</v>
+        <v>935</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>844</v>
+        <v>936</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1023</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1024</v>
+        <v>1181</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>693</v>
+        <v>785</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>572</v>
+        <v>658</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1025</v>
+        <v>1182</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1026</v>
+        <v>1183</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1027</v>
+        <v>1184</v>
       </c>
     </row>
   </sheetData>
@@ -9348,7 +10893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9373,70 +10918,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1028</v>
+        <v>1110</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1029</v>
+        <v>1185</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1030</v>
+        <v>1186</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1031</v>
+        <v>1187</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1032</v>
+        <v>1188</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1033</v>
+        <v>1189</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1034</v>
+        <v>1190</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>549</v>
+        <v>633</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1035</v>
+        <v>1191</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1036</v>
+        <v>1192</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1037</v>
+        <v>1193</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>746</v>
+        <v>838</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1038</v>
+        <v>1194</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>844</v>
+        <v>936</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1023</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1039</v>
+        <v>1195</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1040</v>
+        <v>1196</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>658</v>
+        <v>749</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>620</v>
+        <v>710</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1041</v>
+        <v>1197</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9445,10 +10990,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1026</v>
+        <v>1183</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -9472,7 +11017,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>824</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9490,55 +11072,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1028</v>
+        <v>1110</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1029</v>
+        <v>1185</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>581</v>
+        <v>667</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>709</v>
+        <v>801</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1022</v>
+        <v>1179</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1038</v>
+        <v>1194</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>844</v>
+        <v>936</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1023</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1042</v>
+        <v>1198</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1043</v>
+        <v>1199</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>725</v>
+        <v>817</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1043</v>
+        <v>1199</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1044</v>
+        <v>1200</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1026</v>
+        <v>1183</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -9552,7 +11134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9565,30 +11147,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1045</v>
+        <v>1201</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1046</v>
+        <v>1202</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1047</v>
+        <v>1203</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1023</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1048</v>
+        <v>1204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>659</v>
+        <v>750</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1049</v>
+        <v>1205</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1050</v>
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -9597,14 +11179,14 @@
       <formula1>Lists!$P$2:$P$12</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
-      <formula1>Lists!$M$2:$M$8</formula1>
+      <formula1>Lists!$M$2:$M$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9621,54 +11203,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1051</v>
+        <v>1207</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1052</v>
+        <v>1208</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1053</v>
+        <v>1209</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1054</v>
+        <v>1210</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1055</v>
+        <v>1211</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>550</v>
+        <v>634</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1056</v>
+        <v>1212</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1057</v>
+        <v>1213</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1058</v>
+        <v>1214</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1059</v>
+        <v>1215</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1060</v>
+        <v>1216</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1005</v>
+        <v>1097</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>576</v>
+        <v>662</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1061</v>
+        <v>1217</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -9680,43 +11262,6 @@
       <formula1>Lists!$A$2:$A$3</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="17" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14" style="11" customWidth="1"/>
-    <col min="3" max="3" width="17" style="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="20" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>732</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9735,33 +11280,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>733</v>
+        <v>825</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>734</v>
+        <v>826</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>735</v>
+        <v>827</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>736</v>
+        <v>828</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>737</v>
+        <v>829</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>738</v>
+        <v>830</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>739</v>
+        <v>831</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>740</v>
+        <v>832</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9791,43 +11336,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>741</v>
+        <v>833</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>742</v>
+        <v>834</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>743</v>
+        <v>835</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>744</v>
+        <v>836</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>746</v>
+        <v>838</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>747</v>
+        <v>839</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>748</v>
+        <v>840</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>749</v>
+        <v>841</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>750</v>
+        <v>842</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>751</v>
+        <v>843</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -9858,48 +11403,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>752</v>
+        <v>844</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>753</v>
+        <v>845</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>754</v>
+        <v>846</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>755</v>
+        <v>847</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>744</v>
+        <v>836</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>756</v>
+        <v>848</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>757</v>
+        <v>849</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>758</v>
+        <v>850</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>748</v>
+        <v>840</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>750</v>
+        <v>842</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>643</v>
+        <v>734</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9936,53 +11481,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>759</v>
+        <v>851</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>760</v>
+        <v>852</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>796</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>761</v>
+        <v>853</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>754</v>
+        <v>846</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>762</v>
+        <v>854</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>708</v>
+        <v>800</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>763</v>
+        <v>855</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>744</v>
+        <v>836</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>764</v>
+        <v>856</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>765</v>
+        <v>857</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>766</v>
+        <v>858</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>767</v>
+        <v>859</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>768</v>
+        <v>860</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -10015,33 +11560,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>769</v>
+        <v>861</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>770</v>
+        <v>862</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>771</v>
+        <v>863</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>708</v>
+        <v>800</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>772</v>
+        <v>864</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>773</v>
+        <v>865</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>774</v>
+        <v>866</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>775</v>
+        <v>867</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -41,12 +41,14 @@
     <sheet name="LGU Rates" sheetId="34" r:id="rId34"/>
     <sheet name="Authority Limits" sheetId="35" r:id="rId35"/>
     <sheet name="Numbering" sheetId="36" r:id="rId36"/>
+    <sheet name="Payee Bank Accounts" sheetId="37" r:id="rId37"/>
+    <sheet name="COC Series" sheetId="38" r:id="rId38"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1123">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -315,6 +317,18 @@
     <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code</t>
   </si>
   <si>
+    <t xml:space="preserve">35. Payee Bank Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts (Payee bank accounts). Key: Payee Type + Payee + Account Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36. COC Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From</t>
+  </si>
+  <si>
     <t xml:space="preserve">Validate, fix and load</t>
   </si>
   <si>
@@ -432,6 +446,18 @@
     <t xml:space="preserve">Master &gt; Finance &gt; Payment Gateways</t>
   </si>
   <si>
+    <t xml:space="preserve">Integration connectors (endpoint, mode, credential variable names; the credentials themselves in the secret store), message templates, insurer API mappings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; Integrations / Message Templates / Insurer Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank file layouts (validate each starter layout with the bank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts</t>
+  </si>
+  <si>
     <t xml:space="preserve">Application name, logo, colours, display currency, language</t>
   </si>
   <si>
@@ -1665,6 +1691,96 @@
     <t xml:space="preserve">Numbering: Active</t>
   </si>
   <si>
+    <t xml:space="preserve">Payee Bank Accounts: Payee Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Insurer, Agent/Referrer, Customer or Supplier. Values: Lists sheet, Payee Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Payee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Insurer code, referrer id, client code or supplier code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Code of the Bank master (BDO, BPI, MBT, LBP, UBP ...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Account Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Digits, spaces and -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Account Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Account Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. savings or current (savings when empty). Values: Lists sheet, Bank Account Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Bank Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. E-mail for the bank's credit advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Insurer code (or name). Values: Lists sheet, Insurers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Branch Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Branch the series is for; empty = every branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Prefix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Capital letters, digits and -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: From</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. First COC number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Last COC number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Next Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Next number not yet used (the first number when empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Digits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Digits of the number, zero-padded (8 when empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Remarks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes No</t>
   </si>
   <si>
@@ -1746,6 +1862,12 @@
     <t xml:space="preserve">Cover Lines of business (blank: every line)</t>
   </si>
   <si>
+    <t xml:space="preserve">Payee Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Account Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
@@ -1821,6 +1943,12 @@
     <t xml:space="preserve">motor</t>
   </si>
   <si>
+    <t xml:space="preserve">Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">savings</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
@@ -1896,6 +2024,12 @@
     <t xml:space="preserve">fire</t>
   </si>
   <si>
+    <t xml:space="preserve">Agent/Referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">current</t>
+  </si>
+  <si>
     <t xml:space="preserve">equity</t>
   </si>
   <si>
@@ -1953,6 +2087,9 @@
     <t xml:space="preserve">accident</t>
   </si>
   <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
     <t xml:space="preserve">income</t>
   </si>
   <si>
@@ -1992,6 +2129,9 @@
     <t xml:space="preserve">engineering</t>
   </si>
   <si>
+    <t xml:space="preserve">Supplier</t>
+  </si>
+  <si>
     <t xml:space="preserve">expense</t>
   </si>
   <si>
@@ -3102,9 +3242,6 @@
     <t xml:space="preserve">MPV</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Product</t>
   </si>
   <si>
@@ -3232,6 +3369,54 @@
   </si>
   <si>
     <t xml:space="preserve">1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Type *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0071-2345-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malayan Insurance Co., Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurer *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
 </sst>
 </file>
@@ -3241,7 +3426,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3268,8 +3453,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3297,6 +3496,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3328,7 +3545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3351,6 +3568,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3360,7 +3582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3730,26 +3952,26 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="10"/>
+      <c r="B47" s="4" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" s="4" t="s">
+      <c r="A49" s="10" t="s">
         <v>93</v>
       </c>
+      <c r="B49" s="10"/>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
@@ -3768,26 +3990,26 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="10"/>
+      <c r="B52" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B54" s="4" t="s">
+      <c r="A54" s="10" t="s">
         <v>102</v>
       </c>
+      <c r="B54" s="10"/>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
@@ -3814,26 +4036,26 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="B58" s="10"/>
+      <c r="B58" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="B60" s="4" t="s">
+      <c r="A60" s="10" t="s">
         <v>113</v>
       </c>
+      <c r="B60" s="10"/>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
@@ -3964,185 +4186,185 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="B77" s="10"/>
+      <c r="B77" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="A81" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B81" s="10"/>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100">
@@ -4158,631 +4380,631 @@
         <v>179</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>148</v>
+        <v>226</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>151</v>
+        <v>233</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>245</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>151</v>
+        <v>253</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>255</v>
+        <v>156</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>259</v>
+        <v>199</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="180">
@@ -4790,231 +5012,231 @@
         <v>276</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>148</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>148</v>
+        <v>281</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>148</v>
+        <v>283</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>245</v>
+        <v>156</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>151</v>
+        <v>298</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>302</v>
+        <v>159</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>304</v>
+        <v>180</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>315</v>
+        <v>159</v>
       </c>
     </row>
     <row r="209">
@@ -5030,623 +5252,623 @@
         <v>318</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>148</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>148</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>148</v>
+        <v>323</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>148</v>
+        <v>330</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>333</v>
+        <v>156</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>148</v>
+        <v>341</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>341</v>
+        <v>156</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>151</v>
+        <v>349</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>352</v>
+        <v>298</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>354</v>
+        <v>159</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>356</v>
+        <v>159</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>148</v>
+        <v>364</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>368</v>
+        <v>180</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>151</v>
+        <v>376</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>378</v>
+        <v>159</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>385</v>
+        <v>180</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>148</v>
+        <v>391</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>148</v>
+        <v>393</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>403</v>
+        <v>156</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>405</v>
+        <v>233</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>407</v>
+        <v>156</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>409</v>
+        <v>159</v>
       </c>
     </row>
     <row r="288">
@@ -5654,383 +5876,383 @@
         <v>410</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>151</v>
+        <v>411</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>290</v>
+        <v>413</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>172</v>
+        <v>417</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>148</v>
+        <v>298</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>148</v>
+        <v>421</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>424</v>
+        <v>156</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>426</v>
+        <v>156</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>428</v>
+        <v>156</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>148</v>
+        <v>432</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>148</v>
+        <v>434</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>151</v>
+        <v>436</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>434</v>
+        <v>180</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>148</v>
+        <v>442</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>440</v>
+        <v>180</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>449</v>
+        <v>180</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>148</v>
+        <v>453</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>172</v>
+        <v>457</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>245</v>
+        <v>156</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>463</v>
+        <v>156</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>465</v>
+        <v>253</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>467</v>
+        <v>159</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>469</v>
+        <v>180</v>
       </c>
     </row>
     <row r="336">
@@ -6046,63 +6268,63 @@
         <v>472</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>288</v>
+        <v>473</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>259</v>
+        <v>479</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>479</v>
+        <v>296</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>485</v>
+        <v>267</v>
       </c>
     </row>
     <row r="345">
@@ -6158,79 +6380,79 @@
         <v>498</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>259</v>
+        <v>499</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>259</v>
+        <v>501</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>259</v>
+        <v>505</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>505</v>
+        <v>484</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>507</v>
+        <v>267</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>509</v>
+        <v>267</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>511</v>
+        <v>267</v>
       </c>
     </row>
     <row r="361">
@@ -6246,111 +6468,111 @@
         <v>514</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>259</v>
+        <v>515</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>259</v>
+        <v>517</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>313</v>
+        <v>519</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>259</v>
+        <v>521</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>519</v>
+        <v>267</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>521</v>
+        <v>267</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>523</v>
+        <v>321</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>259</v>
+        <v>529</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>531</v>
+        <v>267</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>535</v>
+        <v>267</v>
       </c>
     </row>
     <row r="376">
@@ -6366,7 +6588,175 @@
         <v>538</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>313</v>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0" t="s">
+        <v>546</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0" t="s">
+        <v>547</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="0" t="s">
+        <v>551</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="B392" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -6397,82 +6787,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>776</v>
+        <v>822</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>777</v>
+        <v>823</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>706</v>
+        <v>752</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>707</v>
+        <v>753</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>711</v>
+        <v>757</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>712</v>
+        <v>758</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>779</v>
+        <v>825</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>780</v>
+        <v>826</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>781</v>
+        <v>827</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>782</v>
+        <v>828</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>783</v>
+        <v>829</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>785</v>
+        <v>831</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>787</v>
+        <v>833</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>726</v>
+        <v>772</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>788</v>
+        <v>834</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -6501,33 +6891,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>789</v>
+        <v>835</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>790</v>
+        <v>836</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>792</v>
+        <v>838</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>794</v>
+        <v>840</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>795</v>
+        <v>841</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6555,33 +6945,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>796</v>
+        <v>842</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>797</v>
+        <v>843</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>798</v>
+        <v>844</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>799</v>
+        <v>845</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>800</v>
+        <v>846</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>801</v>
+        <v>847</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>802</v>
+        <v>848</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6611,45 +7001,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>803</v>
+        <v>849</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>804</v>
+        <v>850</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>789</v>
+        <v>835</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>805</v>
+        <v>851</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>806</v>
+        <v>852</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>807</v>
+        <v>853</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>808</v>
+        <v>854</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>809</v>
+        <v>855</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>810</v>
+        <v>856</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>811</v>
+        <v>857</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -6685,74 +7075,74 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>812</v>
+        <v>858</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>813</v>
+        <v>859</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>814</v>
+        <v>860</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>815</v>
+        <v>861</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>816</v>
+        <v>862</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>817</v>
+        <v>863</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>818</v>
+        <v>864</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>819</v>
+        <v>865</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>743</v>
+        <v>789</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>820</v>
+        <v>866</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>821</v>
+        <v>867</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>822</v>
+        <v>868</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>823</v>
+        <v>869</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>824</v>
+        <v>870</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>825</v>
+        <v>871</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>826</v>
+        <v>872</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>795</v>
+        <v>841</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>571</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -6788,69 +7178,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>827</v>
+        <v>873</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>828</v>
+        <v>874</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>829</v>
+        <v>875</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>830</v>
+        <v>876</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>831</v>
+        <v>877</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>832</v>
+        <v>878</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>833</v>
+        <v>879</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>834</v>
+        <v>880</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>835</v>
+        <v>881</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>836</v>
+        <v>882</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>837</v>
+        <v>883</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>838</v>
+        <v>884</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>839</v>
+        <v>885</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>840</v>
+        <v>886</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>840</v>
+        <v>886</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>841</v>
+        <v>887</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>811</v>
+        <v>857</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>842</v>
+        <v>888</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>591</v>
+        <v>633</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -6881,51 +7271,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>843</v>
+        <v>889</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>844</v>
+        <v>890</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>827</v>
+        <v>873</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>845</v>
+        <v>891</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>846</v>
+        <v>892</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>847</v>
+        <v>893</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>848</v>
+        <v>894</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>849</v>
+        <v>895</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>850</v>
+        <v>896</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>851</v>
+        <v>897</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>853</v>
+        <v>899</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>854</v>
+        <v>900</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>855</v>
+        <v>901</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -6959,67 +7349,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>856</v>
+        <v>902</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>857</v>
+        <v>903</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>858</v>
+        <v>904</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>859</v>
+        <v>905</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>543</v>
+        <v>581</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>860</v>
+        <v>906</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>861</v>
+        <v>907</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>862</v>
+        <v>908</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>863</v>
+        <v>909</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>648</v>
+        <v>694</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>674</v>
+        <v>720</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>674</v>
+        <v>720</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>591</v>
+        <v>633</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>571</v>
+        <v>611</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -7072,87 +7462,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>864</v>
+        <v>910</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>865</v>
+        <v>911</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>866</v>
+        <v>912</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>867</v>
+        <v>913</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>706</v>
+        <v>752</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>707</v>
+        <v>753</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>868</v>
+        <v>914</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>712</v>
+        <v>758</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>859</v>
+        <v>905</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>869</v>
+        <v>915</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>870</v>
+        <v>916</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>871</v>
+        <v>917</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>872</v>
+        <v>918</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>873</v>
+        <v>919</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>874</v>
+        <v>920</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>726</v>
+        <v>772</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>875</v>
+        <v>921</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>876</v>
+        <v>922</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>608</v>
+        <v>650</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -7197,117 +7587,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>856</v>
+        <v>902</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>857</v>
+        <v>903</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>864</v>
+        <v>910</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>877</v>
+        <v>923</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>878</v>
+        <v>924</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>879</v>
+        <v>925</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>880</v>
+        <v>926</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>881</v>
+        <v>927</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>882</v>
+        <v>928</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>883</v>
+        <v>929</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>884</v>
+        <v>930</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>885</v>
+        <v>931</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>886</v>
+        <v>932</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>887</v>
+        <v>933</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>888</v>
+        <v>934</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>889</v>
+        <v>935</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>890</v>
+        <v>936</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>891</v>
+        <v>937</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>892</v>
+        <v>938</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>893</v>
+        <v>939</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>894</v>
+        <v>940</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>895</v>
+        <v>941</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>584</v>
+        <v>624</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>896</v>
+        <v>942</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>897</v>
+        <v>943</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>898</v>
+        <v>944</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>899</v>
+        <v>945</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>900</v>
+        <v>946</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>901</v>
+        <v>947</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>902</v>
+        <v>948</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>903</v>
+        <v>949</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>896</v>
+        <v>942</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>904</v>
+        <v>950</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>900</v>
+        <v>946</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -7326,7 +7716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
@@ -7356,368 +7746,392 @@
     <col min="25" max="25" width="28" style="11" customWidth="1"/>
     <col min="26" max="26" width="30" style="11" customWidth="1"/>
     <col min="27" max="27" width="47" style="11" customWidth="1"/>
+    <col min="28" max="28" width="14" style="11" customWidth="1"/>
+    <col min="29" max="29" width="21" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="20" customHeight="1">
+    <row r="1" spans="1:29" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>543</v>
+        <v>581</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>545</v>
+        <v>583</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>546</v>
+        <v>584</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>547</v>
+        <v>585</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>548</v>
+        <v>586</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>549</v>
+        <v>587</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>550</v>
+        <v>588</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>551</v>
+        <v>589</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>552</v>
+        <v>590</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>553</v>
+        <v>591</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>556</v>
+        <v>594</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>558</v>
+        <v>596</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>559</v>
+        <v>597</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>562</v>
+        <v>600</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>563</v>
+        <v>601</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>564</v>
+        <v>602</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>565</v>
+        <v>603</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>568</v>
+        <v>608</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>569</v>
+        <v>609</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>570</v>
+        <v>610</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>571</v>
+        <v>611</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>571</v>
+        <v>611</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>572</v>
+        <v>612</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>573</v>
+        <v>613</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>574</v>
+        <v>614</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>575</v>
+        <v>615</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>577</v>
+        <v>617</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>578</v>
+        <v>618</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>579</v>
+        <v>619</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>582</v>
+        <v>622</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>583</v>
+        <v>623</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>584</v>
+        <v>624</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>585</v>
+        <v>625</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>586</v>
+        <v>626</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>587</v>
+        <v>627</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>573</v>
+        <v>613</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>590</v>
+        <v>630</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>591</v>
+        <v>633</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>593</v>
+        <v>635</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>594</v>
+        <v>636</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>595</v>
+        <v>637</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>597</v>
+        <v>639</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>599</v>
+        <v>641</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>600</v>
+        <v>642</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>601</v>
+        <v>643</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>602</v>
+        <v>644</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>603</v>
+        <v>645</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>604</v>
+        <v>646</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>605</v>
+        <v>647</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>606</v>
+        <v>648</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>607</v>
+        <v>649</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>608</v>
+        <v>650</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>610</v>
+        <v>652</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>611</v>
+        <v>653</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>612</v>
+        <v>654</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>613</v>
+        <v>655</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>614</v>
+        <v>656</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>615</v>
+        <v>657</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="AC3" s="11" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>617</v>
+        <v>661</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>618</v>
+        <v>662</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>619</v>
+        <v>663</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>621</v>
+        <v>665</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>623</v>
+        <v>667</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>624</v>
+        <v>668</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>625</v>
+        <v>669</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>626</v>
+        <v>670</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>629</v>
+        <v>673</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>630</v>
+        <v>674</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>631</v>
+        <v>675</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>632</v>
+        <v>676</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>633</v>
+        <v>677</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>634</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="AC4" s="11"/>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>636</v>
+        <v>681</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>638</v>
+        <v>683</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>641</v>
+        <v>686</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>642</v>
+        <v>687</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>644</v>
+        <v>689</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -7726,44 +8140,48 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>647</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>648</v>
+        <v>694</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>649</v>
+        <v>695</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>653</v>
+        <v>699</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>654</v>
+        <v>700</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>655</v>
+        <v>701</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -7773,37 +8191,39 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>656</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>657</v>
+        <v>703</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>662</v>
+        <v>708</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -7816,15 +8236,17 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>663</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>664</v>
+        <v>710</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -7835,16 +8257,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>665</v>
+        <v>711</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>666</v>
+        <v>712</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>667</v>
+        <v>713</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -7857,15 +8279,17 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>669</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>670</v>
+        <v>716</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -7877,13 +8301,13 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>673</v>
+        <v>719</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -7896,13 +8320,15 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>674</v>
+        <v>720</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -7914,13 +8340,13 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11" t="s">
-        <v>675</v>
+        <v>721</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>677</v>
+        <v>723</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -7933,13 +8359,15 @@
       <c r="Y10" s="11"/>
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>678</v>
+        <v>724</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -7951,13 +8379,13 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>679</v>
+        <v>725</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>680</v>
+        <v>726</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>681</v>
+        <v>727</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -7970,13 +8398,15 @@
       <c r="Y11" s="11"/>
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>682</v>
+        <v>728</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -7988,13 +8418,13 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>683</v>
+        <v>729</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>684</v>
+        <v>730</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>685</v>
+        <v>731</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -8007,6 +8437,8 @@
       <c r="Y12" s="11"/>
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -8023,10 +8455,10 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
-        <v>686</v>
+        <v>732</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>687</v>
+        <v>733</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -8040,6 +8472,8 @@
       <c r="Y13" s="11"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -8056,10 +8490,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
-        <v>688</v>
+        <v>734</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>689</v>
+        <v>735</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -8073,6 +8507,8 @@
       <c r="Y14" s="11"/>
       <c r="Z14" s="11"/>
       <c r="AA14" s="11"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -8090,7 +8526,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>690</v>
+        <v>736</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -8104,6 +8540,8 @@
       <c r="Y15" s="11"/>
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -8121,7 +8559,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>691</v>
+        <v>737</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -8135,6 +8573,8 @@
       <c r="Y16" s="11"/>
       <c r="Z16" s="11"/>
       <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
+      <c r="AC16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -8152,7 +8592,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>692</v>
+        <v>738</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -8166,6 +8606,8 @@
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
+      <c r="AC17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -8183,7 +8625,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>693</v>
+        <v>739</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -8197,6 +8639,8 @@
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
       <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
+      <c r="AC18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -8214,7 +8658,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>694</v>
+        <v>740</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -8228,6 +8672,8 @@
       <c r="Y19" s="11"/>
       <c r="Z19" s="11"/>
       <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -8245,7 +8691,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>695</v>
+        <v>741</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -8259,6 +8705,8 @@
       <c r="Y20" s="11"/>
       <c r="Z20" s="11"/>
       <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8280,36 +8728,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>905</v>
+        <v>951</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>906</v>
+        <v>952</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>907</v>
+        <v>953</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>743</v>
+        <v>789</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>908</v>
+        <v>954</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>909</v>
+        <v>955</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>910</v>
+        <v>956</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>911</v>
+        <v>957</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>912</v>
+        <v>958</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -8347,80 +8795,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>913</v>
+        <v>959</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>914</v>
+        <v>960</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>735</v>
+        <v>781</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>915</v>
+        <v>961</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>916</v>
+        <v>962</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>917</v>
+        <v>963</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>918</v>
+        <v>964</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>919</v>
+        <v>965</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>920</v>
+        <v>966</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>921</v>
+        <v>967</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>922</v>
+        <v>968</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>923</v>
+        <v>969</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>924</v>
+        <v>970</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>925</v>
+        <v>971</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>926</v>
+        <v>972</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>610</v>
+        <v>652</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>927</v>
+        <v>973</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>928</v>
+        <v>974</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>795</v>
+        <v>841</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>929</v>
+        <v>975</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>930</v>
+        <v>976</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>931</v>
+        <v>977</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -8453,39 +8901,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>932</v>
+        <v>978</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>933</v>
+        <v>979</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>934</v>
+        <v>980</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>935</v>
+        <v>981</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>936</v>
+        <v>982</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>937</v>
+        <v>983</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>938</v>
+        <v>984</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>939</v>
+        <v>985</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>940</v>
+        <v>986</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -8530,122 +8978,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>941</v>
+        <v>987</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>942</v>
+        <v>988</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>943</v>
+        <v>989</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>706</v>
+        <v>752</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>707</v>
+        <v>753</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>944</v>
+        <v>990</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>885</v>
+        <v>931</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>945</v>
+        <v>991</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>946</v>
+        <v>992</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>947</v>
+        <v>993</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>948</v>
+        <v>994</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>949</v>
+        <v>995</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>950</v>
+        <v>996</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>951</v>
+        <v>997</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>952</v>
+        <v>998</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>953</v>
+        <v>999</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>954</v>
+        <v>1000</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>955</v>
+        <v>1001</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>956</v>
+        <v>1002</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>957</v>
+        <v>1003</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>724</v>
+        <v>770</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>726</v>
+        <v>772</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>958</v>
+        <v>1004</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>959</v>
+        <v>1005</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>960</v>
+        <v>1006</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>961</v>
+        <v>1007</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>962</v>
+        <v>1008</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>963</v>
+        <v>1009</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>586</v>
+        <v>626</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -8681,27 +9129,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>964</v>
+        <v>1010</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>965</v>
+        <v>1011</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>966</v>
+        <v>1012</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>967</v>
+        <v>1013</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>968</v>
+        <v>1014</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>969</v>
+        <v>1015</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -8732,48 +9180,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>970</v>
+        <v>1016</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>971</v>
+        <v>1017</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>972</v>
+        <v>1018</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>973</v>
+        <v>1019</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>974</v>
+        <v>1020</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>975</v>
+        <v>1021</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>976</v>
+        <v>1022</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>977</v>
+        <v>1023</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>978</v>
+        <v>1024</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>979</v>
+        <v>1025</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>980</v>
+        <v>1026</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -8811,33 +9259,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>981</v>
+        <v>1027</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>982</v>
+        <v>1028</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>983</v>
+        <v>1029</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>984</v>
+        <v>1030</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>985</v>
+        <v>1031</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>986</v>
+        <v>1032</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>693</v>
+        <v>739</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8865,30 +9313,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>987</v>
+        <v>1033</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>988</v>
+        <v>1034</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>989</v>
+        <v>1035</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>990</v>
+        <v>1036</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>991</v>
+        <v>1037</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>992</v>
+        <v>1038</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>993</v>
+        <v>1039</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -8917,15 +9365,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>994</v>
+        <v>1040</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>995</v>
+        <v>1041</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -8951,21 +9399,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>994</v>
+        <v>1040</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>996</v>
+        <v>1042</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>997</v>
+        <v>1043</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>998</v>
+        <v>1044</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -9008,115 +9456,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>696</v>
+        <v>742</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>697</v>
+        <v>743</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>698</v>
+        <v>744</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>700</v>
+        <v>746</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>701</v>
+        <v>747</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>702</v>
+        <v>748</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>703</v>
+        <v>749</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>705</v>
+        <v>751</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>706</v>
+        <v>752</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>707</v>
+        <v>753</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>708</v>
+        <v>754</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>709</v>
+        <v>755</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>710</v>
+        <v>756</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>711</v>
+        <v>757</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>712</v>
+        <v>758</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>713</v>
+        <v>759</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>714</v>
+        <v>760</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>715</v>
+        <v>761</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>716</v>
+        <v>762</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>717</v>
+        <v>763</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>718</v>
+        <v>764</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>719</v>
+        <v>765</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>720</v>
+        <v>766</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>721</v>
+        <v>767</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>722</v>
+        <v>768</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>723</v>
+        <v>769</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>724</v>
+        <v>770</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>726</v>
+        <v>772</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>727</v>
+        <v>773</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>591</v>
+        <v>633</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -9144,33 +9592,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>996</v>
+        <v>1042</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>999</v>
+        <v>1045</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1000</v>
+        <v>1046</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1001</v>
+        <v>1047</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1002</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1003</v>
+        <v>1049</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1004</v>
+        <v>1050</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1005</v>
+        <v>1051</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9201,51 +9649,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1006</v>
+        <v>1052</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1007</v>
+        <v>1053</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1008</v>
+        <v>1054</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1009</v>
+        <v>1055</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1010</v>
+        <v>1056</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1011</v>
+        <v>1057</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1000</v>
+        <v>1046</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1012</v>
+        <v>1058</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1013</v>
+        <v>1059</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1014</v>
+        <v>1060</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>998</v>
+        <v>1044</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1015</v>
+        <v>1061</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1016</v>
+        <v>1062</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1017</v>
+        <v>1063</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -9277,56 +9725,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1018</v>
+        <v>631</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1019</v>
+        <v>1064</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1020</v>
+        <v>1065</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1021</v>
+        <v>1066</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1022</v>
+        <v>1067</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>843</v>
+        <v>889</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>844</v>
+        <v>890</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1023</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1024</v>
+        <v>1069</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>693</v>
+        <v>739</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>572</v>
+        <v>612</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1025</v>
+        <v>1070</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1026</v>
+        <v>1071</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1027</v>
+        <v>1072</v>
       </c>
     </row>
   </sheetData>
@@ -9373,70 +9821,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1028</v>
+        <v>1073</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1029</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1033</v>
+        <v>1078</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1034</v>
+        <v>1079</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>549</v>
+        <v>587</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1035</v>
+        <v>1080</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1036</v>
+        <v>1081</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1037</v>
+        <v>1082</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1038</v>
+        <v>1083</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>844</v>
+        <v>890</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1023</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1039</v>
+        <v>1084</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1040</v>
+        <v>1085</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>658</v>
+        <v>704</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1041</v>
+        <v>1086</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9445,10 +9893,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1026</v>
+        <v>1071</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -9490,55 +9938,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1028</v>
+        <v>1073</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1029</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>709</v>
+        <v>755</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1022</v>
+        <v>1067</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1038</v>
+        <v>1083</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>844</v>
+        <v>890</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1023</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1042</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1043</v>
+        <v>1088</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1043</v>
+        <v>1088</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1044</v>
+        <v>1089</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1026</v>
+        <v>1071</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -9565,30 +10013,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1045</v>
+        <v>1090</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1046</v>
+        <v>1091</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1047</v>
+        <v>1092</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1023</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1048</v>
+        <v>1093</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1049</v>
+        <v>1094</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -9621,54 +10069,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1051</v>
+        <v>1096</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1052</v>
+        <v>1097</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1053</v>
+        <v>1098</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1054</v>
+        <v>1099</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1055</v>
+        <v>1100</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>550</v>
+        <v>588</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1056</v>
+        <v>1101</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1057</v>
+        <v>1102</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1058</v>
+        <v>1103</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1059</v>
+        <v>1104</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1060</v>
+        <v>1105</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1005</v>
+        <v>1051</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1061</v>
+        <v>1106</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -9678,6 +10126,165 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
       <formula1>Lists!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15" style="11" customWidth="1"/>
+    <col min="4" max="4" width="20" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
+        <v>606</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="A2:A5000">
+      <formula1>Lists!$AB$2:$AB$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
+      <formula1>Lists!$AC$2:$AC$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="I2:I5000">
+      <formula1>Lists!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
+      <formula1>Lists!$N$2:$N$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9696,24 +10303,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>728</v>
+        <v>774</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>729</v>
+        <v>775</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>730</v>
+        <v>776</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>731</v>
+        <v>777</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>732</v>
+        <v>778</v>
       </c>
     </row>
   </sheetData>
@@ -9735,33 +10342,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>733</v>
+        <v>779</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>734</v>
+        <v>780</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>735</v>
+        <v>781</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>736</v>
+        <v>782</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>737</v>
+        <v>783</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>738</v>
+        <v>784</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>739</v>
+        <v>785</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>740</v>
+        <v>786</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9791,43 +10398,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>741</v>
+        <v>787</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>742</v>
+        <v>788</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>743</v>
+        <v>789</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>747</v>
+        <v>793</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>748</v>
+        <v>794</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -9858,48 +10465,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>752</v>
+        <v>798</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>753</v>
+        <v>799</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>754</v>
+        <v>800</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>756</v>
+        <v>802</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>757</v>
+        <v>803</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>748</v>
+        <v>794</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9936,53 +10543,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>759</v>
+        <v>805</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>750</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>708</v>
-      </c>
       <c r="H1" s="8" t="s">
-        <v>763</v>
+        <v>809</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>764</v>
+        <v>810</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>765</v>
+        <v>811</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>767</v>
+        <v>813</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>768</v>
+        <v>814</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -10015,33 +10622,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>770</v>
+        <v>816</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>708</v>
+        <v>754</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>773</v>
+        <v>819</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>774</v>
+        <v>820</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>775</v>
+        <v>821</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1068">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -466,6 +466,24 @@
   </si>
   <si>
     <t xml:space="preserve">Commission &gt; Agents/Referrer Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC licences of the firm, its officers and the agents and sub-agents paid commission (an agent without a licence in force is not paid: compliance.referrer_licence_check)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance &gt; Insurance Commission &gt; Licence Register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fit and proper records of the directors and officers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance &gt; Insurance Commission &gt; Fit and Proper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC certificate of authority number and validity of each insurer (columns of the Insurance Company sheet), mapping of the ledger to the IC annual statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance &gt; Insurance Commission &gt; Insurer Authority / IC Annual Statement &gt; Account mapping</t>
   </si>
   <si>
     <t xml:space="preserve">Petty cash funds</t>
@@ -3241,7 +3259,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3268,8 +3286,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3297,6 +3329,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3328,7 +3378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3351,6 +3401,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3360,7 +3415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3964,62 +4019,62 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="B77" s="10"/>
+      <c r="B77" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="A80" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B80" s="10"/>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>157</v>
@@ -4027,7 +4082,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>157</v>
@@ -4035,106 +4090,106 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="99">
@@ -4158,551 +4213,551 @@
         <v>179</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>207</v>
+        <v>154</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>151</v>
+        <v>216</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>148</v>
+        <v>224</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>151</v>
+        <v>231</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>245</v>
+        <v>154</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>148</v>
+        <v>251</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>259</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170">
@@ -4710,71 +4765,71 @@
         <v>260</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="179">
@@ -4790,191 +4845,191 @@
         <v>276</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>148</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>148</v>
+        <v>281</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>245</v>
+        <v>154</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>172</v>
+        <v>251</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>288</v>
+        <v>157</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>290</v>
+        <v>176</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>172</v>
+        <v>300</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>302</v>
+        <v>178</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>306</v>
+        <v>154</v>
       </c>
     </row>
     <row r="204">
@@ -4982,31 +5037,31 @@
         <v>307</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>313</v>
+        <v>157</v>
       </c>
     </row>
     <row r="208">
@@ -5030,263 +5085,263 @@
         <v>318</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>148</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>148</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>148</v>
+        <v>323</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>322</v>
+        <v>154</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>151</v>
+        <v>328</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>333</v>
+        <v>154</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>148</v>
+        <v>339</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>151</v>
+        <v>347</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>290</v>
+        <v>157</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>155</v>
+        <v>296</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>352</v>
+        <v>157</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>354</v>
+        <v>157</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>356</v>
+        <v>161</v>
       </c>
     </row>
     <row r="243">
@@ -5294,351 +5349,351 @@
         <v>357</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>172</v>
+        <v>358</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>368</v>
+        <v>154</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>151</v>
+        <v>374</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>378</v>
+        <v>157</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>148</v>
+        <v>384</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>383</v>
+        <v>178</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>385</v>
+        <v>154</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>172</v>
+        <v>389</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>148</v>
+        <v>391</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>403</v>
+        <v>231</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>405</v>
+        <v>154</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>407</v>
+        <v>157</v>
       </c>
     </row>
     <row r="287">
@@ -5654,119 +5709,119 @@
         <v>410</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>151</v>
+        <v>411</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>290</v>
+        <v>413</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>148</v>
+        <v>296</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>148</v>
+        <v>419</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>424</v>
+        <v>154</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>426</v>
+        <v>154</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>428</v>
+        <v>154</v>
       </c>
     </row>
     <row r="303">
@@ -5774,255 +5829,255 @@
         <v>429</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>172</v>
+        <v>430</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>148</v>
+        <v>432</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>148</v>
+        <v>434</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>434</v>
+        <v>154</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>148</v>
+        <v>440</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>440</v>
+        <v>154</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>172</v>
+        <v>446</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>445</v>
+        <v>178</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>191</v>
+        <v>455</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>245</v>
+        <v>154</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>463</v>
+        <v>251</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>465</v>
+        <v>157</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>467</v>
+        <v>178</v>
       </c>
     </row>
     <row r="335">
@@ -6046,55 +6101,55 @@
         <v>472</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>288</v>
+        <v>473</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>483</v>
+        <v>265</v>
       </c>
     </row>
     <row r="344">
@@ -6158,71 +6213,71 @@
         <v>498</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>259</v>
+        <v>499</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>259</v>
+        <v>501</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>259</v>
+        <v>482</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>505</v>
+        <v>265</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>507</v>
+        <v>265</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>509</v>
+        <v>265</v>
       </c>
     </row>
     <row r="360">
@@ -6246,55 +6301,55 @@
         <v>514</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>259</v>
+        <v>515</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>259</v>
+        <v>517</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>313</v>
+        <v>519</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>519</v>
+        <v>265</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>521</v>
+        <v>319</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>523</v>
+        <v>265</v>
       </c>
     </row>
     <row r="369">
@@ -6302,47 +6357,47 @@
         <v>524</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>259</v>
+        <v>525</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>259</v>
+        <v>529</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>529</v>
+        <v>265</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>533</v>
+        <v>265</v>
       </c>
     </row>
     <row r="375">
@@ -6366,7 +6421,31 @@
         <v>538</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>313</v>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0" t="s">
+        <v>544</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -6397,82 +6476,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>771</v>
-      </c>
       <c r="J1" s="8" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -6501,33 +6580,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6555,33 +6634,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -6611,45 +6690,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -6685,74 +6764,74 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -6788,69 +6867,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -6881,51 +6960,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -6959,67 +7038,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -7072,87 +7151,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>866</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>867</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>868</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>859</v>
-      </c>
       <c r="O1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -7197,117 +7276,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="N2" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>903</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>896</v>
-      </c>
       <c r="Q2" s="9" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -7360,364 +7439,364 @@
   <sheetData>
     <row r="1" spans="1:27" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="O2" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>589</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="Z2" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="P2" s="11" t="s">
-        <v>580</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>581</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>582</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>583</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>589</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>573</v>
-      </c>
       <c r="AA2" s="11" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="O3" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="P3" s="11" t="s">
-        <v>605</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>606</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>610</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>611</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>612</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>614</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>598</v>
-      </c>
       <c r="AA3" s="11" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -7726,44 +7805,44 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -7773,7 +7852,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7">
@@ -7781,29 +7860,29 @@
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -7816,7 +7895,7 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -7824,7 +7903,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -7835,16 +7914,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -7857,7 +7936,7 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9">
@@ -7865,7 +7944,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -7877,13 +7956,13 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -7902,7 +7981,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -7914,13 +7993,13 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -7939,7 +8018,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -7951,13 +8030,13 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -7976,7 +8055,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -7988,13 +8067,13 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -8023,10 +8102,10 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -8056,10 +8135,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -8090,7 +8169,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -8121,7 +8200,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -8152,7 +8231,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -8183,7 +8262,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -8214,7 +8293,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -8245,7 +8324,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -8280,36 +8359,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -8347,80 +8426,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -8453,39 +8532,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -8530,122 +8609,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -8681,27 +8760,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -8732,48 +8811,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -8811,33 +8890,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8865,30 +8944,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -8917,15 +8996,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -8951,21 +9030,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -9008,115 +9087,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -9144,33 +9223,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9201,51 +9280,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1000</v>
-      </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -9277,56 +9356,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
     </row>
   </sheetData>
@@ -9373,70 +9452,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>1029</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1034</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>1037</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>844</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9445,10 +9524,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -9490,55 +9569,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>1029</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>844</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -9565,30 +9644,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
   </sheetData>
@@ -9621,54 +9700,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -9696,24 +9775,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -9735,33 +9814,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9791,43 +9870,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -9858,48 +9937,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>750</v>
-      </c>
       <c r="F2" s="9" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9936,53 +10015,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>754</v>
-      </c>
       <c r="F1" s="8" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -10015,33 +10094,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -47,12 +47,14 @@
     <sheet name="LGU Rates" sheetId="40" r:id="rId40"/>
     <sheet name="Authority Limits" sheetId="41" r:id="rId41"/>
     <sheet name="Numbering" sheetId="42" r:id="rId42"/>
+    <sheet name="Payee Bank Accounts" sheetId="43" r:id="rId43"/>
+    <sheet name="COC Series" sheetId="44" r:id="rId44"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1280">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -357,6 +359,18 @@
     <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code</t>
   </si>
   <si>
+    <t xml:space="preserve">41. Payee Bank Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts (Payee bank accounts). Key: Payee Type + Payee + Account Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42. COC Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From</t>
+  </si>
+  <si>
     <t xml:space="preserve">Validate, fix and load</t>
   </si>
   <si>
@@ -474,6 +488,18 @@
     <t xml:space="preserve">Master &gt; Finance &gt; Payment Gateways</t>
   </si>
   <si>
+    <t xml:space="preserve">Integration connectors (endpoint, mode, credential variable names; the credentials themselves in the secret store), message templates, insurer API mappings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; Integrations / Message Templates / Insurer Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank file layouts (validate each starter layout with the bank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts</t>
+  </si>
+  <si>
     <t xml:space="preserve">Application name, logo, colours, display currency, language</t>
   </si>
   <si>
@@ -1923,6 +1949,96 @@
     <t xml:space="preserve">Numbering: Active</t>
   </si>
   <si>
+    <t xml:space="preserve">Payee Bank Accounts: Payee Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Insurer, Agent/Referrer, Customer or Supplier. Values: Lists sheet, Payee Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Payee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Insurer code, referrer id, client code or supplier code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Bank Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Code of the Bank master (BDO, BPI, MBT, LBP, UBP ...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Account Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Digits, spaces and -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Account Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Account Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. savings or current (savings when empty). Values: Lists sheet, Bank Account Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Bank Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. E-mail for the bank's credit advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Bank Accounts: Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Insurer code (or name). Values: Lists sheet, Insurers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Branch Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Branch the series is for; empty = every branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Prefix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Capital letters, digits and -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: From</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. First COC number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. Last COC number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Next Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Next number not yet used (the first number when empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Digits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Digits of the number, zero-padded (8 when empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COC Series: Remarks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes No</t>
   </si>
   <si>
@@ -2010,6 +2126,12 @@
     <t xml:space="preserve">Cancellation Reason Return Premium Method</t>
   </si>
   <si>
+    <t xml:space="preserve">Payee Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Account Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
@@ -2043,306 +2165,324 @@
     <t xml:space="preserve">yearly</t>
   </si>
   <si>
+    <t xml:space="preserve">compliance-officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quotation_discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highly Urbanized City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">savings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inactive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current Assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inactive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">renewal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium_tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prorate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fiscal_yearly</t>
+  </si>
+  <si>
     <t xml:space="preserve">system-admin</t>
   </si>
   <si>
-    <t xml:space="preserve">APEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quotation_discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highly Urbanized City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universal Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">broker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">auto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inactive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-current Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inactive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">renewal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">premium_tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per_unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prorate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fiscal_yearly</t>
+    <t xml:space="preserve">EVERSAFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BURGLARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy_issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitan area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non_package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pro-rata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent/Referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly</t>
   </si>
   <si>
     <t xml:space="preserve">sales</t>
   </si>
   <si>
-    <t xml:space="preserve">EVERSAFE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">policy_issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metropolitan area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Component City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non_package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pro-rata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monthly</t>
+    <t xml:space="preserve">FPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return_premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Geographic Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrift Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short-period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">never</t>
   </si>
   <si>
     <t xml:space="preserve">processing</t>
   </si>
   <si>
-    <t xml:space="preserve">FPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">return_premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Special Geographic Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thrift Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Deposit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short-period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">never</t>
+    <t xml:space="preserve">GOLDENHORIZON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claim_settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province / state outside the Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lgt</t>
   </si>
   <si>
     <t xml:space="preserve">operations</t>
   </si>
   <si>
-    <t xml:space="preserve">GOLDENHORIZON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claim_settlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province / state outside the Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trust Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lgt</t>
+    <t xml:space="preserve">INTEGRITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
   </si>
   <si>
     <t xml:space="preserve">claims</t>
   </si>
   <si>
-    <t xml:space="preserve">INTEGRITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
+    <t xml:space="preserve">LIBERTYSHIELD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">journal_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casualty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Income</t>
   </si>
   <si>
     <t xml:space="preserve">accounting</t>
   </si>
   <si>
-    <t xml:space="preserve">LIBERTYSHIELD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casualty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Income</t>
+    <t xml:space="preserve">MALAYAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">write_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Services</t>
   </si>
   <si>
     <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
-    <t xml:space="preserve">MALAYAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">write_off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">own-book</t>
-  </si>
-  <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
@@ -2394,6 +2534,9 @@
     <t xml:space="preserve">IAR</t>
   </si>
   <si>
+    <t xml:space="preserve">underwriting_referral</t>
+  </si>
+  <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
@@ -3579,9 +3722,6 @@
     <t xml:space="preserve">650</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Product</t>
   </si>
   <si>
@@ -3706,6 +3846,54 @@
   </si>
   <si>
     <t xml:space="preserve">1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee Type *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payee *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE Insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0071-2345-67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malayan Insurance Co., Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurer *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
   </si>
 </sst>
 </file>
@@ -3871,7 +4059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B437"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4289,26 +4477,26 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="B53" s="10"/>
+      <c r="B53" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55" s="4" t="s">
+      <c r="A55" s="10" t="s">
         <v>105</v>
       </c>
+      <c r="B55" s="10"/>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
@@ -4327,26 +4515,26 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="10"/>
+      <c r="B58" s="4" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="B60" s="4" t="s">
+      <c r="A60" s="10" t="s">
         <v>114</v>
       </c>
+      <c r="B60" s="10"/>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
@@ -4373,26 +4561,26 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="B64" s="10"/>
+      <c r="B64" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="B66" s="4" t="s">
+      <c r="A66" s="10" t="s">
         <v>125</v>
       </c>
+      <c r="B66" s="10"/>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
@@ -4523,185 +4711,185 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="B83" s="10"/>
+      <c r="B83" s="4" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>163</v>
-      </c>
+      <c r="A87" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" s="10"/>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106">
@@ -4717,631 +4905,631 @@
         <v>191</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>163</v>
+        <v>245</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>257</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>267</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>269</v>
+        <v>211</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>271</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>271</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186">
@@ -5349,231 +5537,231 @@
         <v>288</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>160</v>
+        <v>291</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>160</v>
+        <v>293</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>160</v>
+        <v>295</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>257</v>
+        <v>168</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>302</v>
+        <v>171</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>163</v>
+        <v>310</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>314</v>
+        <v>171</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>316</v>
+        <v>192</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
     </row>
     <row r="215">
@@ -5589,623 +5777,623 @@
         <v>330</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>160</v>
+        <v>331</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>160</v>
+        <v>333</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>160</v>
+        <v>335</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>160</v>
+        <v>342</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>237</v>
+        <v>168</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>345</v>
+        <v>168</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>160</v>
+        <v>245</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>160</v>
+        <v>353</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>353</v>
+        <v>168</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>163</v>
+        <v>361</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>302</v>
+        <v>171</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>366</v>
+        <v>171</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>368</v>
+        <v>171</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>160</v>
+        <v>372</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>160</v>
+        <v>374</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>160</v>
+        <v>376</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>380</v>
+        <v>192</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>163</v>
+        <v>388</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>390</v>
+        <v>171</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>397</v>
+        <v>192</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>160</v>
+        <v>403</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>160</v>
+        <v>405</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>415</v>
+        <v>168</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>417</v>
+        <v>245</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>419</v>
+        <v>168</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>421</v>
+        <v>171</v>
       </c>
     </row>
     <row r="294">
@@ -6213,511 +6401,511 @@
         <v>422</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>163</v>
+        <v>423</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>302</v>
+        <v>425</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>184</v>
+        <v>429</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>160</v>
+        <v>310</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>160</v>
+        <v>433</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>436</v>
+        <v>168</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>438</v>
+        <v>168</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>440</v>
+        <v>168</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>160</v>
+        <v>444</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>163</v>
+        <v>448</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>446</v>
+        <v>192</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>160</v>
+        <v>454</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>452</v>
+        <v>192</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>461</v>
+        <v>192</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>160</v>
+        <v>465</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>184</v>
+        <v>469</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>257</v>
+        <v>168</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>160</v>
+        <v>265</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>480</v>
+        <v>168</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>482</v>
+        <v>171</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>484</v>
+        <v>171</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>167</v>
+        <v>488</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>163</v>
+        <v>490</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>163</v>
+        <v>492</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>494</v>
+        <v>171</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>496</v>
+        <v>192</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>498</v>
+        <v>168</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>500</v>
+        <v>168</v>
       </c>
     </row>
     <row r="358">
@@ -6733,295 +6921,295 @@
         <v>503</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>163</v>
+        <v>504</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>184</v>
+        <v>506</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>160</v>
+        <v>508</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>509</v>
+        <v>171</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>160</v>
+        <v>515</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>160</v>
+        <v>517</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>515</v>
+        <v>171</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>517</v>
+        <v>192</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>160</v>
+        <v>523</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>524</v>
+        <v>171</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>527</v>
+        <v>168</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>203</v>
+        <v>530</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>163</v>
+        <v>532</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>160</v>
+        <v>535</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>540</v>
+        <v>171</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>542</v>
+        <v>171</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>544</v>
+        <v>175</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>553</v>
+        <v>192</v>
       </c>
     </row>
     <row r="396">
@@ -7037,63 +7225,63 @@
         <v>556</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>300</v>
+        <v>557</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>271</v>
+        <v>563</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>563</v>
+        <v>308</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>569</v>
+        <v>279</v>
       </c>
     </row>
     <row r="405">
@@ -7149,79 +7337,79 @@
         <v>582</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>271</v>
+        <v>583</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>271</v>
+        <v>585</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>271</v>
+        <v>589</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="0" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>591</v>
+        <v>279</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>593</v>
+        <v>279</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>595</v>
+        <v>279</v>
       </c>
     </row>
     <row r="421">
@@ -7237,111 +7425,111 @@
         <v>598</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>271</v>
+        <v>599</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>271</v>
+        <v>601</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>325</v>
+        <v>603</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>271</v>
+        <v>605</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>603</v>
+        <v>279</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>605</v>
+        <v>279</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>607</v>
+        <v>333</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>271</v>
+        <v>613</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="0" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>615</v>
+        <v>279</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>619</v>
+        <v>279</v>
       </c>
     </row>
     <row r="436">
@@ -7357,7 +7545,175 @@
         <v>622</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>325</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0" t="s">
+        <v>630</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0" t="s">
+        <v>631</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0" t="s">
+        <v>635</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="B446" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0" t="s">
+        <v>640</v>
+      </c>
+      <c r="B447" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="B448" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0" t="s">
+        <v>645</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="B451" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0" t="s">
+        <v>648</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0" t="s">
+        <v>654</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -7388,82 +7744,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>868</v>
+        <v>915</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>869</v>
+        <v>916</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>798</v>
+        <v>845</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>853</v>
+        <v>900</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>803</v>
+        <v>850</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>804</v>
+        <v>851</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>871</v>
+        <v>918</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>872</v>
+        <v>919</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>873</v>
+        <v>920</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>874</v>
+        <v>921</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>875</v>
+        <v>922</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>876</v>
+        <v>923</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>877</v>
+        <v>924</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>878</v>
+        <v>925</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>879</v>
+        <v>926</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>880</v>
+        <v>927</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -7492,33 +7848,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>881</v>
+        <v>928</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>882</v>
+        <v>929</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>884</v>
+        <v>931</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>885</v>
+        <v>932</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>886</v>
+        <v>933</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>887</v>
+        <v>934</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7546,33 +7902,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>888</v>
+        <v>935</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>889</v>
+        <v>936</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>890</v>
+        <v>937</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>891</v>
+        <v>938</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>892</v>
+        <v>939</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>893</v>
+        <v>940</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>894</v>
+        <v>941</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7602,45 +7958,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>895</v>
+        <v>942</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>896</v>
+        <v>943</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>881</v>
+        <v>928</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>847</v>
+        <v>894</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>897</v>
+        <v>944</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>898</v>
+        <v>945</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>899</v>
+        <v>946</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>900</v>
+        <v>947</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>901</v>
+        <v>948</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>902</v>
+        <v>949</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>903</v>
+        <v>950</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -7676,74 +8032,74 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>904</v>
+        <v>951</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>905</v>
+        <v>952</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>906</v>
+        <v>953</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>907</v>
+        <v>954</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>908</v>
+        <v>955</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>910</v>
+        <v>957</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>911</v>
+        <v>958</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>912</v>
+        <v>959</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>913</v>
+        <v>960</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>914</v>
+        <v>961</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>915</v>
+        <v>962</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>916</v>
+        <v>963</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>917</v>
+        <v>964</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>918</v>
+        <v>965</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>887</v>
+        <v>934</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>750</v>
+        <v>802</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>657</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -7779,69 +8135,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>919</v>
+        <v>966</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>920</v>
+        <v>967</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>921</v>
+        <v>968</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>922</v>
+        <v>969</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>923</v>
+        <v>970</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>924</v>
+        <v>971</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>925</v>
+        <v>972</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>926</v>
+        <v>973</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>927</v>
+        <v>974</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>928</v>
+        <v>975</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>929</v>
+        <v>976</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>930</v>
+        <v>977</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>931</v>
+        <v>978</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>932</v>
+        <v>979</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>932</v>
+        <v>979</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>933</v>
+        <v>980</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>903</v>
+        <v>950</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -7872,51 +8228,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>935</v>
+        <v>982</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>936</v>
+        <v>983</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>919</v>
+        <v>966</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>937</v>
+        <v>984</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>938</v>
+        <v>985</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>939</v>
+        <v>986</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>940</v>
+        <v>987</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>941</v>
+        <v>988</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>942</v>
+        <v>989</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>944</v>
+        <v>991</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>945</v>
+        <v>992</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>946</v>
+        <v>993</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>947</v>
+        <v>994</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -7950,67 +8306,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>949</v>
+        <v>996</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>625</v>
+        <v>663</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>950</v>
+        <v>997</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>626</v>
+        <v>664</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>951</v>
+        <v>998</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>627</v>
+        <v>665</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>952</v>
+        <v>999</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>953</v>
+        <v>1000</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>954</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>955</v>
+        <v>1002</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>739</v>
+        <v>785</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>656</v>
+        <v>696</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>657</v>
+        <v>697</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8063,87 +8419,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>956</v>
+        <v>1003</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>957</v>
+        <v>1004</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>958</v>
+        <v>1005</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>959</v>
+        <v>1006</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>798</v>
+        <v>845</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>853</v>
+        <v>900</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>960</v>
+        <v>1007</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>804</v>
+        <v>851</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>951</v>
+        <v>998</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>961</v>
+        <v>1008</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>962</v>
+        <v>1009</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>963</v>
+        <v>1010</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>964</v>
+        <v>1011</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>965</v>
+        <v>1012</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>966</v>
+        <v>1013</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>967</v>
+        <v>1014</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>968</v>
+        <v>1015</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>696</v>
+        <v>738</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -8188,117 +8544,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>948</v>
+        <v>995</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>949</v>
+        <v>996</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>956</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>969</v>
+        <v>1016</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>970</v>
+        <v>1017</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>971</v>
+        <v>1018</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>972</v>
+        <v>1019</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>973</v>
+        <v>1020</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>974</v>
+        <v>1021</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>975</v>
+        <v>1022</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>976</v>
+        <v>1023</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>978</v>
+        <v>1025</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>980</v>
+        <v>1027</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>981</v>
+        <v>1028</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>982</v>
+        <v>1029</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>983</v>
+        <v>1030</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>984</v>
+        <v>1031</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>985</v>
+        <v>1032</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>986</v>
+        <v>1033</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>987</v>
+        <v>1034</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>670</v>
+        <v>710</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>944</v>
+        <v>991</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>988</v>
+        <v>1035</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>989</v>
+        <v>1036</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>990</v>
+        <v>1037</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>991</v>
+        <v>1038</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>992</v>
+        <v>1039</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>993</v>
+        <v>1040</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>994</v>
+        <v>1041</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>995</v>
+        <v>1042</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>988</v>
+        <v>1035</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>996</v>
+        <v>1043</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>992</v>
+        <v>1039</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -8317,7 +8673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
@@ -8349,390 +8705,414 @@
     <col min="27" max="27" width="47" style="11" customWidth="1"/>
     <col min="28" max="28" width="36" style="11" customWidth="1"/>
     <col min="29" max="29" width="45" style="11" customWidth="1"/>
+    <col min="30" max="30" width="14" style="11" customWidth="1"/>
+    <col min="31" max="31" width="21" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="20" customHeight="1">
+    <row r="1" spans="1:31" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>623</v>
+        <v>661</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>625</v>
+        <v>663</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>626</v>
+        <v>664</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>627</v>
+        <v>665</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>628</v>
+        <v>666</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>629</v>
+        <v>667</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>630</v>
+        <v>668</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>631</v>
+        <v>669</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>632</v>
+        <v>670</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>633</v>
+        <v>671</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>634</v>
+        <v>672</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>635</v>
+        <v>673</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>636</v>
+        <v>674</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>637</v>
+        <v>675</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>638</v>
+        <v>676</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>639</v>
+        <v>677</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>640</v>
+        <v>678</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>641</v>
+        <v>679</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>642</v>
+        <v>680</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>643</v>
+        <v>681</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>644</v>
+        <v>682</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>645</v>
+        <v>683</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>646</v>
+        <v>684</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>647</v>
+        <v>685</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>648</v>
+        <v>686</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>649</v>
+        <v>687</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>650</v>
+        <v>688</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>651</v>
+        <v>689</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="AE1" s="8" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>654</v>
+        <v>694</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>655</v>
+        <v>695</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>656</v>
+        <v>696</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>657</v>
+        <v>697</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>657</v>
+        <v>697</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>659</v>
+        <v>699</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>662</v>
+        <v>702</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>663</v>
+        <v>703</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>664</v>
+        <v>704</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>665</v>
+        <v>705</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>666</v>
+        <v>706</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>667</v>
+        <v>707</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>668</v>
+        <v>708</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>669</v>
+        <v>709</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>670</v>
+        <v>710</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>671</v>
+        <v>711</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>672</v>
+        <v>712</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>673</v>
+        <v>713</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>674</v>
+        <v>714</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>675</v>
+        <v>715</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>659</v>
+        <v>699</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>676</v>
+        <v>716</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>677</v>
+        <v>717</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>678</v>
+        <v>718</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>680</v>
+        <v>722</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>681</v>
+        <v>723</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>682</v>
+        <v>724</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>683</v>
+        <v>725</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>684</v>
+        <v>726</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>684</v>
+        <v>726</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>685</v>
+        <v>727</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>686</v>
+        <v>728</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>687</v>
+        <v>729</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>688</v>
+        <v>730</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>689</v>
+        <v>731</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>690</v>
+        <v>732</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>691</v>
+        <v>733</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>692</v>
+        <v>734</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>693</v>
+        <v>735</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>694</v>
+        <v>736</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>695</v>
+        <v>737</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>696</v>
+        <v>738</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>697</v>
+        <v>739</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>698</v>
+        <v>740</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>699</v>
+        <v>741</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>700</v>
+        <v>742</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>701</v>
+        <v>743</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>702</v>
+        <v>744</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>686</v>
+        <v>728</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>703</v>
+        <v>745</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>704</v>
+        <v>746</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>705</v>
+        <v>747</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>748</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>749</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>706</v>
+        <v>750</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>707</v>
+        <v>751</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>708</v>
+        <v>752</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>709</v>
+        <v>753</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>710</v>
+        <v>754</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>711</v>
+        <v>755</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>712</v>
+        <v>756</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>713</v>
+        <v>757</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>714</v>
+        <v>758</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>715</v>
+        <v>759</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>716</v>
+        <v>760</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>717</v>
+        <v>761</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>720</v>
+        <v>764</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>721</v>
+        <v>765</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>722</v>
+        <v>766</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>723</v>
+        <v>767</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>724</v>
+        <v>768</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11" t="s">
-        <v>725</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="AE4" s="11"/>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>726</v>
+        <v>771</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>727</v>
+        <v>772</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>728</v>
+        <v>773</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>729</v>
+        <v>774</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>730</v>
+        <v>775</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>731</v>
+        <v>776</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>732</v>
+        <v>777</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>733</v>
+        <v>778</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>734</v>
+        <v>779</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>735</v>
+        <v>780</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>736</v>
+        <v>781</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>737</v>
+        <v>782</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -8741,48 +9121,52 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>738</v>
+        <v>783</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>710</v>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>784</v>
+      </c>
+      <c r="AE5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>739</v>
+        <v>785</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>740</v>
+        <v>786</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>741</v>
+        <v>787</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>742</v>
+        <v>788</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>743</v>
+        <v>789</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -8792,39 +9176,41 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>747</v>
+        <v>793</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>748</v>
+        <v>794</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>752</v>
+        <v>798</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>753</v>
+        <v>799</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -8837,17 +9223,19 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>754</v>
+        <v>800</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
+      <c r="AD7" s="11"/>
+      <c r="AE7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -8858,16 +9246,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>756</v>
+        <v>802</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>757</v>
+        <v>803</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>759</v>
+        <v>805</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -8880,17 +9268,19 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
+      <c r="AD8" s="11"/>
+      <c r="AE8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>761</v>
+        <v>807</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -8901,16 +9291,16 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="s">
-        <v>762</v>
+        <v>808</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>763</v>
+        <v>809</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>764</v>
+        <v>810</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>765</v>
+        <v>811</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -8925,13 +9315,15 @@
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -8943,13 +9335,13 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11" t="s">
-        <v>767</v>
+        <v>813</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>768</v>
+        <v>814</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>769</v>
+        <v>815</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -8964,13 +9356,15 @@
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
       <c r="AC10" s="11"/>
+      <c r="AD10" s="11"/>
+      <c r="AE10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>770</v>
+        <v>816</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -8982,13 +9376,13 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>771</v>
+        <v>817</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>773</v>
+        <v>819</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -9003,13 +9397,15 @@
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
       <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>774</v>
+        <v>820</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -9021,13 +9417,13 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>775</v>
+        <v>821</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>776</v>
+        <v>822</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>777</v>
+        <v>823</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -9042,6 +9438,8 @@
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
       <c r="AC12" s="11"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -9058,12 +9456,14 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>779</v>
-      </c>
-      <c r="P13" s="11"/>
+        <v>825</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>826</v>
+      </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
@@ -9077,6 +9477,8 @@
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
       <c r="AC13" s="11"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -9093,10 +9495,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
-        <v>780</v>
+        <v>827</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -9112,6 +9514,8 @@
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
       <c r="AC14" s="11"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -9129,7 +9533,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -9145,6 +9549,8 @@
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
       <c r="AC15" s="11"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -9162,7 +9568,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>783</v>
+        <v>830</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -9178,6 +9584,8 @@
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
+      <c r="AD16" s="11"/>
+      <c r="AE16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -9195,7 +9603,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>784</v>
+        <v>831</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -9211,6 +9619,8 @@
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
       <c r="AC17" s="11"/>
+      <c r="AD17" s="11"/>
+      <c r="AE17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -9228,7 +9638,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -9244,6 +9654,8 @@
       <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
       <c r="AC18" s="11"/>
+      <c r="AD18" s="11"/>
+      <c r="AE18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -9261,7 +9673,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -9277,6 +9689,8 @@
       <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
       <c r="AC19" s="11"/>
+      <c r="AD19" s="11"/>
+      <c r="AE19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -9294,7 +9708,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -9310,6 +9724,8 @@
       <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
       <c r="AC20" s="11"/>
+      <c r="AD20" s="11"/>
+      <c r="AE20" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9331,36 +9747,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>997</v>
+        <v>1044</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>998</v>
+        <v>1045</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>999</v>
+        <v>1046</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1000</v>
+        <v>1047</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1001</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1002</v>
+        <v>1049</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1003</v>
+        <v>1050</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1004</v>
+        <v>1051</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -9398,80 +9814,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1005</v>
+        <v>1052</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1006</v>
+        <v>1053</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>827</v>
+        <v>874</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1007</v>
+        <v>1054</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1008</v>
+        <v>1055</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1009</v>
+        <v>1056</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1010</v>
+        <v>1057</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1011</v>
+        <v>1058</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>883</v>
+        <v>930</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1012</v>
+        <v>1059</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1013</v>
+        <v>1060</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1014</v>
+        <v>1061</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1015</v>
+        <v>1062</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1016</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1017</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1018</v>
+        <v>1065</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>698</v>
+        <v>740</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1019</v>
+        <v>1066</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1020</v>
+        <v>1067</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>887</v>
+        <v>934</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1021</v>
+        <v>1068</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1022</v>
+        <v>1069</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1023</v>
+        <v>1070</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -9504,39 +9920,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1024</v>
+        <v>1071</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1025</v>
+        <v>1072</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1026</v>
+        <v>1073</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1027</v>
+        <v>1074</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1028</v>
+        <v>1075</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1029</v>
+        <v>1076</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1030</v>
+        <v>1077</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1031</v>
+        <v>1078</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1032</v>
+        <v>1079</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -9581,122 +9997,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1033</v>
+        <v>1080</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1034</v>
+        <v>1081</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1035</v>
+        <v>1082</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>798</v>
+        <v>845</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>853</v>
+        <v>900</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>870</v>
+        <v>917</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1036</v>
+        <v>1083</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1037</v>
+        <v>1084</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1038</v>
+        <v>1085</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1039</v>
+        <v>1086</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1040</v>
+        <v>1087</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>1041</v>
+        <v>1088</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>1042</v>
+        <v>1089</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>1043</v>
+        <v>1090</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1044</v>
+        <v>1091</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1045</v>
+        <v>1092</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1046</v>
+        <v>1093</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1047</v>
+        <v>1094</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1048</v>
+        <v>1095</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1049</v>
+        <v>1096</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>816</v>
+        <v>863</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1050</v>
+        <v>1097</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1051</v>
+        <v>1098</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1052</v>
+        <v>1099</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1053</v>
+        <v>1100</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1054</v>
+        <v>1101</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1055</v>
+        <v>1102</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>672</v>
+        <v>712</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -9732,27 +10148,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1056</v>
+        <v>1103</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1057</v>
+        <v>1104</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1058</v>
+        <v>1105</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1059</v>
+        <v>1106</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1060</v>
+        <v>1107</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1061</v>
+        <v>1108</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -9783,48 +10199,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1062</v>
+        <v>1109</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1063</v>
+        <v>1110</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1064</v>
+        <v>1111</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1065</v>
+        <v>1112</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1066</v>
+        <v>1113</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1067</v>
+        <v>1114</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1068</v>
+        <v>1115</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1069</v>
+        <v>1116</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1070</v>
+        <v>1117</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1071</v>
+        <v>1118</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1072</v>
+        <v>1119</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>674</v>
+        <v>714</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>675</v>
+        <v>715</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -9862,33 +10278,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1073</v>
+        <v>1120</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1074</v>
+        <v>1121</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1076</v>
+        <v>1123</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1077</v>
+        <v>1124</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1078</v>
+        <v>1125</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -9916,30 +10332,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1079</v>
+        <v>1126</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1080</v>
+        <v>1127</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1081</v>
+        <v>1128</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1082</v>
+        <v>1129</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1083</v>
+        <v>1130</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1084</v>
+        <v>1131</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1085</v>
+        <v>1132</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -9968,15 +10384,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1086</v>
+        <v>1133</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1087</v>
+        <v>1134</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -10002,21 +10418,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1086</v>
+        <v>1133</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1088</v>
+        <v>1135</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1089</v>
+        <v>1136</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1090</v>
+        <v>1137</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -10059,115 +10475,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>793</v>
+        <v>840</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>794</v>
+        <v>841</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>797</v>
+        <v>844</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>798</v>
+        <v>845</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>800</v>
+        <v>847</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>667</v>
+        <v>707</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>803</v>
+        <v>850</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>804</v>
+        <v>851</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>805</v>
+        <v>852</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>806</v>
+        <v>853</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>807</v>
+        <v>854</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>808</v>
+        <v>855</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>809</v>
+        <v>856</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>811</v>
+        <v>858</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>812</v>
+        <v>859</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>813</v>
+        <v>860</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>814</v>
+        <v>861</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>815</v>
+        <v>862</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>816</v>
+        <v>863</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>818</v>
+        <v>865</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>819</v>
+        <v>866</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>679</v>
+        <v>721</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -10195,33 +10611,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1088</v>
+        <v>1135</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1091</v>
+        <v>1138</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1092</v>
+        <v>1139</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1093</v>
+        <v>1140</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1094</v>
+        <v>1141</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1095</v>
+        <v>1142</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1096</v>
+        <v>1143</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1097</v>
+        <v>1144</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10252,51 +10668,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1098</v>
+        <v>1145</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1099</v>
+        <v>1146</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1100</v>
+        <v>1147</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1102</v>
+        <v>1149</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1092</v>
+        <v>1139</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1104</v>
+        <v>1151</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1105</v>
+        <v>1152</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1106</v>
+        <v>1153</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1090</v>
+        <v>1137</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1107</v>
+        <v>1154</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1108</v>
+        <v>1155</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1109</v>
+        <v>1156</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -10333,87 +10749,87 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1111</v>
+        <v>1158</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1112</v>
+        <v>1159</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1113</v>
+        <v>1160</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1114</v>
+        <v>1161</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1115</v>
+        <v>1162</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1116</v>
+        <v>1163</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1117</v>
+        <v>1164</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1118</v>
+        <v>1165</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1119</v>
+        <v>1166</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1120</v>
+        <v>1167</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1121</v>
+        <v>1168</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1122</v>
+        <v>1169</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1123</v>
+        <v>1170</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1055</v>
+        <v>1102</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1124</v>
+        <v>1171</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1125</v>
+        <v>1172</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1126</v>
+        <v>1173</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1127</v>
+        <v>1174</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>986</v>
+        <v>1033</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1128</v>
+        <v>1175</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -10445,54 +10861,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1129</v>
+        <v>1176</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1130</v>
+        <v>1177</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1131</v>
+        <v>1178</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1132</v>
+        <v>1179</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1133</v>
+        <v>1180</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1134</v>
+        <v>1181</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1135</v>
+        <v>1182</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1136</v>
+        <v>1183</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1138</v>
+        <v>1185</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1139</v>
+        <v>1186</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1140</v>
+        <v>1187</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1141</v>
+        <v>1188</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -10521,33 +10937,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1142</v>
+        <v>1189</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1143</v>
+        <v>1190</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1144</v>
+        <v>1191</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1145</v>
+        <v>1192</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1146</v>
+        <v>1193</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1147</v>
+        <v>1194</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10576,39 +10992,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1025</v>
+        <v>1072</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1148</v>
+        <v>1195</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1149</v>
+        <v>1196</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1150</v>
+        <v>1197</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1151</v>
+        <v>1198</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>704</v>
+        <v>746</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>705</v>
+        <v>747</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1152</v>
+        <v>1199</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -10645,48 +11061,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1153</v>
+        <v>1200</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1154</v>
+        <v>1201</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1155</v>
+        <v>1202</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1156</v>
+        <v>1203</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1157</v>
+        <v>1204</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1158</v>
+        <v>1205</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1159</v>
+        <v>1206</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10722,75 +11138,75 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1160</v>
+        <v>1207</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1161</v>
+        <v>1208</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>909</v>
+        <v>956</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>979</v>
+        <v>1026</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1162</v>
+        <v>1209</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1163</v>
+        <v>1210</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1164</v>
+        <v>1211</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1165</v>
+        <v>1212</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1166</v>
+        <v>1213</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1167</v>
+        <v>1214</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1168</v>
+        <v>1215</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1169</v>
+        <v>1216</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1170</v>
+        <v>1217</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1171</v>
+        <v>1218</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1172</v>
+        <v>1219</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1173</v>
+        <v>1220</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1174</v>
+        <v>1221</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -10822,56 +11238,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1175</v>
+        <v>719</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1176</v>
+        <v>1222</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1177</v>
+        <v>1223</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1178</v>
+        <v>1224</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1179</v>
+        <v>1225</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>935</v>
+        <v>982</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>936</v>
+        <v>983</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1180</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1181</v>
+        <v>1227</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1182</v>
+        <v>1228</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1183</v>
+        <v>1229</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1184</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
@@ -10918,70 +11334,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1185</v>
+        <v>1231</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1186</v>
+        <v>1232</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1187</v>
+        <v>1233</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1188</v>
+        <v>1234</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1189</v>
+        <v>1235</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1190</v>
+        <v>1236</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>633</v>
+        <v>671</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1191</v>
+        <v>1237</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1192</v>
+        <v>1238</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1193</v>
+        <v>1239</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1194</v>
+        <v>1240</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>936</v>
+        <v>983</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1180</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1195</v>
+        <v>1241</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1196</v>
+        <v>1242</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>710</v>
+        <v>754</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1197</v>
+        <v>1243</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10990,10 +11406,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1183</v>
+        <v>1229</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -11029,24 +11445,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>820</v>
+        <v>867</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>821</v>
+        <v>868</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>822</v>
+        <v>869</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>823</v>
+        <v>870</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>824</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -11072,55 +11488,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1185</v>
+        <v>1231</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>667</v>
+        <v>707</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1179</v>
+        <v>1225</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1194</v>
+        <v>1240</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>936</v>
+        <v>983</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1180</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1198</v>
+        <v>1244</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1199</v>
+        <v>1245</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>817</v>
+        <v>864</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1199</v>
+        <v>1245</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1200</v>
+        <v>1246</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1183</v>
+        <v>1229</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -11147,36 +11563,36 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1201</v>
+        <v>1247</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1202</v>
+        <v>1248</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1203</v>
+        <v>1249</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1180</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1204</v>
+        <v>1250</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>750</v>
+        <v>802</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1205</v>
+        <v>1251</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1206</v>
+        <v>1252</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="A2:A5000">
-      <formula1>Lists!$P$2:$P$12</formula1>
+      <formula1>Lists!$P$2:$P$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
       <formula1>Lists!$M$2:$M$9</formula1>
@@ -11203,54 +11619,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1207</v>
+        <v>1253</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1208</v>
+        <v>1254</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1209</v>
+        <v>1255</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1210</v>
+        <v>1256</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1211</v>
+        <v>1257</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>634</v>
+        <v>672</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1212</v>
+        <v>1258</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1213</v>
+        <v>1259</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1214</v>
+        <v>1260</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1215</v>
+        <v>1261</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1216</v>
+        <v>1262</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1097</v>
+        <v>1144</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>662</v>
+        <v>702</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1217</v>
+        <v>1263</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -11260,6 +11676,165 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="H2:H5000">
       <formula1>Lists!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="15" style="11" customWidth="1"/>
+    <col min="4" max="4" width="20" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18" style="11" customWidth="1"/>
+    <col min="7" max="7" width="17" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="A2:A5000">
+      <formula1>Lists!$AD$2:$AD$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
+      <formula1>Lists!$AE$2:$AE$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="I2:I5000">
+      <formula1>Lists!$A$2:$A$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14" style="11" customWidth="1"/>
+    <col min="5" max="5" width="14" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
+    <col min="8" max="8" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
+      <formula1>Lists!$N$2:$N$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11280,33 +11855,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>825</v>
+        <v>872</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>826</v>
+        <v>873</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>827</v>
+        <v>874</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>830</v>
+        <v>877</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>831</v>
+        <v>878</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>832</v>
+        <v>879</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11336,43 +11911,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>833</v>
+        <v>880</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>834</v>
+        <v>881</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>836</v>
+        <v>883</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>839</v>
+        <v>886</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>841</v>
+        <v>888</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>843</v>
+        <v>890</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -11403,48 +11978,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>844</v>
+        <v>891</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>845</v>
+        <v>892</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>846</v>
+        <v>893</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>847</v>
+        <v>894</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>836</v>
+        <v>883</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>848</v>
+        <v>895</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>849</v>
+        <v>896</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>850</v>
+        <v>897</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>840</v>
+        <v>887</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>734</v>
+        <v>779</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11481,53 +12056,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>851</v>
+        <v>898</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>852</v>
+        <v>899</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>796</v>
+        <v>843</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>853</v>
+        <v>900</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>846</v>
+        <v>893</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>854</v>
+        <v>901</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>800</v>
+        <v>847</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>855</v>
+        <v>902</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>836</v>
+        <v>883</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>856</v>
+        <v>903</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>857</v>
+        <v>904</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>858</v>
+        <v>905</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>859</v>
+        <v>906</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>860</v>
+        <v>907</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -11560,33 +12135,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>861</v>
+        <v>908</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>862</v>
+        <v>909</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>800</v>
+        <v>847</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>624</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>864</v>
+        <v>911</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>865</v>
+        <v>912</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>867</v>
+        <v>914</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="1282">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -516,6 +516,12 @@
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Configuration &gt; Schedules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales activity types and outcomes (starter lists are installed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Organization &gt; Sales Activity Types / Sales Activity Outcomes</t>
   </si>
   <si>
     <t xml:space="preserve">Fiscal years and accounting periods (close the periods before the cutover date)</t>
@@ -4059,7 +4065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B459"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4743,33 +4749,33 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="10"/>
+      <c r="B87" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="B88" s="4" t="s">
+      <c r="A88" s="10" t="s">
         <v>168</v>
       </c>
+      <c r="B88" s="10"/>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
         <v>169</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="91">
@@ -4777,23 +4783,23 @@
         <v>172</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94">
@@ -4809,95 +4815,95 @@
         <v>178</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107">
@@ -4937,79 +4943,79 @@
         <v>199</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121">
@@ -5025,39 +5031,39 @@
         <v>212</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127">
@@ -5065,15 +5071,15 @@
         <v>218</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129">
@@ -5081,47 +5087,47 @@
         <v>221</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
     </row>
     <row r="135">
@@ -5129,15 +5135,15 @@
         <v>228</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="137">
@@ -5145,55 +5151,55 @@
         <v>231</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144">
@@ -5201,47 +5207,47 @@
         <v>239</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>245</v>
+        <v>170</v>
       </c>
     </row>
     <row r="150">
@@ -5249,151 +5255,151 @@
         <v>246</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
     </row>
     <row r="169">
@@ -5401,71 +5407,71 @@
         <v>266</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>192</v>
+        <v>267</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>275</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178">
@@ -5489,15 +5495,15 @@
         <v>280</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="B181" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="182">
@@ -5505,23 +5511,23 @@
         <v>283</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="185">
@@ -5529,15 +5535,15 @@
         <v>287</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="187">
@@ -5569,84 +5575,84 @@
         <v>296</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>168</v>
+        <v>297</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>265</v>
+        <v>170</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>192</v>
@@ -5654,10 +5660,10 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>308</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202">
@@ -5673,23 +5679,23 @@
         <v>311</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>314</v>
+        <v>170</v>
       </c>
     </row>
     <row r="206">
@@ -5697,31 +5703,31 @@
         <v>315</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>319</v>
+        <v>194</v>
       </c>
     </row>
     <row r="210">
@@ -5729,15 +5735,15 @@
         <v>320</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>168</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>322</v>
+        <v>170</v>
       </c>
     </row>
     <row r="212">
@@ -5761,15 +5767,15 @@
         <v>327</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>171</v>
+        <v>328</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>329</v>
+        <v>173</v>
       </c>
     </row>
     <row r="216">
@@ -5809,31 +5815,31 @@
         <v>338</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>168</v>
+        <v>339</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>342</v>
+        <v>170</v>
       </c>
     </row>
     <row r="224">
@@ -5841,79 +5847,79 @@
         <v>343</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>171</v>
+        <v>344</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>353</v>
+        <v>247</v>
       </c>
     </row>
     <row r="234">
@@ -5921,55 +5927,55 @@
         <v>354</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>361</v>
+        <v>170</v>
       </c>
     </row>
     <row r="241">
@@ -5977,79 +5983,79 @@
         <v>362</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>168</v>
+        <v>363</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>310</v>
+        <v>173</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>372</v>
+        <v>177</v>
       </c>
     </row>
     <row r="251">
@@ -6073,87 +6079,87 @@
         <v>377</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>192</v>
+        <v>378</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>388</v>
+        <v>170</v>
       </c>
     </row>
     <row r="264">
@@ -6161,71 +6167,71 @@
         <v>389</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>168</v>
+        <v>390</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>398</v>
+        <v>173</v>
       </c>
     </row>
     <row r="273">
@@ -6233,31 +6239,31 @@
         <v>399</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>192</v>
+        <v>400</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>403</v>
+        <v>170</v>
       </c>
     </row>
     <row r="277">
@@ -6273,135 +6279,135 @@
         <v>406</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>171</v>
+        <v>407</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>245</v>
+        <v>170</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>423</v>
+        <v>173</v>
       </c>
     </row>
     <row r="295">
@@ -6433,23 +6439,23 @@
         <v>430</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>171</v>
+        <v>431</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>310</v>
+        <v>173</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>433</v>
+        <v>312</v>
       </c>
     </row>
     <row r="301">
@@ -6457,79 +6463,79 @@
         <v>434</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>192</v>
+        <v>435</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>444</v>
+        <v>170</v>
       </c>
     </row>
     <row r="311">
@@ -6553,39 +6559,39 @@
         <v>449</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>192</v>
+        <v>450</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>454</v>
+        <v>173</v>
       </c>
     </row>
     <row r="318">
@@ -6593,39 +6599,39 @@
         <v>455</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>192</v>
+        <v>456</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>460</v>
+        <v>170</v>
       </c>
     </row>
     <row r="323">
@@ -6633,31 +6639,31 @@
         <v>461</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>192</v>
+        <v>462</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>465</v>
+        <v>194</v>
       </c>
     </row>
     <row r="327">
@@ -6665,23 +6671,23 @@
         <v>466</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>168</v>
+        <v>467</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>469</v>
+        <v>194</v>
       </c>
     </row>
     <row r="330">
@@ -6689,143 +6695,143 @@
         <v>470</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>168</v>
+        <v>471</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>265</v>
+        <v>170</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>171</v>
+        <v>267</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>488</v>
+        <v>192</v>
       </c>
     </row>
     <row r="348">
@@ -6849,71 +6855,71 @@
         <v>493</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>171</v>
+        <v>494</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>502</v>
+        <v>170</v>
       </c>
     </row>
     <row r="359">
@@ -6953,31 +6959,31 @@
         <v>511</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>171</v>
+        <v>512</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>515</v>
+        <v>170</v>
       </c>
     </row>
     <row r="367">
@@ -6993,39 +6999,39 @@
         <v>518</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>171</v>
+        <v>519</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>523</v>
+        <v>170</v>
       </c>
     </row>
     <row r="373">
@@ -7041,31 +7047,31 @@
         <v>526</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>171</v>
+        <v>527</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>530</v>
+        <v>170</v>
       </c>
     </row>
     <row r="378">
@@ -7081,15 +7087,15 @@
         <v>533</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>168</v>
+        <v>534</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>535</v>
+        <v>170</v>
       </c>
     </row>
     <row r="381">
@@ -7097,95 +7103,95 @@
         <v>536</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>211</v>
+        <v>537</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>548</v>
+        <v>173</v>
       </c>
     </row>
     <row r="393">
@@ -7209,15 +7215,15 @@
         <v>553</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>192</v>
+        <v>554</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>555</v>
+        <v>194</v>
       </c>
     </row>
     <row r="397">
@@ -7257,15 +7263,15 @@
         <v>564</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>308</v>
+        <v>565</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>566</v>
+        <v>310</v>
       </c>
     </row>
     <row r="403">
@@ -7281,15 +7287,15 @@
         <v>569</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>279</v>
+        <v>570</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>571</v>
+        <v>281</v>
       </c>
     </row>
     <row r="406">
@@ -7369,55 +7375,55 @@
         <v>590</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>279</v>
+        <v>591</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>279</v>
+        <v>570</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>597</v>
+        <v>281</v>
       </c>
     </row>
     <row r="422">
@@ -7457,39 +7463,39 @@
         <v>606</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>279</v>
+        <v>607</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>333</v>
+        <v>281</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>611</v>
+        <v>281</v>
       </c>
     </row>
     <row r="431">
@@ -7513,15 +7519,15 @@
         <v>616</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>279</v>
+        <v>617</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>618</v>
+        <v>281</v>
       </c>
     </row>
     <row r="435">
@@ -7529,15 +7535,15 @@
         <v>619</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>279</v>
+        <v>620</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>621</v>
+        <v>281</v>
       </c>
     </row>
     <row r="437">
@@ -7577,15 +7583,15 @@
         <v>630</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>333</v>
+        <v>631</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>632</v>
+        <v>335</v>
       </c>
     </row>
     <row r="443">
@@ -7617,15 +7623,15 @@
         <v>639</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>573</v>
+        <v>640</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>641</v>
+        <v>575</v>
       </c>
     </row>
     <row r="448">
@@ -7633,15 +7639,15 @@
         <v>642</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>279</v>
+        <v>643</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>644</v>
+        <v>281</v>
       </c>
     </row>
     <row r="450">
@@ -7649,15 +7655,15 @@
         <v>645</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>568</v>
+        <v>646</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>647</v>
+        <v>570</v>
       </c>
     </row>
     <row r="452">
@@ -7713,7 +7719,15 @@
         <v>660</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>279</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -7744,82 +7758,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -7848,33 +7862,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7902,33 +7916,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7958,45 +7972,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -8032,74 +8046,74 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -8135,69 +8149,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8228,51 +8242,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -8306,67 +8320,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>998</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>999</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1000</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>662</v>
-      </c>
       <c r="K1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8419,87 +8433,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -8544,117 +8558,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="J2" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>1044</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>1037</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>1038</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>1040</v>
-      </c>
-      <c r="N2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>1041</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>1042</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>1035</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>1043</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>1039</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -8711,361 +8725,361 @@
   <sheetData>
     <row r="1" spans="1:31" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="K2" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>709</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="Z2" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>703</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>704</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>705</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>706</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>708</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>709</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>710</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>711</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>712</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>713</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>714</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>715</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>699</v>
-      </c>
       <c r="AA2" s="11" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="K3" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>734</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>731</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>732</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>733</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>735</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>736</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>737</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>738</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>739</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>740</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>741</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>742</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>743</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>744</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>728</v>
-      </c>
       <c r="AA3" s="11" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AE4" s="11"/>
     </row>
@@ -9073,46 +9087,46 @@
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -9121,14 +9135,14 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AE5" s="11"/>
     </row>
@@ -9136,37 +9150,37 @@
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -9176,7 +9190,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
@@ -9188,29 +9202,29 @@
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -9223,7 +9237,7 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
@@ -9235,7 +9249,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -9246,16 +9260,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -9268,7 +9282,7 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
@@ -9280,7 +9294,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -9291,16 +9305,16 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -9323,7 +9337,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -9335,13 +9349,13 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -9364,7 +9378,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -9376,13 +9390,13 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -9405,7 +9419,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -9417,13 +9431,13 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -9456,13 +9470,13 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -9495,10 +9509,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -9533,7 +9547,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -9568,7 +9582,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -9603,7 +9617,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -9638,7 +9652,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -9673,7 +9687,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -9708,7 +9722,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -9747,36 +9761,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -9814,80 +9828,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -9920,39 +9934,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -9997,122 +10011,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -10148,27 +10162,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -10199,48 +10213,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10278,33 +10292,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10332,30 +10346,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -10384,15 +10398,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -10418,21 +10432,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -10475,115 +10489,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -10611,33 +10625,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10668,51 +10682,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -10749,87 +10763,87 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -10861,54 +10875,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -10937,33 +10951,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10992,39 +11006,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -11061,48 +11075,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11138,75 +11152,75 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -11238,56 +11252,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
   </sheetData>
@@ -11334,70 +11348,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11406,10 +11420,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -11445,24 +11459,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -11488,55 +11502,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -11563,30 +11577,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
   </sheetData>
@@ -11619,54 +11633,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -11700,56 +11714,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -11785,49 +11799,49 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -11855,33 +11869,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11911,43 +11925,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -11978,48 +11992,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12056,53 +12070,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -12135,33 +12149,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -3909,7 +3909,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3947,6 +3947,26 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4028,9 +4048,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4056,6 +4076,8 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1281">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">Accounts &gt; Period End &gt; Period Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Remittance masters, reinsurance treaties and reinsurers, incentive programs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Remittance Master; Reinsurance; Incentive</t>
+    <t xml:space="preserve">Remittance masters, incentive programs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Finance &gt; Remittance Master; Incentive</t>
   </si>
   <si>
     <t xml:space="preserve">Referrers / agents and their commission accounts</t>
@@ -542,24 +542,6 @@
     <t xml:space="preserve">Commission &gt; Agents/Referrer Accounts</t>
   </si>
   <si>
-    <t xml:space="preserve">IC licences of the firm, its officers and the agents and sub-agents paid commission (an agent without a licence in force is not paid: compliance.referrer_licence_check)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance &gt; Insurance Commission &gt; Licence Register</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fit and proper records of the directors and officers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance &gt; Insurance Commission &gt; Fit and Proper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IC certificate of authority number and validity of each insurer (columns of the Insurance Company sheet), mapping of the ledger to the IC annual statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance &gt; Insurance Commission &gt; Insurer Authority / IC Annual Statement &gt; Account mapping</t>
-  </si>
-  <si>
     <t xml:space="preserve">Petty cash funds</t>
   </si>
   <si>
@@ -2189,7 +2171,7 @@
     <t xml:space="preserve">yearly</t>
   </si>
   <si>
-    <t xml:space="preserve">compliance-officer</t>
+    <t xml:space="preserve">system-admin</t>
   </si>
   <si>
     <t xml:space="preserve">APEX</t>
@@ -2276,7 +2258,7 @@
     <t xml:space="preserve">fiscal_yearly</t>
   </si>
   <si>
-    <t xml:space="preserve">system-admin</t>
+    <t xml:space="preserve">sales</t>
   </si>
   <si>
     <t xml:space="preserve">EVERSAFE</t>
@@ -2348,7 +2330,7 @@
     <t xml:space="preserve">monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">sales</t>
+    <t xml:space="preserve">processing</t>
   </si>
   <si>
     <t xml:space="preserve">FPG</t>
@@ -2405,7 +2387,7 @@
     <t xml:space="preserve">never</t>
   </si>
   <si>
-    <t xml:space="preserve">processing</t>
+    <t xml:space="preserve">operations</t>
   </si>
   <si>
     <t xml:space="preserve">GOLDENHORIZON</t>
@@ -2444,7 +2426,7 @@
     <t xml:space="preserve">lgt</t>
   </si>
   <si>
-    <t xml:space="preserve">operations</t>
+    <t xml:space="preserve">claims</t>
   </si>
   <si>
     <t xml:space="preserve">INTEGRITY</t>
@@ -2468,7 +2450,7 @@
     <t xml:space="preserve">other</t>
   </si>
   <si>
-    <t xml:space="preserve">claims</t>
+    <t xml:space="preserve">accounting</t>
   </si>
   <si>
     <t xml:space="preserve">LIBERTYSHIELD</t>
@@ -2486,7 +2468,7 @@
     <t xml:space="preserve">Other Income</t>
   </si>
   <si>
-    <t xml:space="preserve">accounting</t>
+    <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
@@ -2502,9 +2484,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cost of Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
     <t xml:space="preserve">MAPFRE</t>
@@ -4105,7 +4084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B462"/>
+  <dimension ref="A1:B459"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4797,62 +4776,62 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B88" s="4" t="s">
-        <v>169</v>
-      </c>
+      <c r="B88" s="10"/>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B91" s="4" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B91" s="10"/>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>179</v>
@@ -4860,7 +4839,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>179</v>
@@ -4868,106 +4847,106 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="B109" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="110">
@@ -4991,551 +4970,551 @@
         <v>201</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>235</v>
+        <v>173</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>273</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>219</v>
+        <v>277</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="B180" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B180" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="181">
@@ -5543,71 +5522,71 @@
         <v>282</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="B182" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="B188" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B189" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="190">
@@ -5623,191 +5602,191 @@
         <v>298</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>299</v>
+        <v>170</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>301</v>
+        <v>170</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>303</v>
+        <v>170</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>273</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>179</v>
+        <v>310</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>316</v>
+        <v>170</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>322</v>
+        <v>194</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>179</v>
+        <v>321</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>200</v>
+        <v>324</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B213" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="215">
@@ -5815,31 +5794,31 @@
         <v>329</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>330</v>
+        <v>173</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B216" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="B218" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="219">
@@ -5863,263 +5842,263 @@
         <v>340</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>341</v>
+        <v>170</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>343</v>
+        <v>170</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>345</v>
+        <v>170</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>176</v>
+        <v>344</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>350</v>
+        <v>173</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>176</v>
+        <v>355</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>361</v>
+        <v>170</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>176</v>
+        <v>363</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>369</v>
+        <v>173</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>179</v>
+        <v>312</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>318</v>
+        <v>177</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>179</v>
+        <v>376</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="B253" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="B253" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="254">
@@ -6127,351 +6106,351 @@
         <v>379</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>380</v>
+        <v>194</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>382</v>
+        <v>170</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>384</v>
+        <v>170</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>176</v>
+        <v>390</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>396</v>
+        <v>173</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>179</v>
+        <v>400</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>406</v>
+        <v>170</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>200</v>
+        <v>405</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>176</v>
+        <v>407</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>411</v>
+        <v>194</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>413</v>
+        <v>170</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>253</v>
+        <v>425</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>176</v>
+        <v>427</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B297" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="B297" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="298">
@@ -6487,119 +6466,119 @@
         <v>432</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>433</v>
+        <v>173</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>435</v>
+        <v>312</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>318</v>
+        <v>170</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>441</v>
+        <v>170</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>176</v>
+        <v>446</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>176</v>
+        <v>448</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B313" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="B313" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="314">
@@ -6607,295 +6586,295 @@
         <v>451</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>452</v>
+        <v>194</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>454</v>
+        <v>170</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>456</v>
+        <v>170</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>176</v>
+        <v>456</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>462</v>
+        <v>170</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>176</v>
+        <v>462</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>468</v>
+        <v>194</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>200</v>
+        <v>467</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>477</v>
+        <v>213</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>273</v>
+        <v>170</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>179</v>
+        <v>490</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>179</v>
+        <v>492</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B350" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="B350" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="351">
@@ -6903,87 +6882,87 @@
         <v>495</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>496</v>
+        <v>173</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>498</v>
+        <v>177</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>500</v>
+        <v>173</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>200</v>
+        <v>504</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>176</v>
+        <v>506</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B361" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="B361" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="362">
@@ -7007,255 +6986,255 @@
         <v>513</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>514</v>
+        <v>173</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>516</v>
+        <v>194</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>518</v>
+        <v>170</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>179</v>
+        <v>517</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>200</v>
+        <v>519</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>523</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>525</v>
+        <v>170</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>200</v>
+        <v>525</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>176</v>
+        <v>527</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>531</v>
+        <v>194</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>533</v>
+        <v>170</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>179</v>
+        <v>532</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>200</v>
+        <v>534</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B381" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="B381" s="4" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>540</v>
+        <v>213</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>543</v>
+        <v>194</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>179</v>
+        <v>550</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>183</v>
+        <v>552</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="B395" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="B395" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="396">
@@ -7263,31 +7242,31 @@
         <v>555</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>556</v>
+        <v>194</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="B397" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="B397" s="4" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="B398" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="B398" s="4" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="B399" s="4" t="s">
         <v>561</v>
-      </c>
-      <c r="B399" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="400">
@@ -7311,55 +7290,55 @@
         <v>566</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>567</v>
+        <v>310</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="B403" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="B403" s="4" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
+        <v>569</v>
+      </c>
+      <c r="B404" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="B404" s="4" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
+        <v>572</v>
+      </c>
+      <c r="B406" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="B406" s="4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="B407" s="4" t="s">
         <v>575</v>
-      </c>
-      <c r="B407" s="4" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
+        <v>576</v>
+      </c>
+      <c r="B408" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="B408" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="409">
@@ -7423,71 +7402,71 @@
         <v>592</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>593</v>
+        <v>281</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>595</v>
+        <v>281</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>576</v>
+        <v>281</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>287</v>
+        <v>599</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>287</v>
+        <v>601</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="B424" s="4" t="s">
         <v>603</v>
-      </c>
-      <c r="B424" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="425">
@@ -7511,55 +7490,55 @@
         <v>608</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>609</v>
+        <v>281</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>611</v>
+        <v>281</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>613</v>
+        <v>335</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>287</v>
+        <v>613</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="0" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>341</v>
+        <v>615</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="B433" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="434">
@@ -7567,47 +7546,47 @@
         <v>618</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>619</v>
+        <v>281</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="B435" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>623</v>
+        <v>281</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>287</v>
+        <v>623</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="B438" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="B439" s="4" t="s">
         <v>627</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="440">
@@ -7631,31 +7610,31 @@
         <v>632</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>633</v>
+        <v>335</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="B443" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
+        <v>635</v>
+      </c>
+      <c r="B444" s="4" t="s">
         <v>636</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="B445" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="B445" s="4" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="446">
@@ -7671,63 +7650,63 @@
         <v>641</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>642</v>
+        <v>575</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="B448" s="4" t="s">
         <v>643</v>
-      </c>
-      <c r="B448" s="4" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>646</v>
+        <v>281</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>581</v>
+        <v>646</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>649</v>
+        <v>570</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>287</v>
+        <v>649</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="B453" s="4" t="s">
         <v>651</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="B454" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="B454" s="4" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="455">
@@ -7767,31 +7746,7 @@
         <v>662</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" s="0" t="s">
-        <v>664</v>
-      </c>
-      <c r="B460" s="4" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" s="0" t="s">
-        <v>666</v>
-      </c>
-      <c r="B461" s="4" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" s="0" t="s">
-        <v>668</v>
-      </c>
-      <c r="B462" s="4" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -7822,82 +7777,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>925</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>918</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>892</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>859</v>
-      </c>
       <c r="N1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -7926,33 +7881,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7980,33 +7935,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8036,45 +7991,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -8110,80 +8065,80 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>955</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>958</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="J1" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>961</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>962</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>963</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>964</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>965</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>966</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>890</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>967</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>968</v>
-      </c>
       <c r="M1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="L2:L5000">
-      <formula1>Lists!$M$2:$M$9</formula1>
+      <formula1>Lists!$M$2:$M$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
       <formula1>Lists!$G$2:$G$3</formula1>
@@ -8213,69 +8168,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>977</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>978</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>851</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>982</v>
-      </c>
       <c r="K1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8306,51 +8261,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -8384,67 +8339,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8497,87 +8452,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>892</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>925</v>
-      </c>
       <c r="N1" s="8" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -8622,117 +8577,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1004</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>1011</v>
-      </c>
       <c r="D1" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>1026</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>1029</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>1030</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>1031</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>1033</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>1034</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>1035</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>1037</v>
-      </c>
       <c r="S1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>992</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1036</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>1038</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>1039</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>1040</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>1041</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>1042</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>999</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>1043</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="P2" s="9" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Q2" s="9" t="s">
         <v>1044</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>1045</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>1046</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>1047</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>1050</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>1043</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>1051</v>
-      </c>
       <c r="R2" s="9" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -8789,361 +8744,361 @@
   <sheetData>
     <row r="1" spans="1:31" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>669</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>677</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>681</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>682</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>693</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="AB1" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="AD1" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="AE1" s="8" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>696</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>697</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>705</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>705</v>
-      </c>
-      <c r="H2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>707</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>712</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>715</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="AA2" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="AB2" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>720</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="AD2" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="AE2" s="11" t="s">
         <v>722</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>723</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="AA2" s="11" t="s">
-        <v>724</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>725</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>726</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>727</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>726</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>728</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>731</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>736</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="P3" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="Q3" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="R3" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="T3" s="11" t="s">
         <v>741</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="U3" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="V3" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="W3" s="11" t="s">
         <v>744</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="X3" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="Y3" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="Z3" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="AA3" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="AB3" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="V3" s="11" t="s">
+      <c r="AC3" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="AD3" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="X3" s="11" t="s">
+      <c r="AE3" s="11" t="s">
         <v>751</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>752</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>736</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>753</v>
-      </c>
-      <c r="AB3" s="11" t="s">
-        <v>754</v>
-      </c>
-      <c r="AC3" s="11" t="s">
-        <v>755</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>756</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="R4" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="S4" s="11" t="s">
         <v>764</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="T4" s="11" t="s">
         <v>765</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="U4" s="11" t="s">
         <v>766</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>767</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>768</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>769</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>770</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>771</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>772</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="AE4" s="11"/>
     </row>
@@ -9151,46 +9106,46 @@
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="R5" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="S5" s="11" t="s">
         <v>783</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="T5" s="11" t="s">
         <v>784</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>785</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>786</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>787</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>788</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>789</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>790</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -9199,14 +9154,14 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="AE5" s="11"/>
     </row>
@@ -9214,37 +9169,37 @@
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -9254,7 +9209,7 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
@@ -9266,29 +9221,29 @@
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -9301,7 +9256,7 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
@@ -9313,7 +9268,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -9324,16 +9279,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -9346,7 +9301,7 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
@@ -9358,7 +9313,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -9368,17 +9323,15 @@
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
-      <c r="M9" s="11" t="s">
-        <v>816</v>
-      </c>
+      <c r="M9" s="11"/>
       <c r="N9" s="11" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -9401,7 +9354,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -9413,13 +9366,13 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -9442,7 +9395,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -9454,13 +9407,13 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -9483,7 +9436,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -9495,13 +9448,13 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -9534,13 +9487,13 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -9573,10 +9526,10 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -9611,7 +9564,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -9646,7 +9599,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -9681,7 +9634,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -9716,7 +9669,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
@@ -9751,7 +9704,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -9786,7 +9739,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
@@ -9825,36 +9778,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -9892,80 +9845,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>1060</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>882</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>1062</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>1063</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>1066</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>938</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1067</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>1068</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>1069</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>1070</v>
-      </c>
       <c r="N1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -9998,39 +9951,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -10075,122 +10028,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>1087</v>
+      </c>
+      <c r="R1" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>851</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>846</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>852</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>918</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>892</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>925</v>
-      </c>
-      <c r="M1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>1092</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>1093</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>1094</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>1095</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>1096</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>1097</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>1098</v>
-      </c>
       <c r="V1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -10226,27 +10179,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -10277,48 +10230,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10356,33 +10309,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10410,30 +10363,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -10462,15 +10415,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -10496,21 +10449,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -10553,115 +10506,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>843</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>845</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>846</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="O1" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>856</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>715</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>857</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>858</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>860</v>
-      </c>
       <c r="T1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -10689,33 +10642,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10746,51 +10699,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -10827,87 +10780,87 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>1165</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>1166</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>846</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>1171</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1034</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>964</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>1172</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>1173</v>
-      </c>
       <c r="N1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>1173</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>1174</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>1175</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="L2" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>1176</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>1110</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>1179</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>1180</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>1181</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>1182</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>1041</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>1183</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -10939,54 +10892,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -11015,33 +10968,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11070,39 +11023,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -11139,48 +11092,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11216,75 +11169,75 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1215</v>
+        <v>1208</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1216</v>
+        <v>1209</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1217</v>
+        <v>1210</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1218</v>
+        <v>1211</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1219</v>
+        <v>1212</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>1220</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>1221</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>1222</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>1223</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>1224</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>1227</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>700</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>1228</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>1229</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -11316,56 +11269,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
     </row>
   </sheetData>
@@ -11412,70 +11365,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>1239</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>1240</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="L1" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>1242</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1243</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>679</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1246</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>1247</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>1248</v>
-      </c>
       <c r="O1" s="8" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1251</v>
+        <v>1244</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11484,10 +11437,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -11523,24 +11476,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -11566,55 +11519,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1252</v>
+        <v>1245</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1253</v>
+        <v>1246</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1253</v>
+        <v>1246</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -11641,30 +11594,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1256</v>
+        <v>1249</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1260</v>
+        <v>1253</v>
       </c>
     </row>
   </sheetData>
@@ -11673,7 +11626,7 @@
       <formula1>Lists!$P$2:$P$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
-      <formula1>Lists!$M$2:$M$9</formula1>
+      <formula1>Lists!$M$2:$M$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11697,54 +11650,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1261</v>
+        <v>1254</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1262</v>
+        <v>1255</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -11778,56 +11731,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -11863,49 +11816,49 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -11933,33 +11886,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>881</v>
+        <v>874</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11989,43 +11942,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -12056,48 +12009,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12134,53 +12087,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -12213,33 +12166,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -42,19 +42,21 @@
     <sheet name="Cancellation Reasons" sheetId="35" r:id="rId35"/>
     <sheet name="Claim Document Checklist" sheetId="36" r:id="rId36"/>
     <sheet name="Repair Shops" sheetId="37" r:id="rId37"/>
-    <sheet name="Commission Rates" sheetId="38" r:id="rId38"/>
-    <sheet name="Premium Taxes" sheetId="39" r:id="rId39"/>
-    <sheet name="LGU Rates" sheetId="40" r:id="rId40"/>
-    <sheet name="Authority Limits" sheetId="41" r:id="rId41"/>
-    <sheet name="Numbering" sheetId="42" r:id="rId42"/>
-    <sheet name="Payee Bank Accounts" sheetId="43" r:id="rId43"/>
-    <sheet name="COC Series" sheetId="44" r:id="rId44"/>
+    <sheet name="Lead Sources" sheetId="38" r:id="rId38"/>
+    <sheet name="Reason Codes" sheetId="39" r:id="rId39"/>
+    <sheet name="Commission Rates" sheetId="40" r:id="rId40"/>
+    <sheet name="Premium Taxes" sheetId="41" r:id="rId41"/>
+    <sheet name="LGU Rates" sheetId="42" r:id="rId42"/>
+    <sheet name="Authority Limits" sheetId="43" r:id="rId43"/>
+    <sheet name="Numbering" sheetId="44" r:id="rId44"/>
+    <sheet name="Payee Bank Accounts" sheetId="45" r:id="rId45"/>
+    <sheet name="COC Series" sheetId="46" r:id="rId46"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1329">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -329,43 +331,55 @@
     <t xml:space="preserve">Master &gt; Insurance Management &gt; Repair Shops. Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">36. Commission Rates</t>
+    <t xml:space="preserve">36. Lead Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Lead Sources. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37. Reason Codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Reason Codes. Key: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38. Commission Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Commission Rate Matrix. Key: Insurer + Product + Line of Business + Policy Type + Effective From</t>
   </si>
   <si>
-    <t xml:space="preserve">37. Premium Taxes</t>
+    <t xml:space="preserve">39. Premium Taxes</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (Taxes &amp; Charges). Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">38. LGU Rates</t>
+    <t xml:space="preserve">40. LGU Rates</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (LGU Tax Rates). Key: Code</t>
   </si>
   <si>
-    <t xml:space="preserve">39. Authority Limits</t>
+    <t xml:space="preserve">41. Authority Limits</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; Authority Matrix. Key: Transaction Type + Role</t>
   </si>
   <si>
-    <t xml:space="preserve">40. Numbering</t>
+    <t xml:space="preserve">42. Numbering</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code</t>
   </si>
   <si>
-    <t xml:space="preserve">41. Payee Bank Accounts</t>
+    <t xml:space="preserve">43. Payee Bank Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts (Payee bank accounts). Key: Payee Type + Payee + Account Number</t>
   </si>
   <si>
-    <t xml:space="preserve">42. COC Series</t>
+    <t xml:space="preserve">44. COC Series</t>
   </si>
   <si>
     <t xml:space="preserve">Operations &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From</t>
@@ -1724,6 +1738,63 @@
     <t xml:space="preserve">Repair Shops: Status</t>
   </si>
   <si>
+    <t xml:space="preserve">Lead Sources: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Sources: Lead Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Sources: Channel Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Direct, Bancassurance / Affinity, Digital ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Sources: Linked Office (branch code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Branch code of the office the source belongs to (Branch master)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Sources: Sort Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Order in the list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Sources: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Sources: Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Used For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required. decline (quotation rejected or dropped), repudiation (claim rejected), lapse (renewal lapsed), refund, adjustment or non-materialise. Values: Lists sheet, Reason Code Used For</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Requires Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Yes when the user must also write the detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Sort Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason Codes: Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">Commission Rates: Insurer</t>
   </si>
   <si>
@@ -2132,6 +2203,9 @@
     <t xml:space="preserve">Cancellation Reason Return Premium Method</t>
   </si>
   <si>
+    <t xml:space="preserve">Reason Code Used For</t>
+  </si>
+  <si>
     <t xml:space="preserve">Payee Type</t>
   </si>
   <si>
@@ -2177,7 +2251,7 @@
     <t xml:space="preserve">APEX</t>
   </si>
   <si>
-    <t xml:space="preserve">BOND</t>
+    <t xml:space="preserve">CL-COMP</t>
   </si>
   <si>
     <t xml:space="preserve">quotation_discount</t>
@@ -2219,6 +2293,9 @@
     <t xml:space="preserve">auto</t>
   </si>
   <si>
+    <t xml:space="preserve">decline</t>
+  </si>
+  <si>
     <t xml:space="preserve">Insurer</t>
   </si>
   <si>
@@ -2261,307 +2338,343 @@
     <t xml:space="preserve">sales</t>
   </si>
   <si>
+    <t xml:space="preserve">AXA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL-VOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy_issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitan area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non_package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pro-rata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repudiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent/Referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processing</t>
+  </si>
+  <si>
     <t xml:space="preserve">EVERSAFE</t>
   </si>
   <si>
-    <t xml:space="preserve">BURGLARY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">policy_issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metropolitan area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Component City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non_package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pro-rata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent/Referrer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processing</t>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return_premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Geographic Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrift Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short-period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">never</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operations</t>
   </si>
   <si>
     <t xml:space="preserve">FPG</t>
   </si>
   <si>
-    <t xml:space="preserve">CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">return_premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Special Geographic Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thrift Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Deposit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short-period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">never</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operations</t>
+    <t xml:space="preserve">GPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claim_settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province / state outside the Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lgt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claims</t>
   </si>
   <si>
     <t xml:space="preserve">GOLDENHORIZON</t>
   </si>
   <si>
-    <t xml:space="preserve">CGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claim_settlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province / state outside the Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trust Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lgt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claims</t>
+    <t xml:space="preserve">MOTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting</t>
   </si>
   <si>
     <t xml:space="preserve">INTEGRITY</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting</t>
+    <t xml:space="preserve">PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">journal_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casualty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non-materialise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
     <t xml:space="preserve">LIBERTYSHIELD</t>
   </si>
   <si>
-    <t xml:space="preserve">EAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casualty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting-manager</t>
+    <t xml:space="preserve">PARCEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">write_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-sales-associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAAGAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRAVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commission_payout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-sales-officer</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">EB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">write_off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost of Services</t>
+    <t xml:space="preserve">petty_cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-sales-unit-head</t>
   </si>
   <si>
     <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
-    <t xml:space="preserve">FIRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commission_payout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating Expenses</t>
+    <t xml:space="preserve">remittance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-ops-associate</t>
   </si>
   <si>
     <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
-    <t xml:space="preserve">GPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">petty_cash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Expenses</t>
+    <t xml:space="preserve">remittance_settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-ops-officer</t>
   </si>
   <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">HOME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remittance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income Tax</t>
+    <t xml:space="preserve">underwriting_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-ops-unit-head</t>
   </si>
   <si>
     <t xml:space="preserve">SECUREGUARD</t>
   </si>
   <si>
-    <t xml:space="preserve">HULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remittance_settlement</t>
+    <t xml:space="preserve">tis-ccd-pdu</t>
   </si>
   <si>
     <t xml:space="preserve">SENTINEL</t>
   </si>
   <si>
-    <t xml:space="preserve">IAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">underwriting_referral</t>
+    <t xml:space="preserve">tis-ccd-pdc</t>
   </si>
   <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">MARINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVEL</t>
+    <t xml:space="preserve">tis-ccd-bp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRONGHOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-ccd-recon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-it-admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-general-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-superid</t>
   </si>
   <si>
     <t xml:space="preserve">Company Code *</t>
@@ -3725,6 +3838,42 @@
     <t xml:space="preserve">650</t>
   </si>
   <si>
+    <t xml:space="preserve">Lead Source *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked Office (branch code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE EVENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor show / event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used For *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMPLE LAP-PRICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found a cheaper premium elsewhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300</t>
+  </si>
+  <si>
     <t xml:space="preserve">Product</t>
   </si>
   <si>
@@ -3786,9 +3935,6 @@
   </si>
   <si>
     <t xml:space="preserve">Notarial fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150</t>
   </si>
   <si>
     <t xml:space="preserve">SAMPLE VAL</t>
@@ -4084,7 +4230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B459"/>
+  <dimension ref="A1:B475"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4518,26 +4664,26 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="B55" s="10"/>
+      <c r="B55" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="B57" s="4" t="s">
+      <c r="A57" s="10" t="s">
         <v>109</v>
       </c>
+      <c r="B57" s="10"/>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
@@ -4556,26 +4702,26 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="10"/>
+      <c r="B60" s="4" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="B62" s="4" t="s">
+      <c r="A62" s="10" t="s">
         <v>118</v>
       </c>
+      <c r="B62" s="10"/>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
@@ -4602,26 +4748,26 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="10"/>
+      <c r="B66" s="4" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="B68" s="4" t="s">
+      <c r="A68" s="10" t="s">
         <v>129</v>
       </c>
+      <c r="B68" s="10"/>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
@@ -4776,54 +4922,54 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B88" s="10"/>
+      <c r="B88" s="4" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>170</v>
-      </c>
+      <c r="A90" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B90" s="10"/>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>177</v>
@@ -4831,10 +4977,10 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96">
@@ -4842,103 +4988,103 @@
         <v>180</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109">
@@ -4970,87 +5116,87 @@
         <v>201</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
     </row>
     <row r="123">
@@ -5058,455 +5204,455 @@
         <v>214</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>229</v>
+        <v>174</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>240</v>
+        <v>177</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>247</v>
+        <v>174</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>173</v>
+        <v>251</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>267</v>
+        <v>174</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>170</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>277</v>
+        <v>217</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
     </row>
     <row r="180">
@@ -5522,63 +5668,63 @@
         <v>282</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="B183" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="189">
@@ -5602,103 +5748,103 @@
         <v>298</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>170</v>
+        <v>299</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>170</v>
+        <v>301</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>267</v>
+        <v>177</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>192</v>
+        <v>271</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>310</v>
+        <v>196</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>312</v>
+        <v>198</v>
       </c>
     </row>
     <row r="204">
@@ -5706,79 +5852,79 @@
         <v>313</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>170</v>
+        <v>314</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>170</v>
+        <v>316</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>316</v>
+        <v>174</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>173</v>
+        <v>320</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>321</v>
+        <v>177</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>326</v>
+        <v>174</v>
       </c>
     </row>
     <row r="214">
@@ -5794,23 +5940,23 @@
         <v>329</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>173</v>
+        <v>330</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>333</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218">
@@ -5842,236 +5988,236 @@
         <v>340</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>170</v>
+        <v>341</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>170</v>
+        <v>343</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>344</v>
+        <v>174</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>173</v>
+        <v>348</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>247</v>
+        <v>174</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>355</v>
+        <v>177</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>194</v>
+        <v>251</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>170</v>
+        <v>359</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>363</v>
+        <v>177</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>173</v>
+        <v>367</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>312</v>
+        <v>177</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>173</v>
+        <v>316</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>177</v>
@@ -6079,18 +6225,18 @@
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>374</v>
+        <v>177</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>376</v>
+        <v>181</v>
       </c>
     </row>
     <row r="253">
@@ -6106,199 +6252,199 @@
         <v>379</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>194</v>
+        <v>380</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>170</v>
+        <v>382</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>390</v>
+        <v>174</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>173</v>
+        <v>394</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>400</v>
+        <v>177</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>170</v>
+        <v>404</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>405</v>
+        <v>174</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>407</v>
+        <v>174</v>
       </c>
     </row>
     <row r="279">
@@ -6306,143 +6452,143 @@
         <v>408</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>173</v>
+        <v>409</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>194</v>
+        <v>411</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>247</v>
+        <v>174</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>173</v>
+        <v>251</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>425</v>
+        <v>174</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>427</v>
+        <v>177</v>
       </c>
     </row>
     <row r="297">
@@ -6466,111 +6612,111 @@
         <v>432</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>173</v>
+        <v>433</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>312</v>
+        <v>435</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>435</v>
+        <v>177</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>194</v>
+        <v>316</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>170</v>
+        <v>439</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>446</v>
+        <v>174</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>448</v>
+        <v>174</v>
       </c>
     </row>
     <row r="313">
@@ -6586,287 +6732,287 @@
         <v>451</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>194</v>
+        <v>452</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>170</v>
+        <v>454</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>456</v>
+        <v>174</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>170</v>
+        <v>460</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>462</v>
+        <v>174</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>170</v>
+        <v>466</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>467</v>
+        <v>174</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>194</v>
+        <v>471</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>471</v>
+        <v>174</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>173</v>
+        <v>475</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>267</v>
+        <v>174</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>194</v>
+        <v>271</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>490</v>
+        <v>177</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>492</v>
+        <v>196</v>
       </c>
     </row>
     <row r="350">
@@ -6882,79 +7028,79 @@
         <v>495</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>173</v>
+        <v>496</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>177</v>
+        <v>498</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>504</v>
+        <v>174</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>506</v>
+        <v>174</v>
       </c>
     </row>
     <row r="361">
@@ -6986,39 +7132,39 @@
         <v>513</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>173</v>
+        <v>514</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>194</v>
+        <v>516</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>517</v>
+        <v>198</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>519</v>
+        <v>174</v>
       </c>
     </row>
     <row r="369">
@@ -7026,47 +7172,47 @@
         <v>520</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>173</v>
+        <v>521</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>194</v>
+        <v>523</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>525</v>
+        <v>174</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>527</v>
+        <v>174</v>
       </c>
     </row>
     <row r="375">
@@ -7074,39 +7220,39 @@
         <v>528</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>194</v>
+        <v>531</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>532</v>
+        <v>198</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>534</v>
+        <v>174</v>
       </c>
     </row>
     <row r="380">
@@ -7114,92 +7260,92 @@
         <v>535</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>170</v>
+        <v>536</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>173</v>
+        <v>541</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B391" s="4" t="s">
         <v>177</v>
@@ -7207,26 +7353,26 @@
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>550</v>
+        <v>181</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>552</v>
+        <v>177</v>
       </c>
     </row>
     <row r="395">
@@ -7242,23 +7388,23 @@
         <v>555</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>194</v>
+        <v>556</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>559</v>
+        <v>198</v>
       </c>
     </row>
     <row r="399">
@@ -7266,247 +7412,247 @@
         <v>560</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>561</v>
+        <v>174</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>563</v>
+        <v>174</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>310</v>
+        <v>565</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="B403" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="B403" s="4" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>570</v>
+        <v>177</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>281</v>
+        <v>198</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>573</v>
+        <v>174</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>575</v>
+        <v>174</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="0" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>581</v>
+        <v>217</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>583</v>
+        <v>177</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>585</v>
+        <v>198</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="0" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>281</v>
+        <v>586</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>281</v>
+        <v>588</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>570</v>
+        <v>314</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>281</v>
+        <v>591</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>281</v>
+        <v>593</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>281</v>
+        <v>606</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>281</v>
+        <v>608</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="B429" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="B429" s="4" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="430">
@@ -7514,23 +7660,23 @@
         <v>611</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>281</v>
+        <v>612</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>615</v>
+        <v>285</v>
       </c>
     </row>
     <row r="433">
@@ -7538,215 +7684,343 @@
         <v>616</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>617</v>
+        <v>285</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>281</v>
+        <v>593</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>620</v>
+        <v>285</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>623</v>
+        <v>285</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>335</v>
+        <v>630</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>634</v>
+        <v>285</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>636</v>
+        <v>285</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>638</v>
+        <v>339</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>640</v>
+        <v>285</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>575</v>
+        <v>636</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>281</v>
+        <v>640</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>646</v>
+        <v>285</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>570</v>
+        <v>643</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>649</v>
+        <v>285</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="0" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>661</v>
+        <v>339</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="B461" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0" t="s">
         <v>662</v>
       </c>
-      <c r="B459" s="4" t="s">
-        <v>281</v>
+      <c r="B462" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="B463" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0" t="s">
+        <v>665</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="B465" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="B466" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0" t="s">
+        <v>670</v>
+      </c>
+      <c r="B467" s="4" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="B468" s="4" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0" t="s">
+        <v>673</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0" t="s">
+        <v>675</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0" t="s">
+        <v>677</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0" t="s">
+        <v>679</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0" t="s">
+        <v>683</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0" t="s">
+        <v>685</v>
+      </c>
+      <c r="B475" s="4" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -7777,82 +8051,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>916</v>
+        <v>953</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>917</v>
+        <v>954</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>837</v>
+        <v>874</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>918</v>
+        <v>955</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>845</v>
+        <v>882</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>846</v>
+        <v>883</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>851</v>
+        <v>888</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>919</v>
+        <v>956</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>920</v>
+        <v>957</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>921</v>
+        <v>958</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>922</v>
+        <v>959</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>923</v>
+        <v>960</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>924</v>
+        <v>961</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>925</v>
+        <v>962</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>926</v>
+        <v>963</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>927</v>
+        <v>964</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>866</v>
+        <v>903</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>928</v>
+        <v>965</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -7881,33 +8155,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>929</v>
+        <v>966</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>930</v>
+        <v>967</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>932</v>
+        <v>969</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>933</v>
+        <v>970</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>934</v>
+        <v>971</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>935</v>
+        <v>972</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7935,33 +8209,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>936</v>
+        <v>973</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>937</v>
+        <v>974</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>938</v>
+        <v>975</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>939</v>
+        <v>976</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>940</v>
+        <v>977</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>941</v>
+        <v>978</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>942</v>
+        <v>979</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -7991,45 +8265,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>943</v>
+        <v>980</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>944</v>
+        <v>981</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>929</v>
+        <v>966</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>895</v>
+        <v>932</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>945</v>
+        <v>982</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>946</v>
+        <v>983</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>947</v>
+        <v>984</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>948</v>
+        <v>985</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>949</v>
+        <v>986</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>950</v>
+        <v>987</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>951</v>
+        <v>988</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -8065,80 +8339,80 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>952</v>
+        <v>989</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>953</v>
+        <v>990</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>954</v>
+        <v>991</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>955</v>
+        <v>992</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>956</v>
+        <v>993</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>957</v>
+        <v>994</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>958</v>
+        <v>995</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>959</v>
+        <v>996</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>883</v>
+        <v>920</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>960</v>
+        <v>997</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>961</v>
+        <v>998</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>962</v>
+        <v>999</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>964</v>
+        <v>1001</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>965</v>
+        <v>1002</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>966</v>
+        <v>1003</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>935</v>
+        <v>972</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>798</v>
+        <v>827</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>699</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="L2:L5000">
-      <formula1>Lists!$M$2:$M$8</formula1>
+      <formula1>Lists!$M$2:$M$22</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
       <formula1>Lists!$G$2:$G$3</formula1>
@@ -8168,69 +8442,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>967</v>
+        <v>1004</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>968</v>
+        <v>1005</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>969</v>
+        <v>1006</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>970</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>971</v>
+        <v>1008</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>972</v>
+        <v>1009</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>973</v>
+        <v>1010</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>974</v>
+        <v>1011</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>975</v>
+        <v>1012</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>976</v>
+        <v>1013</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>977</v>
+        <v>1014</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>978</v>
+        <v>1015</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>979</v>
+        <v>1016</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>980</v>
+        <v>1017</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>980</v>
+        <v>1017</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>981</v>
+        <v>1018</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>951</v>
+        <v>988</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>982</v>
+        <v>1019</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8261,51 +8535,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>983</v>
+        <v>1020</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>984</v>
+        <v>1021</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>967</v>
+        <v>1004</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>985</v>
+        <v>1022</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>986</v>
+        <v>1023</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>987</v>
+        <v>1024</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>988</v>
+        <v>1025</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>989</v>
+        <v>1026</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>990</v>
+        <v>1027</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>991</v>
+        <v>1028</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>992</v>
+        <v>1029</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>993</v>
+        <v>1030</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>994</v>
+        <v>1031</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>995</v>
+        <v>1032</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -8339,67 +8613,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>996</v>
+        <v>1033</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>997</v>
+        <v>1034</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>998</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>999</v>
+        <v>1036</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1000</v>
+        <v>1037</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1001</v>
+        <v>1038</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1002</v>
+        <v>1039</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1003</v>
+        <v>1040</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>698</v>
+        <v>722</v>
       </c>
       <c r="H2" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>723</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>699</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8452,87 +8726,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1004</v>
+        <v>1041</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1005</v>
+        <v>1042</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1006</v>
+        <v>1043</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1007</v>
+        <v>1044</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>845</v>
+        <v>882</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>846</v>
+        <v>883</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1008</v>
+        <v>1045</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>918</v>
+        <v>955</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>999</v>
+        <v>1036</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1009</v>
+        <v>1046</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1010</v>
+        <v>1047</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1011</v>
+        <v>1048</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1012</v>
+        <v>1049</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1013</v>
+        <v>1050</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1014</v>
+        <v>1051</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>866</v>
+        <v>903</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1015</v>
+        <v>1052</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>1016</v>
+        <v>1053</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -8577,117 +8851,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>996</v>
+        <v>1033</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>997</v>
+        <v>1034</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1004</v>
+        <v>1041</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1017</v>
+        <v>1054</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1018</v>
+        <v>1055</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1019</v>
+        <v>1056</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1020</v>
+        <v>1057</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1021</v>
+        <v>1058</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1022</v>
+        <v>1059</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1023</v>
+        <v>1060</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1024</v>
+        <v>1061</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1025</v>
+        <v>1062</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1026</v>
+        <v>1063</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1027</v>
+        <v>1064</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1028</v>
+        <v>1065</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1029</v>
+        <v>1066</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1030</v>
+        <v>1067</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1031</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1032</v>
+        <v>1069</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1033</v>
+        <v>1070</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1035</v>
+        <v>1072</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>992</v>
+        <v>1029</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1037</v>
+        <v>1074</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1038</v>
+        <v>1075</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1040</v>
+        <v>1077</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1042</v>
+        <v>1079</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1043</v>
+        <v>1080</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1044</v>
+        <v>1081</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>1040</v>
+        <v>1077</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -8706,7 +8980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE20"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
@@ -8738,414 +9012,427 @@
     <col min="27" max="27" width="47" style="11" customWidth="1"/>
     <col min="28" max="28" width="36" style="11" customWidth="1"/>
     <col min="29" max="29" width="45" style="11" customWidth="1"/>
-    <col min="30" max="30" width="14" style="11" customWidth="1"/>
-    <col min="31" max="31" width="21" style="11" customWidth="1"/>
+    <col min="30" max="30" width="24" style="11" customWidth="1"/>
+    <col min="31" max="31" width="14" style="11" customWidth="1"/>
+    <col min="32" max="32" width="21" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="20" customHeight="1">
+    <row r="1" spans="1:32" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>663</v>
+        <v>686</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>667</v>
+        <v>690</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>669</v>
+        <v>692</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>670</v>
+        <v>693</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>671</v>
+        <v>694</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>672</v>
+        <v>695</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>674</v>
+        <v>697</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>675</v>
+        <v>698</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>676</v>
+        <v>699</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>677</v>
+        <v>700</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>678</v>
+        <v>701</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>679</v>
+        <v>702</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>680</v>
+        <v>703</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>681</v>
+        <v>704</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>682</v>
+        <v>705</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>683</v>
+        <v>706</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>684</v>
+        <v>707</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>685</v>
+        <v>708</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>686</v>
+        <v>709</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>687</v>
+        <v>710</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>688</v>
+        <v>711</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>691</v>
+        <v>714</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>692</v>
+        <v>715</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>693</v>
+        <v>716</v>
+      </c>
+      <c r="AF1" s="8" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>696</v>
+        <v>720</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>698</v>
+        <v>722</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>699</v>
+        <v>723</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>699</v>
+        <v>723</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>702</v>
+        <v>726</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>703</v>
+        <v>727</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>711</v>
+        <v>735</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="U2" s="11" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>714</v>
+        <v>738</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>715</v>
+        <v>739</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="Y2" s="11" t="s">
-        <v>717</v>
+        <v>741</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="AA2" s="11" t="s">
-        <v>718</v>
+        <v>742</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>719</v>
+        <v>743</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>721</v>
+        <v>745</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>722</v>
+        <v>746</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>728</v>
+        <v>753</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>729</v>
+        <v>754</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>733</v>
+        <v>758</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>734</v>
+        <v>759</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>736</v>
+        <v>761</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>738</v>
+        <v>763</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>739</v>
+        <v>764</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>741</v>
+        <v>766</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>742</v>
+        <v>767</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>744</v>
+        <v>769</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>746</v>
+        <v>771</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>730</v>
+        <v>755</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>747</v>
+        <v>772</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>748</v>
+        <v>773</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>750</v>
+        <v>775</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>751</v>
+        <v>776</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>752</v>
+        <v>778</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>753</v>
+        <v>779</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>754</v>
+        <v>780</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>755</v>
+        <v>781</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>756</v>
+        <v>782</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>757</v>
+        <v>783</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>758</v>
+        <v>784</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>759</v>
+        <v>785</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>761</v>
+        <v>787</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>762</v>
+        <v>788</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>763</v>
+        <v>789</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>764</v>
+        <v>790</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>766</v>
+        <v>792</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>767</v>
+        <v>793</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>768</v>
+        <v>794</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>770</v>
+        <v>796</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11" t="s">
-        <v>771</v>
+        <v>797</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>772</v>
-      </c>
-      <c r="AE4" s="11"/>
+        <v>798</v>
+      </c>
+      <c r="AE4" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="AF4" s="11"/>
     </row>
     <row r="5">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>779</v>
+        <v>806</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>782</v>
+        <v>809</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -9154,52 +9441,55 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>785</v>
+        <v>812</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>756</v>
+        <v>782</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>786</v>
-      </c>
-      <c r="AE5" s="11"/>
+        <v>813</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>814</v>
+      </c>
+      <c r="AF5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>787</v>
+        <v>815</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>788</v>
+        <v>816</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>790</v>
+        <v>818</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>794</v>
+        <v>822</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -9209,41 +9499,44 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>795</v>
+        <v>823</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
+      <c r="AD6" s="11" t="s">
+        <v>824</v>
+      </c>
       <c r="AE6" s="11"/>
+      <c r="AF6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>796</v>
+        <v>825</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>797</v>
+        <v>826</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>798</v>
+        <v>827</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>800</v>
+        <v>829</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>801</v>
+        <v>830</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -9256,19 +9549,22 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>802</v>
+        <v>831</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
+      <c r="AD7" s="11" t="s">
+        <v>832</v>
+      </c>
       <c r="AE7" s="11"/>
+      <c r="AF7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>803</v>
+        <v>833</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -9279,16 +9575,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>804</v>
+        <v>834</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>805</v>
+        <v>835</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>806</v>
+        <v>836</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>807</v>
+        <v>837</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -9301,19 +9597,20 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
       <c r="AD8" s="11"/>
       <c r="AE8" s="11"/>
+      <c r="AF8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>809</v>
+        <v>839</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -9323,15 +9620,17 @@
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
+      <c r="M9" s="11" t="s">
+        <v>840</v>
+      </c>
       <c r="N9" s="11" t="s">
-        <v>810</v>
+        <v>841</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>811</v>
+        <v>842</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>812</v>
+        <v>843</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -9343,18 +9642,21 @@
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
-      <c r="AA9" s="11"/>
+      <c r="AA9" s="11" t="s">
+        <v>844</v>
+      </c>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>813</v>
+        <v>845</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -9364,15 +9666,15 @@
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
+      <c r="M10" s="11" t="s">
+        <v>846</v>
+      </c>
       <c r="N10" s="11" t="s">
-        <v>814</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>815</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="O10" s="11"/>
       <c r="P10" s="11" t="s">
-        <v>816</v>
+        <v>848</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -9389,13 +9691,14 @@
       <c r="AC10" s="11"/>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
+      <c r="AF10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>817</v>
+        <v>849</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -9405,15 +9708,15 @@
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+      <c r="M11" s="11" t="s">
+        <v>850</v>
+      </c>
       <c r="N11" s="11" t="s">
-        <v>818</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>819</v>
-      </c>
+        <v>851</v>
+      </c>
+      <c r="O11" s="11"/>
       <c r="P11" s="11" t="s">
-        <v>820</v>
+        <v>852</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -9430,13 +9733,14 @@
       <c r="AC11" s="11"/>
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>821</v>
+        <v>853</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -9446,15 +9750,15 @@
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
+      <c r="M12" s="11" t="s">
+        <v>854</v>
+      </c>
       <c r="N12" s="11" t="s">
-        <v>822</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>823</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="O12" s="11"/>
       <c r="P12" s="11" t="s">
-        <v>824</v>
+        <v>856</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -9471,6 +9775,7 @@
       <c r="AC12" s="11"/>
       <c r="AD12" s="11"/>
       <c r="AE12" s="11"/>
+      <c r="AF12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -9485,15 +9790,15 @@
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
+      <c r="M13" s="11" t="s">
+        <v>857</v>
+      </c>
       <c r="N13" s="11" t="s">
-        <v>825</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>826</v>
-      </c>
+        <v>858</v>
+      </c>
+      <c r="O13" s="11"/>
       <c r="P13" s="11" t="s">
-        <v>827</v>
+        <v>859</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -9510,6 +9815,7 @@
       <c r="AC13" s="11"/>
       <c r="AD13" s="11"/>
       <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -9524,13 +9830,13 @@
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
+      <c r="M14" s="11" t="s">
+        <v>860</v>
+      </c>
       <c r="N14" s="11" t="s">
-        <v>828</v>
-      </c>
-      <c r="O14" s="11" t="s">
-        <v>829</v>
-      </c>
+        <v>861</v>
+      </c>
+      <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
@@ -9547,6 +9853,7 @@
       <c r="AC14" s="11"/>
       <c r="AD14" s="11"/>
       <c r="AE14" s="11"/>
+      <c r="AF14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -9561,11 +9868,13 @@
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11" t="s">
-        <v>830</v>
-      </c>
+      <c r="M15" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
@@ -9582,6 +9891,7 @@
       <c r="AC15" s="11"/>
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
+      <c r="AF15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -9596,11 +9906,13 @@
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11" t="s">
-        <v>831</v>
-      </c>
+      <c r="M16" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
@@ -9617,6 +9929,7 @@
       <c r="AC16" s="11"/>
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
+      <c r="AF16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -9631,11 +9944,13 @@
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11" t="s">
-        <v>832</v>
-      </c>
+      <c r="M17" s="11" t="s">
+        <v>866</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
@@ -9652,6 +9967,7 @@
       <c r="AC17" s="11"/>
       <c r="AD17" s="11"/>
       <c r="AE17" s="11"/>
+      <c r="AF17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -9666,11 +9982,11 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
+      <c r="M18" s="11" t="s">
+        <v>868</v>
+      </c>
       <c r="N18" s="11"/>
-      <c r="O18" s="11" t="s">
-        <v>833</v>
-      </c>
+      <c r="O18" s="11"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
@@ -9687,6 +10003,7 @@
       <c r="AC18" s="11"/>
       <c r="AD18" s="11"/>
       <c r="AE18" s="11"/>
+      <c r="AF18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -9701,11 +10018,11 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
+      <c r="M19" s="11" t="s">
+        <v>869</v>
+      </c>
       <c r="N19" s="11"/>
-      <c r="O19" s="11" t="s">
-        <v>834</v>
-      </c>
+      <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
@@ -9722,6 +10039,7 @@
       <c r="AC19" s="11"/>
       <c r="AD19" s="11"/>
       <c r="AE19" s="11"/>
+      <c r="AF19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -9736,11 +10054,11 @@
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+      <c r="M20" s="11" t="s">
+        <v>870</v>
+      </c>
       <c r="N20" s="11"/>
-      <c r="O20" s="11" t="s">
-        <v>835</v>
-      </c>
+      <c r="O20" s="11"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
@@ -9757,6 +10075,79 @@
       <c r="AC20" s="11"/>
       <c r="AD20" s="11"/>
       <c r="AE20" s="11"/>
+      <c r="AF20" s="11"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="11"/>
+      <c r="AD21" s="11"/>
+      <c r="AE21" s="11"/>
+      <c r="AF21" s="11"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="11"/>
+      <c r="AD22" s="11"/>
+      <c r="AE22" s="11"/>
+      <c r="AF22" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9778,36 +10169,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1045</v>
+        <v>1082</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1046</v>
+        <v>1083</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1047</v>
+        <v>1084</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>883</v>
+        <v>920</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1048</v>
+        <v>1085</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1049</v>
+        <v>1086</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1050</v>
+        <v>1087</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1051</v>
+        <v>1088</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1052</v>
+        <v>1089</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -9845,80 +10236,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1053</v>
+        <v>1090</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1054</v>
+        <v>1091</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>875</v>
+        <v>912</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1055</v>
+        <v>1092</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1056</v>
+        <v>1093</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1057</v>
+        <v>1094</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1058</v>
+        <v>1095</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1059</v>
+        <v>1096</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1060</v>
+        <v>1097</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1061</v>
+        <v>1098</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1062</v>
+        <v>1099</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1063</v>
+        <v>1100</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1064</v>
+        <v>1101</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1065</v>
+        <v>1102</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1066</v>
+        <v>1103</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>742</v>
+        <v>767</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1067</v>
+        <v>1104</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1068</v>
+        <v>1105</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>935</v>
+        <v>972</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1069</v>
+        <v>1106</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1070</v>
+        <v>1107</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1071</v>
+        <v>1108</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -9951,39 +10342,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1072</v>
+        <v>1109</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1073</v>
+        <v>1110</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1074</v>
+        <v>1111</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1075</v>
+        <v>1112</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1076</v>
+        <v>1113</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1077</v>
+        <v>1114</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1078</v>
+        <v>1115</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1079</v>
+        <v>1116</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1080</v>
+        <v>1117</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -10028,122 +10419,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1081</v>
+        <v>1118</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1082</v>
+        <v>1119</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1083</v>
+        <v>1120</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>839</v>
+        <v>876</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>845</v>
+        <v>882</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>846</v>
+        <v>883</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>918</v>
+        <v>955</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1084</v>
+        <v>1121</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1025</v>
+        <v>1062</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1085</v>
+        <v>1122</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1086</v>
+        <v>1123</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1087</v>
+        <v>1124</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1088</v>
+        <v>1125</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>1089</v>
+        <v>1126</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>1090</v>
+        <v>1127</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>1091</v>
+        <v>1128</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1092</v>
+        <v>1129</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1093</v>
+        <v>1130</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1094</v>
+        <v>1131</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1095</v>
+        <v>1132</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1096</v>
+        <v>1133</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1097</v>
+        <v>1134</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>864</v>
+        <v>901</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>866</v>
+        <v>903</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1098</v>
+        <v>1135</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1099</v>
+        <v>1136</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1100</v>
+        <v>1137</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1101</v>
+        <v>1138</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1102</v>
+        <v>1139</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1103</v>
+        <v>1140</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>714</v>
+        <v>738</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -10179,27 +10570,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1104</v>
+        <v>1141</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1105</v>
+        <v>1142</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1106</v>
+        <v>1143</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1107</v>
+        <v>1144</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1108</v>
+        <v>1145</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1109</v>
+        <v>1146</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -10230,48 +10621,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1110</v>
+        <v>1147</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1111</v>
+        <v>1148</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1112</v>
+        <v>1149</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1113</v>
+        <v>1150</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1114</v>
+        <v>1151</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1115</v>
+        <v>1152</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1116</v>
+        <v>1153</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1117</v>
+        <v>1154</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1118</v>
+        <v>1155</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1119</v>
+        <v>1156</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1120</v>
+        <v>1157</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>717</v>
+        <v>741</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10309,33 +10700,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1121</v>
+        <v>1158</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1122</v>
+        <v>1159</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1123</v>
+        <v>1160</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1124</v>
+        <v>1161</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1126</v>
+        <v>1163</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10363,30 +10754,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1127</v>
+        <v>1164</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1128</v>
+        <v>1165</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1129</v>
+        <v>1166</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1131</v>
+        <v>1168</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1132</v>
+        <v>1169</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1133</v>
+        <v>1170</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -10394,7 +10785,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="D2:D5000">
-      <formula1>Lists!$AA$2:$AA$8</formula1>
+      <formula1>Lists!$AA$2:$AA$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E2:E5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -10415,15 +10806,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1134</v>
+        <v>1171</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1135</v>
+        <v>1172</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -10449,21 +10840,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1134</v>
+        <v>1171</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1136</v>
+        <v>1173</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1137</v>
+        <v>1174</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1138</v>
+        <v>1175</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -10506,115 +10897,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>836</v>
+        <v>873</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>837</v>
+        <v>874</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>838</v>
+        <v>875</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>839</v>
+        <v>876</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>840</v>
+        <v>877</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>841</v>
+        <v>878</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>842</v>
+        <v>879</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>843</v>
+        <v>880</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>845</v>
+        <v>882</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>846</v>
+        <v>883</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>848</v>
+        <v>885</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>850</v>
+        <v>887</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>851</v>
+        <v>888</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>853</v>
+        <v>890</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>854</v>
+        <v>891</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>855</v>
+        <v>892</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>856</v>
+        <v>893</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>857</v>
+        <v>894</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>858</v>
+        <v>895</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>859</v>
+        <v>896</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>860</v>
+        <v>897</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>861</v>
+        <v>898</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>862</v>
+        <v>899</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>863</v>
+        <v>900</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>864</v>
+        <v>901</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>866</v>
+        <v>903</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>867</v>
+        <v>904</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -10642,33 +11033,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1136</v>
+        <v>1173</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1139</v>
+        <v>1176</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1141</v>
+        <v>1178</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1142</v>
+        <v>1179</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1143</v>
+        <v>1180</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1144</v>
+        <v>1181</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1145</v>
+        <v>1182</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10699,51 +11090,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1146</v>
+        <v>1183</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1147</v>
+        <v>1184</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1148</v>
+        <v>1185</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1149</v>
+        <v>1186</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1150</v>
+        <v>1187</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1151</v>
+        <v>1188</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1152</v>
+        <v>1189</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1153</v>
+        <v>1190</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1154</v>
+        <v>1191</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1138</v>
+        <v>1175</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1155</v>
+        <v>1192</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1156</v>
+        <v>1193</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1157</v>
+        <v>1194</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -10780,87 +11171,87 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1159</v>
+        <v>1196</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>839</v>
+        <v>876</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1160</v>
+        <v>1197</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1161</v>
+        <v>1198</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1162</v>
+        <v>1199</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1163</v>
+        <v>1200</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1164</v>
+        <v>1201</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1025</v>
+        <v>1062</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1027</v>
+        <v>1064</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>957</v>
+        <v>994</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1165</v>
+        <v>1202</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1166</v>
+        <v>1203</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1167</v>
+        <v>1204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1168</v>
+        <v>1205</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1169</v>
+        <v>1206</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1170</v>
+        <v>1207</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1171</v>
+        <v>1208</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1103</v>
+        <v>1140</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1172</v>
+        <v>1209</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1173</v>
+        <v>1210</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1174</v>
+        <v>1211</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1175</v>
+        <v>1212</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1176</v>
+        <v>1213</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -10892,54 +11283,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1177</v>
+        <v>1214</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1178</v>
+        <v>1215</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1179</v>
+        <v>1216</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1180</v>
+        <v>1217</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1181</v>
+        <v>1218</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1182</v>
+        <v>1219</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1183</v>
+        <v>1220</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1184</v>
+        <v>1221</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1185</v>
+        <v>1222</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1187</v>
+        <v>1224</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1188</v>
+        <v>1225</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1189</v>
+        <v>1226</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -10968,33 +11359,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1190</v>
+        <v>1227</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1191</v>
+        <v>1228</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1192</v>
+        <v>1229</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1194</v>
+        <v>1231</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1195</v>
+        <v>1232</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11023,39 +11414,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1073</v>
+        <v>1110</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1196</v>
+        <v>1233</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1197</v>
+        <v>1234</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1198</v>
+        <v>1235</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1199</v>
+        <v>1236</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>748</v>
+        <v>773</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1200</v>
+        <v>1237</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -11092,48 +11483,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1201</v>
+        <v>1238</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1202</v>
+        <v>1239</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1203</v>
+        <v>1240</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>886</v>
+        <v>923</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1204</v>
+        <v>1241</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1205</v>
+        <v>1242</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1206</v>
+        <v>1243</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1207</v>
+        <v>1244</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11169,75 +11560,75 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1208</v>
+        <v>1245</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1209</v>
+        <v>1246</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1025</v>
+        <v>1062</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>957</v>
+        <v>994</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1027</v>
+        <v>1064</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>839</v>
+        <v>876</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1210</v>
+        <v>1247</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1211</v>
+        <v>1248</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1212</v>
+        <v>1249</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1213</v>
+        <v>1250</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1214</v>
+        <v>1251</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1215</v>
+        <v>1252</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1216</v>
+        <v>1253</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1217</v>
+        <v>1254</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1218</v>
+        <v>1255</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1219</v>
+        <v>1256</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1220</v>
+        <v>1257</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1221</v>
+        <v>1258</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1222</v>
+        <v>1259</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -11252,6 +11643,178 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="17" style="11" customWidth="1"/>
+    <col min="3" max="3" width="18" style="11" customWidth="1"/>
+    <col min="4" max="4" width="33" style="11" customWidth="1"/>
+    <col min="5" max="5" width="16" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G2:G5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="14" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19" style="11" customWidth="1"/>
+    <col min="5" max="5" width="16" style="11" customWidth="1"/>
+    <col min="6" max="6" width="17" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="C2:C5000">
+      <formula1>Lists!$AD$2:$AD$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G2:G5000">
+      <formula1>Lists!$B$2:$B$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" style="11" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>909</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11269,65 +11832,65 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1223</v>
+        <v>1272</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1224</v>
+        <v>1273</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1225</v>
+        <v>1274</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1226</v>
+        <v>1275</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>983</v>
+        <v>1020</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>984</v>
+        <v>1021</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1227</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1228</v>
+        <v>1277</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1229</v>
+        <v>1278</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1230</v>
+        <v>1279</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1231</v>
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$14</formula1>
+      <formula1>Lists!$N$2:$N$17</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
-      <formula1>Lists!$O$2:$O$20</formula1>
+      <formula1>Lists!$O$2:$O$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="D2:D5000">
       <formula1>Lists!$H$2:$H$4</formula1>
@@ -11340,7 +11903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11365,70 +11928,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1232</v>
+        <v>1281</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1233</v>
+        <v>1282</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1234</v>
+        <v>1283</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1235</v>
+        <v>1284</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1236</v>
+        <v>1285</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1237</v>
+        <v>1286</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>673</v>
+        <v>696</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1238</v>
+        <v>1287</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1239</v>
+        <v>1288</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1240</v>
+        <v>1289</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>886</v>
+        <v>923</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1241</v>
+        <v>1290</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>984</v>
+        <v>1021</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1227</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1242</v>
+        <v>1291</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1243</v>
+        <v>1292</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>797</v>
+        <v>826</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>756</v>
+        <v>782</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1244</v>
+        <v>1266</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11437,10 +12000,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1230</v>
+        <v>1279</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -11464,44 +12027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="17" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14" style="11" customWidth="1"/>
-    <col min="3" max="3" width="17" style="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="20" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>868</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>871</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>872</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11519,55 +12045,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1232</v>
+        <v>1281</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1226</v>
+        <v>1275</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1241</v>
+        <v>1290</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>984</v>
+        <v>1021</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1227</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1245</v>
+        <v>1293</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1246</v>
+        <v>1294</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1246</v>
+        <v>1294</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1247</v>
+        <v>1295</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1230</v>
+        <v>1279</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -11581,7 +12107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11594,30 +12120,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1248</v>
+        <v>1296</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1249</v>
+        <v>1297</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1250</v>
+        <v>1298</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1227</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1251</v>
+        <v>1299</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>798</v>
+        <v>827</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1252</v>
+        <v>1300</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1253</v>
+        <v>1301</v>
       </c>
     </row>
   </sheetData>
@@ -11626,14 +12152,14 @@
       <formula1>Lists!$P$2:$P$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
-      <formula1>Lists!$M$2:$M$8</formula1>
+      <formula1>Lists!$M$2:$M$22</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11650,54 +12176,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1254</v>
+        <v>1302</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1255</v>
+        <v>1303</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1256</v>
+        <v>1304</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1257</v>
+        <v>1305</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1258</v>
+        <v>1306</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>674</v>
+        <v>697</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1259</v>
+        <v>1307</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1260</v>
+        <v>1308</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1261</v>
+        <v>1309</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1262</v>
+        <v>1310</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1263</v>
+        <v>1311</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1145</v>
+        <v>1182</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1264</v>
+        <v>1312</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -11713,7 +12239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11731,65 +12257,65 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1265</v>
+        <v>1313</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1266</v>
+        <v>1314</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1004</v>
+        <v>1041</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1018</v>
+        <v>1055</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>997</v>
+        <v>1034</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1267</v>
+        <v>1315</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1268</v>
+        <v>1316</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1269</v>
+        <v>1317</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>805</v>
+        <v>847</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1270</v>
+        <v>1318</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1271</v>
+        <v>1319</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1272</v>
+        <v>1320</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>751</v>
+        <v>777</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="A2:A5000">
-      <formula1>Lists!$AD$2:$AD$5</formula1>
+      <formula1>Lists!$AE$2:$AE$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F2:F5000">
-      <formula1>Lists!$AE$2:$AE$3</formula1>
+      <formula1>Lists!$AF$2:$AF$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="I2:I5000">
       <formula1>Lists!$A$2:$A$3</formula1>
@@ -11799,7 +12325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11816,56 +12342,56 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1273</v>
+        <v>1321</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1256</v>
+        <v>1304</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1274</v>
+        <v>1322</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1275</v>
+        <v>1323</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1259</v>
+        <v>1307</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>1276</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1228</v>
+        <v>1277</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>1277</v>
+        <v>1325</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1278</v>
+        <v>1326</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1279</v>
+        <v>1327</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1278</v>
+        <v>1326</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1280</v>
+        <v>1328</v>
       </c>
       <c r="H2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$14</formula1>
+      <formula1>Lists!$N$2:$N$17</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11886,33 +12412,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>873</v>
+        <v>910</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>874</v>
+        <v>911</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>875</v>
+        <v>912</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>876</v>
+        <v>913</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>877</v>
+        <v>914</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>878</v>
+        <v>915</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>879</v>
+        <v>916</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>880</v>
+        <v>917</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11942,43 +12468,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>881</v>
+        <v>918</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>882</v>
+        <v>919</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>883</v>
+        <v>920</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>884</v>
+        <v>921</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>886</v>
+        <v>923</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>887</v>
+        <v>924</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>888</v>
+        <v>925</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>889</v>
+        <v>926</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>890</v>
+        <v>927</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>891</v>
+        <v>928</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -12009,48 +12535,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>892</v>
+        <v>929</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>894</v>
+        <v>931</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>885</v>
+        <v>922</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>895</v>
+        <v>932</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>884</v>
+        <v>921</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>896</v>
+        <v>933</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>898</v>
+        <v>935</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>888</v>
+        <v>925</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>890</v>
+        <v>927</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12087,53 +12613,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>899</v>
+        <v>936</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>900</v>
+        <v>937</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>901</v>
+        <v>938</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>894</v>
+        <v>931</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>902</v>
+        <v>939</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>848</v>
+        <v>885</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>903</v>
+        <v>940</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>884</v>
+        <v>921</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>904</v>
+        <v>941</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>905</v>
+        <v>942</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>906</v>
+        <v>943</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>907</v>
+        <v>944</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>908</v>
+        <v>945</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -12166,33 +12692,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>909</v>
+        <v>946</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>910</v>
+        <v>947</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>848</v>
+        <v>885</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>664</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>912</v>
+        <v>949</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>913</v>
+        <v>950</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>914</v>
+        <v>951</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>915</v>
+        <v>952</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1333">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -73,10 +73,10 @@
     <t xml:space="preserve">Blank template: fill in the object sheets.</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master &gt; Go-Live Data Load (System Administrator). API: POST /api/data-load/batches (multipart field "file", field kit).</t>
+    <t xml:space="preserve">Upload with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API: POST /api/data-load/batches (multipart field "file", field kit), System Administrator; the go-live scripts (npm run rehearsal:golive) use it.</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover date</t>
@@ -514,10 +514,22 @@
     <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts</t>
   </si>
   <si>
-    <t xml:space="preserve">Application name, logo, colours, display currency, language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master &gt; System Settings</t>
+    <t xml:space="preserve">Application name, logo, colours (the brand pack of the deployment, BRAND_PACK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display currency, language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; System Settings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail layout, documents and reports layout, document signatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; E-mail Layout / Documents and Reports Layout / Document Signatures</t>
   </si>
   <si>
     <t xml:space="preserve">Company logo and letterhead images</t>
@@ -4230,7 +4242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B475"/>
+  <dimension ref="A1:B477"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4938,54 +4950,54 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B90" s="10"/>
+      <c r="B90" s="4" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>174</v>
-      </c>
+      <c r="A92" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92" s="10"/>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>181</v>
@@ -4993,10 +5005,10 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98">
@@ -5004,103 +5016,103 @@
         <v>184</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111">
@@ -5132,87 +5144,87 @@
         <v>205</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
     </row>
     <row r="125">
@@ -5220,455 +5232,455 @@
         <v>218</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>177</v>
+        <v>240</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>271</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>174</v>
+        <v>275</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>281</v>
+        <v>221</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>283</v>
+        <v>202</v>
       </c>
     </row>
     <row r="182">
@@ -5684,63 +5696,63 @@
         <v>286</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="191">
@@ -5764,103 +5776,103 @@
         <v>302</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>174</v>
+        <v>305</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>271</v>
+        <v>181</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>196</v>
+        <v>275</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>314</v>
+        <v>200</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>316</v>
+        <v>202</v>
       </c>
     </row>
     <row r="206">
@@ -5868,79 +5880,79 @@
         <v>317</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>174</v>
+        <v>318</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>174</v>
+        <v>320</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>320</v>
+        <v>178</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>177</v>
+        <v>324</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>325</v>
+        <v>181</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>330</v>
+        <v>178</v>
       </c>
     </row>
     <row r="216">
@@ -5956,23 +5968,23 @@
         <v>333</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>177</v>
+        <v>334</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>337</v>
+        <v>181</v>
       </c>
     </row>
     <row r="220">
@@ -6004,236 +6016,236 @@
         <v>344</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>174</v>
+        <v>345</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>174</v>
+        <v>347</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>348</v>
+        <v>178</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>177</v>
+        <v>352</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>359</v>
+        <v>181</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>174</v>
+        <v>363</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>367</v>
+        <v>181</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>177</v>
+        <v>371</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>316</v>
+        <v>181</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>177</v>
+        <v>320</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>181</v>
@@ -6241,18 +6253,18 @@
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>378</v>
+        <v>181</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>380</v>
+        <v>185</v>
       </c>
     </row>
     <row r="255">
@@ -6268,199 +6280,199 @@
         <v>383</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>198</v>
+        <v>384</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>174</v>
+        <v>386</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>394</v>
+        <v>178</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>177</v>
+        <v>398</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>404</v>
+        <v>181</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>174</v>
+        <v>408</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>409</v>
+        <v>178</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>411</v>
+        <v>178</v>
       </c>
     </row>
     <row r="281">
@@ -6468,143 +6480,143 @@
         <v>412</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>177</v>
+        <v>413</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>198</v>
+        <v>415</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>429</v>
+        <v>178</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>431</v>
+        <v>181</v>
       </c>
     </row>
     <row r="299">
@@ -6628,111 +6640,111 @@
         <v>436</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>177</v>
+        <v>437</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>316</v>
+        <v>439</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>439</v>
+        <v>181</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>198</v>
+        <v>320</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>174</v>
+        <v>443</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>450</v>
+        <v>178</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>452</v>
+        <v>178</v>
       </c>
     </row>
     <row r="315">
@@ -6748,287 +6760,287 @@
         <v>455</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>198</v>
+        <v>456</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>174</v>
+        <v>458</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>460</v>
+        <v>178</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>174</v>
+        <v>464</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>466</v>
+        <v>178</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>174</v>
+        <v>470</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>471</v>
+        <v>178</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>198</v>
+        <v>475</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>475</v>
+        <v>178</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>177</v>
+        <v>479</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>271</v>
+        <v>178</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>198</v>
+        <v>275</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>494</v>
+        <v>181</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>496</v>
+        <v>200</v>
       </c>
     </row>
     <row r="352">
@@ -7044,79 +7056,79 @@
         <v>499</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>177</v>
+        <v>500</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>181</v>
+        <v>502</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>508</v>
+        <v>178</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>510</v>
+        <v>178</v>
       </c>
     </row>
     <row r="363">
@@ -7148,39 +7160,39 @@
         <v>517</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>177</v>
+        <v>518</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>198</v>
+        <v>520</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>521</v>
+        <v>202</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>523</v>
+        <v>178</v>
       </c>
     </row>
     <row r="371">
@@ -7188,47 +7200,47 @@
         <v>524</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>177</v>
+        <v>525</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>198</v>
+        <v>527</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>529</v>
+        <v>178</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>531</v>
+        <v>178</v>
       </c>
     </row>
     <row r="377">
@@ -7236,39 +7248,39 @@
         <v>532</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>177</v>
+        <v>533</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>198</v>
+        <v>535</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>536</v>
+        <v>202</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>538</v>
+        <v>178</v>
       </c>
     </row>
     <row r="382">
@@ -7276,92 +7288,92 @@
         <v>539</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>174</v>
+        <v>540</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>177</v>
+        <v>545</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B393" s="4" t="s">
         <v>181</v>
@@ -7369,26 +7381,26 @@
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>554</v>
+        <v>185</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>556</v>
+        <v>181</v>
       </c>
     </row>
     <row r="397">
@@ -7404,39 +7416,39 @@
         <v>559</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>174</v>
+        <v>562</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>563</v>
+        <v>178</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>565</v>
+        <v>178</v>
       </c>
     </row>
     <row r="403">
@@ -7452,47 +7464,47 @@
         <v>568</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>177</v>
+        <v>569</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>198</v>
+        <v>571</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>573</v>
+        <v>178</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>575</v>
+        <v>178</v>
       </c>
     </row>
     <row r="410">
@@ -7500,39 +7512,39 @@
         <v>576</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>217</v>
+        <v>577</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>177</v>
+        <v>579</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>580</v>
+        <v>181</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>582</v>
+        <v>202</v>
       </c>
     </row>
     <row r="415">
@@ -7564,23 +7576,23 @@
         <v>589</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>314</v>
+        <v>590</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>593</v>
+        <v>318</v>
       </c>
     </row>
     <row r="421">
@@ -7588,23 +7600,23 @@
         <v>594</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>285</v>
+        <v>595</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>598</v>
+        <v>289</v>
       </c>
     </row>
     <row r="424">
@@ -7676,63 +7688,63 @@
         <v>615</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>285</v>
+        <v>616</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>285</v>
+        <v>618</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>593</v>
+        <v>289</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>285</v>
+        <v>597</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>622</v>
+        <v>289</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>624</v>
+        <v>289</v>
       </c>
     </row>
     <row r="440">
@@ -7764,47 +7776,47 @@
         <v>631</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>285</v>
+        <v>632</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>285</v>
+        <v>634</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>636</v>
+        <v>343</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>638</v>
+        <v>289</v>
       </c>
     </row>
     <row r="449">
@@ -7820,39 +7832,39 @@
         <v>641</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>285</v>
+        <v>642</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>648</v>
+        <v>289</v>
       </c>
     </row>
     <row r="455">
@@ -7884,23 +7896,23 @@
         <v>655</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>339</v>
+        <v>656</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>659</v>
+        <v>343</v>
       </c>
     </row>
     <row r="461">
@@ -7924,55 +7936,55 @@
         <v>664</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>598</v>
+        <v>665</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>285</v>
+        <v>602</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>593</v>
+        <v>289</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>674</v>
+        <v>597</v>
       </c>
     </row>
     <row r="470">
@@ -8020,7 +8032,23 @@
         <v>685</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>285</v>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -8051,82 +8079,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -8155,33 +8183,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8209,33 +8237,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8265,45 +8293,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -8339,74 +8367,74 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -8442,69 +8470,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8535,51 +8563,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -8613,67 +8641,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="G2" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>718</v>
-      </c>
       <c r="J2" s="9" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8726,87 +8754,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -8851,117 +8879,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="L2" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>1077</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>1079</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>1080</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>1073</v>
-      </c>
       <c r="Q2" s="9" t="s">
+        <v>1085</v>
+      </c>
+      <c r="R2" s="9" t="s">
         <v>1081</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>1077</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -9019,373 +9047,373 @@
   <sheetData>
     <row r="1" spans="1:32" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="M2" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>734</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>735</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>737</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="Z2" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>730</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>731</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>733</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>735</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>736</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>737</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>738</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>739</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>740</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>741</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>725</v>
-      </c>
       <c r="AA2" s="11" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="M3" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>766</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>769</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>772</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>759</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>760</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>761</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>762</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>763</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>764</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>765</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>766</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>767</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>768</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>769</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>770</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>771</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>755</v>
-      </c>
       <c r="AA3" s="11" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="AF3" s="11" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="AF4" s="11"/>
     </row>
@@ -9393,46 +9421,46 @@
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -9441,17 +9469,17 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="AF5" s="11"/>
     </row>
@@ -9459,37 +9487,37 @@
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -9499,12 +9527,12 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AE6" s="11"/>
       <c r="AF6" s="11"/>
@@ -9514,29 +9542,29 @@
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -9549,12 +9577,12 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
       <c r="AD7" s="11" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AE7" s="11"/>
       <c r="AF7" s="11"/>
@@ -9564,7 +9592,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -9575,16 +9603,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -9597,7 +9625,7 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
@@ -9610,7 +9638,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -9621,16 +9649,16 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -9643,7 +9671,7 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
@@ -9656,7 +9684,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -9667,14 +9695,14 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -9698,7 +9726,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -9709,14 +9737,14 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -9740,7 +9768,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -9751,14 +9779,14 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="11" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -9791,14 +9819,14 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -9831,10 +9859,10 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
@@ -9869,10 +9897,10 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
@@ -9907,10 +9935,10 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
@@ -9945,10 +9973,10 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
@@ -9983,7 +10011,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
@@ -10019,7 +10047,7 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
@@ -10055,7 +10083,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
@@ -10091,7 +10119,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
@@ -10127,7 +10155,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
@@ -10169,36 +10197,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -10236,80 +10264,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -10342,39 +10370,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -10419,122 +10447,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -10570,27 +10598,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -10621,48 +10649,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10700,33 +10728,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10754,30 +10782,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -10806,15 +10834,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -10840,21 +10868,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -10897,115 +10925,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -11033,33 +11061,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11090,51 +11118,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -11171,87 +11199,87 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -11283,54 +11311,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -11359,33 +11387,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11414,39 +11442,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -11483,48 +11511,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11560,75 +11588,75 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -11658,42 +11686,42 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -11724,42 +11752,42 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -11789,24 +11817,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -11832,56 +11860,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
     </row>
   </sheetData>
@@ -11928,70 +11956,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12000,10 +12028,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -12045,55 +12073,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -12120,30 +12148,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>
@@ -12176,54 +12204,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -12257,56 +12285,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -12342,49 +12370,49 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -12412,33 +12440,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -12468,43 +12496,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -12535,48 +12563,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12613,53 +12641,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -12692,33 +12720,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -51,12 +51,13 @@
     <sheet name="Numbering" sheetId="44" r:id="rId44"/>
     <sheet name="Payee Bank Accounts" sheetId="45" r:id="rId45"/>
     <sheet name="COC Series" sheetId="46" r:id="rId46"/>
+    <sheet name="Control" sheetId="47" state="hidden" r:id="rId47"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="1333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="1363">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -73,16 +74,16 @@
     <t xml:space="preserve">Blank template: fill in the object sheets.</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API: POST /api/data-load/batches (multipart field "file", field kit), System Administrator; the go-live scripts (npm run rehearsal:golive) use it.</t>
+    <t xml:space="preserve">Upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; Data Migration &amp; Go-Live &gt; Loads: upload, review the result of each row, then submit the load for approval.</t>
   </si>
   <si>
     <t xml:space="preserve">Cutover date</t>
   </si>
   <si>
-    <t xml:space="preserve">Not set yet: golive.cutover_date (Settings sheet of the configuration workbook, or Master &gt; Configuration)</t>
+    <t xml:space="preserve">Not set yet: set it on Data Migration &amp; Go-Live &gt; Go-Live before the migration workbook is validated.</t>
   </si>
   <si>
     <t xml:space="preserve">How to fill in</t>
@@ -109,7 +110,7 @@
     <t xml:space="preserve">Formats</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates as YYYY-MM-DD; amounts as plain numbers (no currency sign); rates as fractions where the column says so (0.20 for 20%). The sheets are formatted as text so Excel keeps codes and dates as typed.</t>
+    <t xml:space="preserve">Dates as YYYY-MM-DD; amounts as plain numbers (no currency sign) with at most two decimals; rates as fractions where the column says so (0.20 for 20%). The sheets are formatted as text so Excel keeps codes and dates as typed.</t>
   </si>
   <si>
     <t xml:space="preserve">Keys</t>
@@ -118,6 +119,18 @@
     <t xml:space="preserve">Every row is matched on its natural key (code, username, setting key, legacy number ...): a row whose key exists updates that record, a new key creates one. Loading the same or a corrected workbook again never duplicates; unchanged rows are skipped.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hidden values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cell shown masked (with **) keeps the value stored in BrokerVerse; a masked TIN, birth date or key is refused: enter the full value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The hidden Control sheet identifies this file (kit, sheets, layout). Do not remove it; a file of another kit or of an older layout is refused: download the template again.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Load order</t>
   </si>
   <si>
@@ -130,7 +143,7 @@
     <t xml:space="preserve">2. Settings</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Configuration. Key: Setting Key</t>
+    <t xml:space="preserve">Master &gt; Configuration. Key: Setting Key. After: Company</t>
   </si>
   <si>
     <t xml:space="preserve">3. Countries</t>
@@ -142,37 +155,37 @@
     <t xml:space="preserve">4. Regions</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Province (regions are shown with their provinces; no Region screen of its own). Key: Country + Region Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Province (regions are shown with their provinces; no Region screen of its own). Key: Country + Region Code. After: Countries</t>
   </si>
   <si>
     <t xml:space="preserve">5. Provinces</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Province. Key: Country + Province Name</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; Province. Key: Country + Province Name. After: Regions</t>
   </si>
   <si>
     <t xml:space="preserve">6. Cities and Municipalities</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City / Municipality. Key: Province + City / Municipality Name</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City / Municipality. Key: Province + City / Municipality Name. After: Provinces</t>
   </si>
   <si>
     <t xml:space="preserve">7. Barangays</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City / Municipality (barangays are picked on the address forms; no Barangay screen of its own). Key: City / Municipality + Barangay Name</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Location &gt; City / Municipality (barangays are picked on the address forms; no Barangay screen of its own). Key: City / Municipality + Barangay Name. After: Cities and Municipalities</t>
   </si>
   <si>
     <t xml:space="preserve">8. Branches</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Organization &gt; Branch. Key: Branch Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Organization &gt; Branch. Key: Branch Code. After: Company, Cities and Municipalities</t>
   </si>
   <si>
     <t xml:space="preserve">9. Departments</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Department (opened from Master &gt; Generals &gt; Organization &gt; Branch). Key: Department Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Department (opened from Master &gt; Generals &gt; Organization &gt; Branch). Key: Department Code. After: Branches</t>
   </si>
   <si>
     <t xml:space="preserve">10. Hierarchy</t>
@@ -184,13 +197,13 @@
     <t xml:space="preserve">11. Designations</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Employee Management &gt; Designation. Key: Designation Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Employee Management &gt; Designation. Key: Designation Code. After: Hierarchy</t>
   </si>
   <si>
     <t xml:space="preserve">12. Users</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; User. Key: Username</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; User. Key: Username. After: Branches, Departments, Designations</t>
   </si>
   <si>
     <t xml:space="preserve">13. Currencies</t>
@@ -202,13 +215,13 @@
     <t xml:space="preserve">14. Exchange Rates</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Exchange Rate. Key: Currency Code + To Currency Code + Effective From</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Exchange Rate. Key: Currency Code + To Currency Code + Effective From. After: Currencies</t>
   </si>
   <si>
     <t xml:space="preserve">15. Chart of Accounts</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Main Account / Sub Account. Key: Account Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Main Account / Sub Account. Key: Account Code. After: Currencies</t>
   </si>
   <si>
     <t xml:space="preserve">16. Banks</t>
@@ -220,31 +233,31 @@
     <t xml:space="preserve">17. Bank Accounts</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Bank (choose Bank accounts in the Upload dialog). Key: Account Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Bank (choose Bank accounts in the Upload dialog). Key: Account Code. After: Banks, Currencies, Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">18. Signatories</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Signatories. Key: Signatory Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Signatories. Key: Signatory Code. After: Users</t>
   </si>
   <si>
     <t xml:space="preserve">19. Transaction Codes</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Transaction Code. Key: Transaction Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Transaction Code. Key: Transaction Code. After: Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">20. Write-off Reasons</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Account Determination (write-off reasons). Key: Reason Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Account Determination (write-off reasons). Key: Reason Code. After: Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">21. Insurers</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Insurance Company. Key: Insurance Company Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Insurance Company. Key: Insurance Company Code. After: Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">22. Lines of Business</t>
@@ -256,19 +269,19 @@
     <t xml:space="preserve">23. Products</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Product. Key: Product Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Product. Key: Product Code. After: Lines of Business, Insurers</t>
   </si>
   <si>
     <t xml:space="preserve">24. Policy Types</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Product (policy types). Key: Policy Type Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Product (policy types). Key: Policy Type Code. After: Products</t>
   </si>
   <si>
     <t xml:space="preserve">25. Covers</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Cover. Key: Cover Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Cover. Key: Cover Code. After: Products</t>
   </si>
   <si>
     <t xml:space="preserve">26. Vehicle Brands</t>
@@ -280,19 +293,19 @@
     <t xml:space="preserve">27. Vehicle Models</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle models in the Upload dialog). Key: Brand + Model</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle models in the Upload dialog). Key: Brand + Model. After: Vehicle Brands</t>
   </si>
   <si>
     <t xml:space="preserve">28. Vehicle Variants</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle variants in the Upload dialog). Key: Model + Variant</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle (choose Vehicle variants in the Upload dialog). Key: Model + Variant. After: Vehicle Models</t>
   </si>
   <si>
     <t xml:space="preserve">29. Vehicles</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle. Key: Vehicle Code</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; Insurance Management &gt; Vehicle. Key: Vehicle Code. After: Vehicle Variants</t>
   </si>
   <si>
     <t xml:space="preserve">30. Suppliers</t>
@@ -304,7 +317,7 @@
     <t xml:space="preserve">31. Asset Classes</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Asset Classes. Key: Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Asset Classes. Key: Code. After: Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">32. Short-Period Rates</t>
@@ -322,7 +335,7 @@
     <t xml:space="preserve">34. Claim Document Checklist</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Insurance Management &gt; Claim Document Checklist. Key: Code</t>
+    <t xml:space="preserve">Master &gt; Insurance Management &gt; Claim Document Checklist. Key: Code. After: Products</t>
   </si>
   <si>
     <t xml:space="preserve">35. Repair Shops</t>
@@ -346,46 +359,46 @@
     <t xml:space="preserve">38. Commission Rates</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Commission Rate Matrix. Key: Insurer + Product + Line of Business + Policy Type + Effective From</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Commission Rate Matrix. Key: Insurer + Product + Line of Business + Policy Type + Effective From. After: Insurers, Products</t>
   </si>
   <si>
     <t xml:space="preserve">39. Premium Taxes</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (Taxes &amp; Charges). Key: Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (Taxes &amp; Charges). Key: Code. After: Products, Chart of Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">40. LGU Rates</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (LGU Tax Rates). Key: Code</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates (LGU Tax Rates). Key: Code. After: Cities and Municipalities</t>
   </si>
   <si>
     <t xml:space="preserve">41. Authority Limits</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; Authority Matrix. Key: Transaction Type + Role</t>
+    <t xml:space="preserve">Master &gt; Generals &gt; User Management &gt; Authority Matrix. Key: Transaction Type + Role. After: Users</t>
   </si>
   <si>
     <t xml:space="preserve">42. Numbering</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code</t>
+    <t xml:space="preserve">Master &gt; Configuration &gt; Document Numbering. Key: Series Code. After: Branches</t>
   </si>
   <si>
     <t xml:space="preserve">43. Payee Bank Accounts</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts (Payee bank accounts). Key: Payee Type + Payee + Account Number</t>
+    <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts (Payee bank accounts). Key: Payee Type + Payee + Account Number. After: Banks, Insurers, Suppliers</t>
   </si>
   <si>
     <t xml:space="preserve">44. COC Series</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validate, fix and load</t>
+    <t xml:space="preserve">Operations &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From. After: Insurers, Branches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate, review and load</t>
   </si>
   <si>
     <t xml:space="preserve">1. Upload and validate</t>
@@ -394,22 +407,28 @@
     <t xml:space="preserve">The upload validates without saving: every sheet runs through its importer in the load order above inside one database transaction that is rolled back, so a row may refer to a record of an earlier sheet of the same workbook (e.g. a policy to a client and an insurer).</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rows read, valid and with errors per sheet; each error with its sheet, row number, column and message.</t>
+    <t xml:space="preserve">2. Result of each row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New: the key is not in BrokerVerse, the row creates a record. Changed: the key is stored with other values; the review shows each changed column, old -&gt; new. Unchanged: equal to the stored record, nothing to load. Duplicate: the row would create a record that matches another record (below); it loads only once resolved. Error: a check failed (column and message).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Fix</t>
   </si>
   <si>
-    <t xml:space="preserve">Download errors: a workbook in this layout with only the rows in error and an Errors column. Correct those rows and upload that file (or the whole corrected workbook) again.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Load runs when the latest validation has no error (or with "load valid rows only"). Everything is loaded in one transaction, recorded in the history and the audit trail.</t>
+    <t xml:space="preserve">Download errors: a workbook in this layout with the rows in error and the unresolved duplicates and an Errors column. Correct those rows and upload that file (or the whole corrected workbook) again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Duplicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve each duplicate on the review: Load as new (a reason is kept), Use existing (the row creates nothing and the legacy value is mapped to the existing record for every later load), or, for a policy number of another insurer, Load with insurer suffix (number/INSURER CODE). Or fix the file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load runs when the latest validation has no error and no unresolved duplicate. Everything is loaded in one transaction, recorded in the load history and in the history of each record.</t>
   </si>
   <si>
     <t xml:space="preserve">Rules</t>
@@ -436,7 +455,13 @@
     <t xml:space="preserve">Settings</t>
   </si>
   <si>
-    <t xml:space="preserve">Only settings of Master &gt; Configuration are loaded; settings of another screen (System Settings, Company, Premium Taxes, Account Determination) are changed there. golive.locked is switched on in Master &gt; Configuration, not by a workbook.</t>
+    <t xml:space="preserve">Only settings of Master &gt; Configuration are loaded; settings of another screen (the brand pack, Company, Premium Taxes, Account Determination, the go-live lock) are changed there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A new master record whose name equals another record of the same master once punctuation and words such as Inc, Corp or Company are set aside is a Duplicate.</t>
   </si>
   <si>
     <t xml:space="preserve">Promotion</t>
@@ -514,7 +539,7 @@
     <t xml:space="preserve">Master &gt; Finance &gt; Bank File Layouts</t>
   </si>
   <si>
-    <t xml:space="preserve">Application name, logo, colours (the brand pack of the deployment, BRAND_PACK)</t>
+    <t xml:space="preserve">Application name, logo, favicon, colours (the brand pack of the deployment, BRAND_PACK, applied again at every start)</t>
   </si>
   <si>
     <t xml:space="preserve">Deployment configuration</t>
@@ -523,7 +548,7 @@
     <t xml:space="preserve">Display currency, language</t>
   </si>
   <si>
-    <t xml:space="preserve">Master &gt; System Configuration &gt; System Settings</t>
+    <t xml:space="preserve">Master &gt; System Configuration &gt; Configuration (Company &amp; Branding)</t>
   </si>
   <si>
     <t xml:space="preserve">E-mail layout, documents and reports layout, document signatures</t>
@@ -1684,7 +1709,7 @@
     <t xml:space="preserve">Claim Document Checklist: Claim Type (* = all)</t>
   </si>
   <si>
-    <t xml:space="preserve">Required. Claim type as on the claim (Own Damage, Theft, Third Party ...) or * for every type</t>
+    <t xml:space="preserve">Required. Claim type or cause of loss as on the claim, or words of the cause of loss (Theft, Third Party, Collision ...; several separated by ;) or * for every claim</t>
   </si>
   <si>
     <t xml:space="preserve">Claim Document Checklist: Document</t>
@@ -2260,7 +2285,7 @@
     <t xml:space="preserve">system-admin</t>
   </si>
   <si>
-    <t xml:space="preserve">APEX</t>
+    <t xml:space="preserve">AXA</t>
   </si>
   <si>
     <t xml:space="preserve">CL-COMP</t>
@@ -2350,7 +2375,7 @@
     <t xml:space="preserve">sales</t>
   </si>
   <si>
-    <t xml:space="preserve">AXA</t>
+    <t xml:space="preserve">FPG</t>
   </si>
   <si>
     <t xml:space="preserve">CL-VOL</t>
@@ -2425,7 +2450,7 @@
     <t xml:space="preserve">processing</t>
   </si>
   <si>
-    <t xml:space="preserve">EVERSAFE</t>
+    <t xml:space="preserve">MAAGAP</t>
   </si>
   <si>
     <t xml:space="preserve">CTPL</t>
@@ -2485,7 +2510,7 @@
     <t xml:space="preserve">operations</t>
   </si>
   <si>
-    <t xml:space="preserve">FPG</t>
+    <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
     <t xml:space="preserve">GPA</t>
@@ -2527,7 +2552,7 @@
     <t xml:space="preserve">claims</t>
   </si>
   <si>
-    <t xml:space="preserve">GOLDENHORIZON</t>
+    <t xml:space="preserve">MAPFRE</t>
   </si>
   <si>
     <t xml:space="preserve">MOTOR</t>
@@ -2554,7 +2579,7 @@
     <t xml:space="preserve">accounting</t>
   </si>
   <si>
-    <t xml:space="preserve">INTEGRITY</t>
+    <t xml:space="preserve">MERCANTILE</t>
   </si>
   <si>
     <t xml:space="preserve">PA</t>
@@ -2575,7 +2600,7 @@
     <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
-    <t xml:space="preserve">LIBERTYSHIELD</t>
+    <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
     <t xml:space="preserve">PARCEL</t>
@@ -2587,13 +2612,16 @@
     <t xml:space="preserve">eb</t>
   </si>
   <si>
+    <t xml:space="preserve">reassignment</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cost of Services</t>
   </si>
   <si>
     <t xml:space="preserve">tis-sales-associate</t>
   </si>
   <si>
-    <t xml:space="preserve">MAAGAP</t>
+    <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
     <t xml:space="preserve">TRAVEL</t>
@@ -2605,90 +2633,117 @@
     <t xml:space="preserve">life</t>
   </si>
   <si>
+    <t xml:space="preserve">period_close</t>
+  </si>
+  <si>
     <t xml:space="preserve">Operating Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">tis-sales-officer</t>
   </si>
   <si>
-    <t xml:space="preserve">MALAYAN</t>
+    <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
     <t xml:space="preserve">petty_cash</t>
   </si>
   <si>
+    <t xml:space="preserve">period_reopen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Other Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">tis-sales-unit-head</t>
   </si>
   <si>
-    <t xml:space="preserve">MAPFRE</t>
-  </si>
-  <si>
     <t xml:space="preserve">remittance</t>
   </si>
   <si>
+    <t xml:space="preserve">year_end_reverse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Income Tax</t>
   </si>
   <si>
     <t xml:space="preserve">tis-ops-associate</t>
   </si>
   <si>
-    <t xml:space="preserve">MERCANTILE</t>
-  </si>
-  <si>
     <t xml:space="preserve">remittance_settlement</t>
   </si>
   <si>
+    <t xml:space="preserve">cas_print_void</t>
+  </si>
+  <si>
     <t xml:space="preserve">tis-ops-officer</t>
   </si>
   <si>
-    <t xml:space="preserve">PIONEER</t>
-  </si>
-  <si>
     <t xml:space="preserve">underwriting_referral</t>
   </si>
   <si>
+    <t xml:space="preserve">cas_document_change</t>
+  </si>
+  <si>
     <t xml:space="preserve">tis-ops-unit-head</t>
   </si>
   <si>
-    <t xml:space="preserve">SECUREGUARD</t>
+    <t xml:space="preserve">incentive_batch_reject</t>
   </si>
   <si>
     <t xml:space="preserve">tis-ccd-pdu</t>
   </si>
   <si>
-    <t xml:space="preserve">SENTINEL</t>
+    <t xml:space="preserve">incentive_adjustment</t>
   </si>
   <si>
     <t xml:space="preserve">tis-ccd-pdc</t>
   </si>
   <si>
-    <t xml:space="preserve">STANDARD</t>
+    <t xml:space="preserve">year_end_cancel</t>
   </si>
   <si>
     <t xml:space="preserve">tis-ccd-bp</t>
   </si>
   <si>
-    <t xml:space="preserve">STRONGHOLD</t>
+    <t xml:space="preserve">sales_invoice_cancel</t>
   </si>
   <si>
     <t xml:space="preserve">tis-ccd-recon</t>
   </si>
   <si>
+    <t xml:space="preserve">invoice_payment_cancel</t>
+  </si>
+  <si>
     <t xml:space="preserve">tis-finance</t>
   </si>
   <si>
+    <t xml:space="preserve">delegation</t>
+  </si>
+  <si>
     <t xml:space="preserve">tis-it-admin</t>
   </si>
   <si>
+    <t xml:space="preserve">delegation_end</t>
+  </si>
+  <si>
     <t xml:space="preserve">tis-general-manager</t>
   </si>
   <si>
+    <t xml:space="preserve">sod_exception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tis-auditor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">access_review</t>
+  </si>
+  <si>
     <t xml:space="preserve">tis-superid</t>
   </si>
   <si>
+    <t xml:space="preserve">access_change</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company Code *</t>
   </si>
   <si>
@@ -4055,6 +4110,42 @@
   </si>
   <si>
     <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">master:company,settings,master:country,master:region,master:state,master:city,master:barangay,master:branch,master:department,master:hierarchy,master:designation,users,master:currency,master:exchange-rate,chart-of-accounts,master:bank,master:bank-account,master:signatory,master:transaction-code,master:write-off-reason,master:insurance-company,master:line-of-business,master:product,master:policy-type,master:cover,master:vehicle-brand,master:vehicle-model,master:vehicle-variant,master:vehicle,master:supplier,master:asset-class,master:short-period-rate,master:cancellation-reason,master:claim-document-requirement,master:repair-shop,master:lead-source,master:reason-code,commission-rates,premium-charges,lgu-rates,authority-limits,numbering,payee-bank-accounts,coc-series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2da9ec6b2b6ec7c9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10T07:27:21.775Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated by</t>
   </si>
 </sst>
 </file>
@@ -4062,7 +4153,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -4242,7 +4333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B477"/>
+  <dimension ref="A1:B481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4334,26 +4425,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="10"/>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="B14" s="10"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -4692,26 +4783,26 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="B57" s="10"/>
+      <c r="B57" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="B59" s="4" t="s">
+      <c r="A59" s="10" t="s">
         <v>113</v>
       </c>
+      <c r="B59" s="10"/>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
@@ -4730,34 +4821,34 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="10"/>
+      <c r="B62" s="4" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="B65" s="4" t="s">
+      <c r="A65" s="10" t="s">
         <v>124</v>
       </c>
+      <c r="B65" s="10"/>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
@@ -4776,42 +4867,42 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="10"/>
+      <c r="B68" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="B72" s="4" t="s">
+      <c r="A72" s="10" t="s">
         <v>137</v>
       </c>
+      <c r="B72" s="10"/>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
@@ -4966,185 +5057,185 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="B92" s="10"/>
+      <c r="B92" s="4" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="0" t="s">
-        <v>182</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>181</v>
-      </c>
+      <c r="A96" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B96" s="10"/>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115">
@@ -5160,631 +5251,631 @@
         <v>209</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>230</v>
+        <v>186</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>181</v>
+        <v>245</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>181</v>
+        <v>235</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>181</v>
+        <v>283</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>285</v>
+        <v>186</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>287</v>
+        <v>229</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>289</v>
+        <v>210</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="195">
@@ -5792,231 +5883,231 @@
         <v>306</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>178</v>
+        <v>307</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>178</v>
+        <v>309</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>178</v>
+        <v>311</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>178</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>181</v>
+        <v>328</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>334</v>
+        <v>210</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>345</v>
+        <v>189</v>
       </c>
     </row>
     <row r="224">
@@ -6032,623 +6123,623 @@
         <v>348</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>178</v>
+        <v>349</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>178</v>
+        <v>351</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>178</v>
+        <v>353</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>178</v>
+        <v>360</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>363</v>
+        <v>186</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>178</v>
+        <v>263</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>178</v>
+        <v>371</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>371</v>
+        <v>186</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>181</v>
+        <v>379</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>382</v>
+        <v>328</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>384</v>
+        <v>189</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>386</v>
+        <v>189</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>178</v>
+        <v>390</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>178</v>
+        <v>392</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>178</v>
+        <v>394</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>398</v>
+        <v>210</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>181</v>
+        <v>406</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>408</v>
+        <v>189</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>415</v>
+        <v>210</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>178</v>
+        <v>421</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>178</v>
+        <v>423</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>433</v>
+        <v>186</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>435</v>
+        <v>263</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>437</v>
+        <v>186</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>439</v>
+        <v>189</v>
       </c>
     </row>
     <row r="303">
@@ -6656,511 +6747,511 @@
         <v>440</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>181</v>
+        <v>441</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>320</v>
+        <v>443</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>202</v>
+        <v>447</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>178</v>
+        <v>328</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>178</v>
+        <v>451</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>454</v>
+        <v>186</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>456</v>
+        <v>186</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>458</v>
+        <v>186</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>178</v>
+        <v>462</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>178</v>
+        <v>464</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>181</v>
+        <v>466</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>464</v>
+        <v>210</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>178</v>
+        <v>472</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>470</v>
+        <v>210</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>479</v>
+        <v>210</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>178</v>
+        <v>483</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>202</v>
+        <v>487</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>178</v>
+        <v>283</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>498</v>
+        <v>186</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>500</v>
+        <v>189</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>502</v>
+        <v>189</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>185</v>
+        <v>506</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>181</v>
+        <v>508</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>181</v>
+        <v>510</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>512</v>
+        <v>189</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>514</v>
+        <v>210</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>516</v>
+        <v>186</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>518</v>
+        <v>186</v>
       </c>
     </row>
     <row r="367">
@@ -7176,407 +7267,407 @@
         <v>521</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>181</v>
+        <v>522</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>202</v>
+        <v>524</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>178</v>
+        <v>526</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>527</v>
+        <v>189</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>178</v>
+        <v>533</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>178</v>
+        <v>535</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>533</v>
+        <v>189</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>535</v>
+        <v>210</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>178</v>
+        <v>541</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>542</v>
+        <v>189</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>545</v>
+        <v>186</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>221</v>
+        <v>548</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>181</v>
+        <v>550</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>178</v>
+        <v>553</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>558</v>
+        <v>189</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>560</v>
+        <v>189</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>562</v>
+        <v>193</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>178</v>
+        <v>566</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>178</v>
+        <v>568</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>569</v>
+        <v>210</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>571</v>
+        <v>186</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>202</v>
+        <v>575</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>178</v>
+        <v>577</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>178</v>
+        <v>579</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="0" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>577</v>
+        <v>189</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>579</v>
+        <v>210</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>202</v>
+        <v>585</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="0" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>586</v>
+        <v>229</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>588</v>
+        <v>189</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>590</v>
+        <v>210</v>
       </c>
     </row>
     <row r="419">
@@ -7592,63 +7683,63 @@
         <v>593</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>318</v>
+        <v>594</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>289</v>
+        <v>600</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>600</v>
+        <v>326</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>606</v>
+        <v>297</v>
       </c>
     </row>
     <row r="428">
@@ -7704,79 +7795,79 @@
         <v>619</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>289</v>
+        <v>620</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>289</v>
+        <v>622</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>289</v>
+        <v>626</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>628</v>
+        <v>297</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>630</v>
+        <v>297</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>632</v>
+        <v>297</v>
       </c>
     </row>
     <row r="444">
@@ -7792,111 +7883,111 @@
         <v>635</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>289</v>
+        <v>636</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>289</v>
+        <v>638</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>343</v>
+        <v>640</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>289</v>
+        <v>642</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>640</v>
+        <v>297</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>642</v>
+        <v>297</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>644</v>
+        <v>351</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>289</v>
+        <v>650</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>652</v>
+        <v>297</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>656</v>
+        <v>297</v>
       </c>
     </row>
     <row r="459">
@@ -7912,39 +8003,39 @@
         <v>659</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>343</v>
+        <v>660</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>667</v>
+        <v>351</v>
       </c>
     </row>
     <row r="465">
@@ -7952,71 +8043,71 @@
         <v>668</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>602</v>
+        <v>669</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>289</v>
+        <v>673</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>597</v>
+        <v>610</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>678</v>
+        <v>297</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>682</v>
+        <v>605</v>
       </c>
     </row>
     <row r="474">
@@ -8048,7 +8139,39 @@
         <v>689</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>289</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0" t="s">
+        <v>691</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0" t="s">
+        <v>693</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0" t="s">
+        <v>695</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -8079,82 +8202,82 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>958</v>
+        <v>976</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>878</v>
+        <v>896</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>960</v>
+        <v>978</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>961</v>
+        <v>979</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>962</v>
+        <v>980</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>963</v>
+        <v>981</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>964</v>
+        <v>982</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>965</v>
+        <v>983</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>966</v>
+        <v>984</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>967</v>
+        <v>985</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -8183,33 +8306,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>970</v>
+        <v>988</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>971</v>
+        <v>989</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>973</v>
+        <v>991</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>974</v>
+        <v>992</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>975</v>
+        <v>993</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>976</v>
+        <v>994</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8237,33 +8360,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>977</v>
+        <v>995</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>979</v>
+        <v>997</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>980</v>
+        <v>998</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>981</v>
+        <v>999</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>982</v>
+        <v>1000</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>983</v>
+        <v>1001</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8293,45 +8416,45 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>985</v>
+        <v>1003</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>970</v>
+        <v>988</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>936</v>
+        <v>954</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>986</v>
+        <v>1004</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>988</v>
+        <v>1006</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>989</v>
+        <v>1007</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>990</v>
+        <v>1008</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>991</v>
+        <v>1009</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -8367,80 +8490,80 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>994</v>
+        <v>1012</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>999</v>
+        <v>1017</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1002</v>
+        <v>1020</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1003</v>
+        <v>1021</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1004</v>
+        <v>1022</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1005</v>
+        <v>1023</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1006</v>
+        <v>1024</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1007</v>
+        <v>1025</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>976</v>
+        <v>994</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="L2:L5000">
-      <formula1>Lists!$M$2:$M$22</formula1>
+      <formula1>Lists!$M$2:$M$23</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="M2:M5000">
       <formula1>Lists!$G$2:$G$3</formula1>
@@ -8470,69 +8593,69 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1008</v>
+        <v>1026</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1009</v>
+        <v>1027</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1010</v>
+        <v>1028</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1012</v>
+        <v>1030</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1013</v>
+        <v>1031</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1014</v>
+        <v>1032</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1015</v>
+        <v>1033</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1016</v>
+        <v>1034</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1017</v>
+        <v>1035</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1018</v>
+        <v>1036</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1019</v>
+        <v>1037</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1020</v>
+        <v>1038</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1021</v>
+        <v>1039</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1021</v>
+        <v>1039</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1022</v>
+        <v>1040</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1023</v>
+        <v>1041</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8563,51 +8686,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1024</v>
+        <v>1042</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1008</v>
+        <v>1026</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1026</v>
+        <v>1044</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1027</v>
+        <v>1045</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1028</v>
+        <v>1046</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1029</v>
+        <v>1047</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1030</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1031</v>
+        <v>1049</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1032</v>
+        <v>1050</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1033</v>
+        <v>1051</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1034</v>
+        <v>1052</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1035</v>
+        <v>1053</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1036</v>
+        <v>1054</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -8641,67 +8764,67 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1037</v>
+        <v>1055</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1038</v>
+        <v>1056</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1039</v>
+        <v>1057</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1040</v>
+        <v>1058</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1041</v>
+        <v>1059</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1042</v>
+        <v>1060</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1043</v>
+        <v>1061</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1044</v>
+        <v>1062</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -8754,87 +8877,87 @@
   <sheetData>
     <row r="1" spans="1:15" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1046</v>
+        <v>1064</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1047</v>
+        <v>1065</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1048</v>
+        <v>1066</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1049</v>
+        <v>1067</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1040</v>
+        <v>1058</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1050</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1051</v>
+        <v>1069</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1052</v>
+        <v>1070</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1053</v>
+        <v>1071</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1054</v>
+        <v>1072</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1055</v>
+        <v>1073</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1056</v>
+        <v>1074</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>1057</v>
+        <v>1075</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="O2" s="9"/>
     </row>
@@ -8879,117 +9002,117 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1037</v>
+        <v>1055</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1038</v>
+        <v>1056</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1058</v>
+        <v>1076</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1059</v>
+        <v>1077</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1060</v>
+        <v>1078</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1061</v>
+        <v>1079</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1062</v>
+        <v>1080</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1063</v>
+        <v>1081</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1064</v>
+        <v>1082</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1065</v>
+        <v>1083</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1066</v>
+        <v>1084</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1067</v>
+        <v>1085</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1068</v>
+        <v>1086</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1069</v>
+        <v>1087</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1070</v>
+        <v>1088</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1071</v>
+        <v>1089</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1072</v>
+        <v>1090</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1073</v>
+        <v>1091</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1074</v>
+        <v>1092</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1075</v>
+        <v>1093</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1076</v>
+        <v>1094</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1033</v>
+        <v>1051</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1077</v>
+        <v>1095</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1078</v>
+        <v>1096</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1079</v>
+        <v>1097</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1080</v>
+        <v>1098</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1082</v>
+        <v>1100</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1083</v>
+        <v>1101</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1084</v>
+        <v>1102</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1077</v>
+        <v>1095</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1085</v>
+        <v>1103</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -9008,7 +9131,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
@@ -9047,373 +9170,373 @@
   <sheetData>
     <row r="1" spans="1:32" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="Q2" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>748</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>753</v>
+      </c>
+      <c r="Z2" s="11" t="s">
         <v>737</v>
       </c>
-      <c r="R2" s="11" t="s">
-        <v>738</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>739</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>740</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>741</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>742</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>743</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>744</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>745</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="AA2" s="11" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="AC2" s="11" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="Q3" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="Z3" s="11" t="s">
         <v>767</v>
       </c>
-      <c r="R3" s="11" t="s">
-        <v>768</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>769</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>770</v>
-      </c>
-      <c r="U3" s="11" t="s">
-        <v>771</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>772</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>773</v>
-      </c>
-      <c r="X3" s="11" t="s">
-        <v>774</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>775</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>759</v>
-      </c>
       <c r="AA3" s="11" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="AF3" s="11" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="AF4" s="11"/>
     </row>
@@ -9421,46 +9544,46 @@
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -9469,17 +9592,17 @@
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="AF5" s="11"/>
     </row>
@@ -9487,37 +9610,37 @@
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -9527,12 +9650,12 @@
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="11" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="AE6" s="11"/>
       <c r="AF6" s="11"/>
@@ -9542,29 +9665,29 @@
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -9577,12 +9700,12 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="11" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
       <c r="AD7" s="11" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="AE7" s="11"/>
       <c r="AF7" s="11"/>
@@ -9592,7 +9715,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -9603,16 +9726,16 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
       <c r="M8" s="11" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -9625,11 +9748,13 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="11" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
+      <c r="AD8" s="11" t="s">
+        <v>851</v>
+      </c>
       <c r="AE8" s="11"/>
       <c r="AF8" s="11"/>
     </row>
@@ -9638,7 +9763,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -9649,16 +9774,16 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>845</v>
+        <v>854</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -9671,11 +9796,13 @@
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
+      <c r="AD9" s="11" t="s">
+        <v>858</v>
+      </c>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
     </row>
@@ -9684,7 +9811,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -9695,14 +9822,14 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>851</v>
+        <v>861</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="11" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -9717,7 +9844,9 @@
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
       <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
+      <c r="AD10" s="11" t="s">
+        <v>863</v>
+      </c>
       <c r="AE10" s="11"/>
       <c r="AF10" s="11"/>
     </row>
@@ -9726,7 +9855,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -9737,14 +9866,12 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11" t="s">
-        <v>854</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>855</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="N11" s="11"/>
       <c r="O11" s="11"/>
       <c r="P11" s="11" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -9759,7 +9886,9 @@
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
       <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
+      <c r="AD11" s="11" t="s">
+        <v>867</v>
+      </c>
       <c r="AE11" s="11"/>
       <c r="AF11" s="11"/>
     </row>
@@ -9768,7 +9897,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -9779,14 +9908,12 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11" t="s">
-        <v>858</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>859</v>
-      </c>
+        <v>869</v>
+      </c>
+      <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -9801,7 +9928,9 @@
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
       <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
+      <c r="AD12" s="11" t="s">
+        <v>871</v>
+      </c>
       <c r="AE12" s="11"/>
       <c r="AF12" s="11"/>
     </row>
@@ -9819,14 +9948,12 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11" t="s">
-        <v>861</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>862</v>
-      </c>
+        <v>872</v>
+      </c>
+      <c r="N13" s="11"/>
       <c r="O13" s="11"/>
       <c r="P13" s="11" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -9841,7 +9968,9 @@
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
       <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
+      <c r="AD13" s="11" t="s">
+        <v>874</v>
+      </c>
       <c r="AE13" s="11"/>
       <c r="AF13" s="11"/>
     </row>
@@ -9859,11 +9988,9 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11" t="s">
-        <v>864</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>865</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
@@ -9879,7 +10006,9 @@
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
       <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
+      <c r="AD14" s="11" t="s">
+        <v>876</v>
+      </c>
       <c r="AE14" s="11"/>
       <c r="AF14" s="11"/>
     </row>
@@ -9897,11 +10026,9 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11" t="s">
-        <v>866</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>867</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="N15" s="11"/>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -9917,7 +10044,9 @@
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
       <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
+      <c r="AD15" s="11" t="s">
+        <v>878</v>
+      </c>
       <c r="AE15" s="11"/>
       <c r="AF15" s="11"/>
     </row>
@@ -9935,11 +10064,9 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11" t="s">
-        <v>868</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>869</v>
-      </c>
+        <v>879</v>
+      </c>
+      <c r="N16" s="11"/>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
@@ -9955,7 +10082,9 @@
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
+      <c r="AD16" s="11" t="s">
+        <v>880</v>
+      </c>
       <c r="AE16" s="11"/>
       <c r="AF16" s="11"/>
     </row>
@@ -9973,11 +10102,9 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>871</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="N17" s="11"/>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -9993,7 +10120,9 @@
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
       <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
+      <c r="AD17" s="11" t="s">
+        <v>882</v>
+      </c>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
     </row>
@@ -10011,7 +10140,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
@@ -10029,7 +10158,9 @@
       <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
       <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
+      <c r="AD18" s="11" t="s">
+        <v>884</v>
+      </c>
       <c r="AE18" s="11"/>
       <c r="AF18" s="11"/>
     </row>
@@ -10047,7 +10178,7 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
@@ -10065,7 +10196,9 @@
       <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
       <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
+      <c r="AD19" s="11" t="s">
+        <v>886</v>
+      </c>
       <c r="AE19" s="11"/>
       <c r="AF19" s="11"/>
     </row>
@@ -10083,7 +10216,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
@@ -10101,7 +10234,9 @@
       <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
       <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
+      <c r="AD20" s="11" t="s">
+        <v>888</v>
+      </c>
       <c r="AE20" s="11"/>
       <c r="AF20" s="11"/>
     </row>
@@ -10119,7 +10254,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11" t="s">
-        <v>875</v>
+        <v>889</v>
       </c>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
@@ -10137,7 +10272,9 @@
       <c r="AA21" s="11"/>
       <c r="AB21" s="11"/>
       <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
+      <c r="AD21" s="11" t="s">
+        <v>890</v>
+      </c>
       <c r="AE21" s="11"/>
       <c r="AF21" s="11"/>
     </row>
@@ -10155,7 +10292,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
@@ -10173,9 +10310,49 @@
       <c r="AA22" s="11"/>
       <c r="AB22" s="11"/>
       <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
+      <c r="AD22" s="11" t="s">
+        <v>892</v>
+      </c>
       <c r="AE22" s="11"/>
       <c r="AF22" s="11"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="11"/>
+      <c r="AB23" s="11"/>
+      <c r="AC23" s="11"/>
+      <c r="AD23" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="AE23" s="11"/>
+      <c r="AF23" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10197,36 +10374,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1086</v>
+        <v>1104</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1087</v>
+        <v>1105</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1088</v>
+        <v>1106</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1089</v>
+        <v>1107</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1090</v>
+        <v>1108</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1091</v>
+        <v>1109</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1092</v>
+        <v>1110</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1093</v>
+        <v>1111</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -10264,80 +10441,80 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1094</v>
+        <v>1112</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1095</v>
+        <v>1113</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1096</v>
+        <v>1114</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1098</v>
+        <v>1116</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1099</v>
+        <v>1117</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1100</v>
+        <v>1118</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1101</v>
+        <v>1119</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1102</v>
+        <v>1120</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1103</v>
+        <v>1121</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1104</v>
+        <v>1122</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1105</v>
+        <v>1123</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1106</v>
+        <v>1124</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1107</v>
+        <v>1125</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1108</v>
+        <v>1126</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1109</v>
+        <v>1127</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>976</v>
+        <v>994</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1110</v>
+        <v>1128</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1111</v>
+        <v>1129</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1112</v>
+        <v>1130</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -10370,39 +10547,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1113</v>
+        <v>1131</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1115</v>
+        <v>1133</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1116</v>
+        <v>1134</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1117</v>
+        <v>1135</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1118</v>
+        <v>1136</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1119</v>
+        <v>1137</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1120</v>
+        <v>1138</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1121</v>
+        <v>1139</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -10447,122 +10624,122 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1122</v>
+        <v>1140</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1123</v>
+        <v>1141</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1124</v>
+        <v>1142</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1125</v>
+        <v>1143</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1066</v>
+        <v>1084</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1126</v>
+        <v>1144</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1127</v>
+        <v>1145</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1128</v>
+        <v>1146</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1129</v>
+        <v>1147</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>1130</v>
+        <v>1148</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>1131</v>
+        <v>1149</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>1132</v>
+        <v>1150</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1133</v>
+        <v>1151</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1134</v>
+        <v>1152</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1135</v>
+        <v>1153</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1136</v>
+        <v>1154</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1137</v>
+        <v>1155</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1138</v>
+        <v>1156</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>905</v>
+        <v>923</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1139</v>
+        <v>1157</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1140</v>
+        <v>1158</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1141</v>
+        <v>1159</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1142</v>
+        <v>1160</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1143</v>
+        <v>1161</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1144</v>
+        <v>1162</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -10598,27 +10775,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1145</v>
+        <v>1163</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1146</v>
+        <v>1164</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1147</v>
+        <v>1165</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1148</v>
+        <v>1166</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1149</v>
+        <v>1167</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1150</v>
+        <v>1168</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -10649,48 +10826,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1151</v>
+        <v>1169</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1152</v>
+        <v>1170</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1153</v>
+        <v>1171</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1154</v>
+        <v>1172</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1155</v>
+        <v>1173</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1156</v>
+        <v>1174</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1157</v>
+        <v>1175</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1158</v>
+        <v>1176</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1159</v>
+        <v>1177</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1160</v>
+        <v>1178</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1161</v>
+        <v>1179</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -10728,33 +10905,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1162</v>
+        <v>1180</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1163</v>
+        <v>1181</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1164</v>
+        <v>1182</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1165</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1166</v>
+        <v>1184</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1167</v>
+        <v>1185</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -10782,30 +10959,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1168</v>
+        <v>1186</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1169</v>
+        <v>1187</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1170</v>
+        <v>1188</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1171</v>
+        <v>1189</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1172</v>
+        <v>1190</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1174</v>
+        <v>1192</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -10834,15 +11011,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -10868,21 +11045,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1177</v>
+        <v>1195</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1179</v>
+        <v>1197</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -10925,115 +11102,115 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>877</v>
+        <v>895</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>878</v>
+        <v>896</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>881</v>
+        <v>899</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>883</v>
+        <v>901</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>889</v>
+        <v>907</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>894</v>
+        <v>912</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>897</v>
+        <v>915</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>898</v>
+        <v>916</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>899</v>
+        <v>917</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>900</v>
+        <v>918</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>901</v>
+        <v>919</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>902</v>
+        <v>920</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>903</v>
+        <v>921</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>905</v>
+        <v>923</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="T2" s="9"/>
     </row>
@@ -11061,33 +11238,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1177</v>
+        <v>1195</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1181</v>
+        <v>1199</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1183</v>
+        <v>1201</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1184</v>
+        <v>1202</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1186</v>
+        <v>1204</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11118,51 +11295,51 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1187</v>
+        <v>1205</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1188</v>
+        <v>1206</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1189</v>
+        <v>1207</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1190</v>
+        <v>1208</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1191</v>
+        <v>1209</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1192</v>
+        <v>1210</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1181</v>
+        <v>1199</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1193</v>
+        <v>1211</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1194</v>
+        <v>1212</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1195</v>
+        <v>1213</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1179</v>
+        <v>1197</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1196</v>
+        <v>1214</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1197</v>
+        <v>1215</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1198</v>
+        <v>1216</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -11199,87 +11376,87 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1200</v>
+        <v>1218</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1201</v>
+        <v>1219</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1202</v>
+        <v>1220</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1203</v>
+        <v>1221</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1205</v>
+        <v>1223</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1066</v>
+        <v>1084</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1068</v>
+        <v>1086</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1206</v>
+        <v>1224</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1207</v>
+        <v>1225</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1208</v>
+        <v>1226</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1209</v>
+        <v>1227</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1210</v>
+        <v>1228</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1212</v>
+        <v>1230</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1144</v>
+        <v>1162</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1213</v>
+        <v>1231</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1214</v>
+        <v>1232</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1215</v>
+        <v>1233</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1216</v>
+        <v>1234</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1075</v>
+        <v>1093</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1217</v>
+        <v>1235</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -11311,54 +11488,54 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1218</v>
+        <v>1236</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1219</v>
+        <v>1237</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1220</v>
+        <v>1238</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1221</v>
+        <v>1239</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1222</v>
+        <v>1240</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1223</v>
+        <v>1241</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1224</v>
+        <v>1242</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1226</v>
+        <v>1244</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1227</v>
+        <v>1245</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1228</v>
+        <v>1246</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1229</v>
+        <v>1247</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1230</v>
+        <v>1248</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -11387,33 +11564,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1231</v>
+        <v>1249</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1232</v>
+        <v>1250</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1233</v>
+        <v>1251</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1234</v>
+        <v>1252</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1235</v>
+        <v>1253</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1236</v>
+        <v>1254</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -11442,39 +11619,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1237</v>
+        <v>1255</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1238</v>
+        <v>1256</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1239</v>
+        <v>1257</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1240</v>
+        <v>1258</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1241</v>
+        <v>1259</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -11511,48 +11688,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1242</v>
+        <v>1260</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1243</v>
+        <v>1261</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1244</v>
+        <v>1262</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1245</v>
+        <v>1263</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1246</v>
+        <v>1264</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1248</v>
+        <v>1266</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -11588,75 +11765,75 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1249</v>
+        <v>1267</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1250</v>
+        <v>1268</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1066</v>
+        <v>1084</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1068</v>
+        <v>1086</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1251</v>
+        <v>1269</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1252</v>
+        <v>1270</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1253</v>
+        <v>1271</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1254</v>
+        <v>1272</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1255</v>
+        <v>1273</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1256</v>
+        <v>1274</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1257</v>
+        <v>1275</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1259</v>
+        <v>1277</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1260</v>
+        <v>1278</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1261</v>
+        <v>1279</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -11686,42 +11863,42 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1264</v>
+        <v>1282</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1265</v>
+        <v>1283</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1266</v>
+        <v>1284</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1267</v>
+        <v>1285</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1268</v>
+        <v>1286</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1269</v>
+        <v>1287</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>976</v>
+        <v>994</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1270</v>
+        <v>1288</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -11752,42 +11929,42 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1271</v>
+        <v>1289</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1272</v>
+        <v>1290</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1273</v>
+        <v>1291</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1274</v>
+        <v>1292</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1275</v>
+        <v>1293</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -11795,7 +11972,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="C2:C5000">
-      <formula1>Lists!$AD$2:$AD$7</formula1>
+      <formula1>Lists!$AD$2:$AD$23</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G2:G5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -11817,24 +11994,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -11860,62 +12037,62 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1276</v>
+        <v>1294</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1277</v>
+        <v>1295</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1278</v>
+        <v>1296</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1279</v>
+        <v>1297</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1024</v>
+        <v>1042</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1281</v>
+        <v>1299</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1282</v>
+        <v>1300</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1283</v>
+        <v>1301</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1284</v>
+        <v>1302</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$17</formula1>
+      <formula1>Lists!$N$2:$N$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
       <formula1>Lists!$O$2:$O$9</formula1>
@@ -11956,70 +12133,70 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1285</v>
+        <v>1303</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1286</v>
+        <v>1304</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1287</v>
+        <v>1305</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1288</v>
+        <v>1306</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1289</v>
+        <v>1307</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1290</v>
+        <v>1308</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1291</v>
+        <v>1309</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1292</v>
+        <v>1310</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1293</v>
+        <v>1311</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1294</v>
+        <v>1312</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1295</v>
+        <v>1313</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1296</v>
+        <v>1314</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1270</v>
+        <v>1288</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12028,10 +12205,10 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1283</v>
+        <v>1301</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -12073,55 +12250,55 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1285</v>
+        <v>1303</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1279</v>
+        <v>1297</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1294</v>
+        <v>1312</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1297</v>
+        <v>1315</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1298</v>
+        <v>1316</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1298</v>
+        <v>1316</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1299</v>
+        <v>1317</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1283</v>
+        <v>1301</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I2" s="9"/>
     </row>
@@ -12148,30 +12325,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1300</v>
+        <v>1318</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1301</v>
+        <v>1319</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1302</v>
+        <v>1320</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1303</v>
+        <v>1321</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1304</v>
+        <v>1322</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1305</v>
+        <v>1323</v>
       </c>
     </row>
   </sheetData>
@@ -12180,7 +12357,7 @@
       <formula1>Lists!$P$2:$P$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
-      <formula1>Lists!$M$2:$M$22</formula1>
+      <formula1>Lists!$M$2:$M$23</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12204,54 +12381,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1307</v>
+        <v>1325</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1308</v>
+        <v>1326</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1309</v>
+        <v>1327</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1310</v>
+        <v>1328</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1311</v>
+        <v>1329</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1312</v>
+        <v>1330</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1313</v>
+        <v>1331</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1314</v>
+        <v>1332</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1315</v>
+        <v>1333</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1186</v>
+        <v>1204</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1316</v>
+        <v>1334</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -12285,56 +12462,56 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1317</v>
+        <v>1335</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1318</v>
+        <v>1336</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1059</v>
+        <v>1077</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1038</v>
+        <v>1056</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1319</v>
+        <v>1337</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1320</v>
+        <v>1338</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>851</v>
+        <v>817</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1322</v>
+        <v>1340</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1323</v>
+        <v>1341</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1324</v>
+        <v>1342</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
@@ -12370,58 +12547,131 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1325</v>
+        <v>1343</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1308</v>
+        <v>1326</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1326</v>
+        <v>1344</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1327</v>
+        <v>1345</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1311</v>
+        <v>1329</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1328</v>
+        <v>1346</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1281</v>
+        <v>1299</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>1329</v>
+        <v>1347</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1330</v>
+        <v>1348</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1331</v>
+        <v>1349</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1330</v>
+        <v>1348</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1332</v>
+        <v>1350</v>
       </c>
       <c r="H2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$17</formula1>
+      <formula1>Lists!$N$2:$N$10</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="20" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12440,33 +12690,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>918</v>
+        <v>936</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -12496,43 +12746,43 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>923</v>
+        <v>941</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>928</v>
+        <v>946</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>930</v>
+        <v>948</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>931</v>
+        <v>949</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>932</v>
+        <v>950</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -12563,48 +12813,48 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>933</v>
+        <v>951</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>934</v>
+        <v>952</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>935</v>
+        <v>953</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>936</v>
+        <v>954</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>937</v>
+        <v>955</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>938</v>
+        <v>956</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>939</v>
+        <v>957</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>931</v>
+        <v>949</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -12641,53 +12891,53 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>940</v>
+        <v>958</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>935</v>
+        <v>953</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>943</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>889</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>944</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>925</v>
-      </c>
       <c r="J1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>947</v>
+        <v>965</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>948</v>
+        <v>966</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>949</v>
+        <v>967</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -12720,33 +12970,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>950</v>
+        <v>968</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>951</v>
+        <v>969</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>889</v>
+        <v>907</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>953</v>
+        <v>971</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>954</v>
+        <v>972</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>956</v>
+        <v>974</v>
       </c>
       <c r="E2" s="9"/>
     </row>

--- a/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/GoLive_Configuration_Workbook.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1964" uniqueCount="1465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1478">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -396,7 +396,7 @@
     <t xml:space="preserve">44. COC Series</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From. After: Insurers, Branches</t>
+    <t xml:space="preserve">Policy Servicing &gt; CTPL Authentication (COC series). Key: Insurer + Prefix + From. After: Insurers, Branches</t>
   </si>
   <si>
     <t xml:space="preserve">45. Feature Entitlements</t>
@@ -597,7 +597,7 @@
     <t xml:space="preserve">Referrers / agents and their commission accounts</t>
   </si>
   <si>
-    <t xml:space="preserve">Commission &gt; Agents/Referrer Accounts</t>
+    <t xml:space="preserve">Accounts &gt; Commission &gt; Agents/Referrer Accounts</t>
   </si>
   <si>
     <t xml:space="preserve">Petty cash funds</t>
@@ -2460,252 +2460,255 @@
     <t xml:space="preserve">sales</t>
   </si>
   <si>
+    <t xml:space="preserve">CTINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL-VOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy_issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitan area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non_package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corporate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pro-rata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFS confirmation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">repudiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent/Referrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processing</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAAGAP</t>
   </si>
   <si>
-    <t xml:space="preserve">CL-VOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">policy_issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metropolitan area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independent Component City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">direct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non_package</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corporate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insurer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pro-rata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TFS confirmation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repudiation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent/Referrer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">any</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processing</t>
+    <t xml:space="preserve">CTPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return_premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special Geographic Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thrift Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short-period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-current Liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">never</t>
+  </si>
+  <si>
+    <t xml:space="preserve">operations</t>
   </si>
   <si>
     <t xml:space="preserve">MALAYAN</t>
   </si>
   <si>
-    <t xml:space="preserve">CTPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">return_premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Special Geographic Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thrift Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Deposit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">both</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short-period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lapse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-current Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">never</t>
-  </si>
-  <si>
-    <t xml:space="preserve">operations</t>
+    <t xml:space="preserve">GPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claim_settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province / state outside the Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lgt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per_document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claims</t>
   </si>
   <si>
     <t xml:space="preserve">PIONEER</t>
   </si>
   <si>
-    <t xml:space="preserve">GPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claim_settlement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Province / state outside the Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trust Account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lgt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per_document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claims</t>
+    <t xml:space="preserve">MOTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">renewal_terms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting</t>
   </si>
   <si>
     <t xml:space="preserve">STANDARD</t>
   </si>
   <si>
-    <t xml:space="preserve">MOTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">renewal_terms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Government Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adjustment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting</t>
+    <t xml:space="preserve">PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_voucher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region IV-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casualty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non-materialise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting-manager</t>
   </si>
   <si>
     <t xml:space="preserve">STRONGHOLD</t>
   </si>
   <si>
-    <t xml:space="preserve">PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">payment_voucher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region IV-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casualty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non-materialise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accounting-manager</t>
-  </si>
-  <si>
     <t xml:space="preserve">PARCEL</t>
   </si>
   <si>
@@ -3006,6 +3009,42 @@
     <t xml:space="preserve">scheme_end</t>
   </si>
   <si>
+    <t xml:space="preserve">dealer_scheme_return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dealer_scheme_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scheme_application_cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lockin_renew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lockin_hold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lockin_release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lockin_not_renewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lockin_end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fmv_edit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rate_override</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incentive_disqualify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incentive_exclude</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company Code *</t>
   </si>
   <si>
@@ -4449,7 +4488,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T04:55:40.552Z</t>
+    <t xml:space="preserve">2026-10-12T02:03:01.076Z</t>
   </si>
   <si>
     <t xml:space="preserve">Generated by</t>
@@ -8632,52 +8671,52 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>983</v>
+        <v>996</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>993</v>
+        <v>1006</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="Q1" s="8" t="s">
         <v>723</v>
@@ -8685,38 +8724,38 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -8751,16 +8790,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -8768,16 +8807,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8805,16 +8844,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -8822,16 +8861,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -8861,22 +8900,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>723</v>
@@ -8884,22 +8923,22 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -8935,40 +8974,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>723</v>
@@ -8976,24 +9015,24 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -9038,34 +9077,34 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>723</v>
@@ -9073,31 +9112,31 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>788</v>
@@ -9131,25 +9170,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>723</v>
@@ -9157,25 +9196,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -9209,55 +9248,55 @@
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>724</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>725</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>726</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>723</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>859</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>760</v>
@@ -9323,49 +9362,49 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>993</v>
+        <v>1006</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>723</v>
@@ -9373,38 +9412,38 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>806</v>
@@ -9452,58 +9491,58 @@
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="S1" s="8" t="s">
         <v>723</v>
@@ -9511,58 +9550,58 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>775</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="S2" s="9"/>
     </row>
@@ -9581,7 +9620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH65"/>
+  <dimension ref="A1:AH77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="11" customWidth="1"/>
@@ -10216,17 +10255,19 @@
       <c r="M8" s="11" t="s">
         <v>881</v>
       </c>
-      <c r="N8" s="11"/>
+      <c r="N8" s="11" t="s">
+        <v>882</v>
+      </c>
       <c r="O8" s="11" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
       <c r="S8" s="11" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
@@ -10237,13 +10278,13 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="11"/>
       <c r="AB8" s="11" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AC8" s="11"/>
       <c r="AD8" s="11"/>
       <c r="AE8" s="11"/>
       <c r="AF8" s="11" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AG8" s="11"/>
       <c r="AH8" s="11"/>
@@ -10253,7 +10294,7 @@
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -10264,19 +10305,19 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N9" s="11"/>
       <c r="O9" s="11" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
@@ -10287,13 +10328,13 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AG9" s="11"/>
       <c r="AH9" s="11"/>
@@ -10303,7 +10344,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -10314,17 +10355,17 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="11" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
       <c r="S10" s="11" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
@@ -10339,7 +10380,7 @@
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
       <c r="AF10" s="11" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="AG10" s="11"/>
       <c r="AH10" s="11"/>
@@ -10349,7 +10390,7 @@
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -10360,17 +10401,17 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="M11" s="11" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
       <c r="P11" s="11" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
       <c r="S11" s="11" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
@@ -10385,7 +10426,7 @@
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
       <c r="AF11" s="11" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AG11" s="11"/>
       <c r="AH11" s="11"/>
@@ -10395,7 +10436,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -10406,17 +10447,17 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
       <c r="S12" s="11" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
@@ -10431,7 +10472,7 @@
       <c r="AD12" s="11"/>
       <c r="AE12" s="11"/>
       <c r="AF12" s="11" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AG12" s="11"/>
       <c r="AH12" s="11"/>
@@ -10450,17 +10491,17 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
       <c r="M13" s="11" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
       <c r="P13" s="11" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
       <c r="S13" s="11" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
@@ -10475,7 +10516,7 @@
       <c r="AD13" s="11"/>
       <c r="AE13" s="11"/>
       <c r="AF13" s="11" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AG13" s="11"/>
       <c r="AH13" s="11"/>
@@ -10494,17 +10535,17 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="11" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
@@ -10519,7 +10560,7 @@
       <c r="AD14" s="11"/>
       <c r="AE14" s="11"/>
       <c r="AF14" s="11" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AG14" s="11"/>
       <c r="AH14" s="11"/>
@@ -10538,7 +10579,7 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
@@ -10546,7 +10587,7 @@
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
       <c r="S15" s="11" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
@@ -10561,7 +10602,7 @@
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
       <c r="AF15" s="11" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AG15" s="11"/>
       <c r="AH15" s="11"/>
@@ -10580,7 +10621,7 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
@@ -10588,7 +10629,7 @@
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
@@ -10603,7 +10644,7 @@
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
       <c r="AF16" s="11" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="AG16" s="11"/>
       <c r="AH16" s="11"/>
@@ -10622,7 +10663,7 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
@@ -10630,7 +10671,7 @@
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
@@ -10645,7 +10686,7 @@
       <c r="AD17" s="11"/>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AG17" s="11"/>
       <c r="AH17" s="11"/>
@@ -10664,7 +10705,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
       <c r="M18" s="11" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
@@ -10672,7 +10713,7 @@
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
       <c r="S18" s="11" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="T18" s="11"/>
       <c r="U18" s="11"/>
@@ -10687,7 +10728,7 @@
       <c r="AD18" s="11"/>
       <c r="AE18" s="11"/>
       <c r="AF18" s="11" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AG18" s="11"/>
       <c r="AH18" s="11"/>
@@ -10706,7 +10747,7 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
       <c r="M19" s="11" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
@@ -10727,7 +10768,7 @@
       <c r="AD19" s="11"/>
       <c r="AE19" s="11"/>
       <c r="AF19" s="11" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AG19" s="11"/>
       <c r="AH19" s="11"/>
@@ -10746,7 +10787,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
       <c r="M20" s="11" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
@@ -10767,7 +10808,7 @@
       <c r="AD20" s="11"/>
       <c r="AE20" s="11"/>
       <c r="AF20" s="11" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AG20" s="11"/>
       <c r="AH20" s="11"/>
@@ -10786,7 +10827,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
@@ -10807,7 +10848,7 @@
       <c r="AD21" s="11"/>
       <c r="AE21" s="11"/>
       <c r="AF21" s="11" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="AG21" s="11"/>
       <c r="AH21" s="11"/>
@@ -10826,7 +10867,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
@@ -10847,7 +10888,7 @@
       <c r="AD22" s="11"/>
       <c r="AE22" s="11"/>
       <c r="AF22" s="11" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="AG22" s="11"/>
       <c r="AH22" s="11"/>
@@ -10866,7 +10907,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
       <c r="M23" s="11" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="N23" s="11"/>
       <c r="O23" s="11"/>
@@ -10887,7 +10928,7 @@
       <c r="AD23" s="11"/>
       <c r="AE23" s="11"/>
       <c r="AF23" s="11" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AG23" s="11"/>
       <c r="AH23" s="11"/>
@@ -10906,7 +10947,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
       <c r="M24" s="11" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
@@ -10927,7 +10968,7 @@
       <c r="AD24" s="11"/>
       <c r="AE24" s="11"/>
       <c r="AF24" s="11" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AG24" s="11"/>
       <c r="AH24" s="11"/>
@@ -10965,7 +11006,7 @@
       <c r="AD25" s="11"/>
       <c r="AE25" s="11"/>
       <c r="AF25" s="11" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="AG25" s="11"/>
       <c r="AH25" s="11"/>
@@ -11003,7 +11044,7 @@
       <c r="AD26" s="11"/>
       <c r="AE26" s="11"/>
       <c r="AF26" s="11" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AG26" s="11"/>
       <c r="AH26" s="11"/>
@@ -11041,7 +11082,7 @@
       <c r="AD27" s="11"/>
       <c r="AE27" s="11"/>
       <c r="AF27" s="11" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AG27" s="11"/>
       <c r="AH27" s="11"/>
@@ -11079,7 +11120,7 @@
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
       <c r="AF28" s="11" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AG28" s="11"/>
       <c r="AH28" s="11"/>
@@ -11117,7 +11158,7 @@
       <c r="AD29" s="11"/>
       <c r="AE29" s="11"/>
       <c r="AF29" s="11" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AG29" s="11"/>
       <c r="AH29" s="11"/>
@@ -11155,7 +11196,7 @@
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
       <c r="AF30" s="11" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="AG30" s="11"/>
       <c r="AH30" s="11"/>
@@ -11193,7 +11234,7 @@
       <c r="AD31" s="11"/>
       <c r="AE31" s="11"/>
       <c r="AF31" s="11" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AG31" s="11"/>
       <c r="AH31" s="11"/>
@@ -11231,7 +11272,7 @@
       <c r="AD32" s="11"/>
       <c r="AE32" s="11"/>
       <c r="AF32" s="11" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AG32" s="11"/>
       <c r="AH32" s="11"/>
@@ -11269,7 +11310,7 @@
       <c r="AD33" s="11"/>
       <c r="AE33" s="11"/>
       <c r="AF33" s="11" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AG33" s="11"/>
       <c r="AH33" s="11"/>
@@ -11307,7 +11348,7 @@
       <c r="AD34" s="11"/>
       <c r="AE34" s="11"/>
       <c r="AF34" s="11" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AG34" s="11"/>
       <c r="AH34" s="11"/>
@@ -11345,7 +11386,7 @@
       <c r="AD35" s="11"/>
       <c r="AE35" s="11"/>
       <c r="AF35" s="11" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="AG35" s="11"/>
       <c r="AH35" s="11"/>
@@ -11383,7 +11424,7 @@
       <c r="AD36" s="11"/>
       <c r="AE36" s="11"/>
       <c r="AF36" s="11" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="AG36" s="11"/>
       <c r="AH36" s="11"/>
@@ -11421,7 +11462,7 @@
       <c r="AD37" s="11"/>
       <c r="AE37" s="11"/>
       <c r="AF37" s="11" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AG37" s="11"/>
       <c r="AH37" s="11"/>
@@ -11459,7 +11500,7 @@
       <c r="AD38" s="11"/>
       <c r="AE38" s="11"/>
       <c r="AF38" s="11" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AG38" s="11"/>
       <c r="AH38" s="11"/>
@@ -11497,7 +11538,7 @@
       <c r="AD39" s="11"/>
       <c r="AE39" s="11"/>
       <c r="AF39" s="11" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AG39" s="11"/>
       <c r="AH39" s="11"/>
@@ -11535,7 +11576,7 @@
       <c r="AD40" s="11"/>
       <c r="AE40" s="11"/>
       <c r="AF40" s="11" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AG40" s="11"/>
       <c r="AH40" s="11"/>
@@ -11573,7 +11614,7 @@
       <c r="AD41" s="11"/>
       <c r="AE41" s="11"/>
       <c r="AF41" s="11" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AG41" s="11"/>
       <c r="AH41" s="11"/>
@@ -11611,7 +11652,7 @@
       <c r="AD42" s="11"/>
       <c r="AE42" s="11"/>
       <c r="AF42" s="11" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AG42" s="11"/>
       <c r="AH42" s="11"/>
@@ -11649,7 +11690,7 @@
       <c r="AD43" s="11"/>
       <c r="AE43" s="11"/>
       <c r="AF43" s="11" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AG43" s="11"/>
       <c r="AH43" s="11"/>
@@ -11687,7 +11728,7 @@
       <c r="AD44" s="11"/>
       <c r="AE44" s="11"/>
       <c r="AF44" s="11" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AG44" s="11"/>
       <c r="AH44" s="11"/>
@@ -11725,7 +11766,7 @@
       <c r="AD45" s="11"/>
       <c r="AE45" s="11"/>
       <c r="AF45" s="11" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AG45" s="11"/>
       <c r="AH45" s="11"/>
@@ -11763,7 +11804,7 @@
       <c r="AD46" s="11"/>
       <c r="AE46" s="11"/>
       <c r="AF46" s="11" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="AG46" s="11"/>
       <c r="AH46" s="11"/>
@@ -11801,7 +11842,7 @@
       <c r="AD47" s="11"/>
       <c r="AE47" s="11"/>
       <c r="AF47" s="11" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="AG47" s="11"/>
       <c r="AH47" s="11"/>
@@ -11839,7 +11880,7 @@
       <c r="AD48" s="11"/>
       <c r="AE48" s="11"/>
       <c r="AF48" s="11" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AG48" s="11"/>
       <c r="AH48" s="11"/>
@@ -11877,7 +11918,7 @@
       <c r="AD49" s="11"/>
       <c r="AE49" s="11"/>
       <c r="AF49" s="11" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AG49" s="11"/>
       <c r="AH49" s="11"/>
@@ -11915,7 +11956,7 @@
       <c r="AD50" s="11"/>
       <c r="AE50" s="11"/>
       <c r="AF50" s="11" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AG50" s="11"/>
       <c r="AH50" s="11"/>
@@ -11953,7 +11994,7 @@
       <c r="AD51" s="11"/>
       <c r="AE51" s="11"/>
       <c r="AF51" s="11" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AG51" s="11"/>
       <c r="AH51" s="11"/>
@@ -11991,7 +12032,7 @@
       <c r="AD52" s="11"/>
       <c r="AE52" s="11"/>
       <c r="AF52" s="11" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AG52" s="11"/>
       <c r="AH52" s="11"/>
@@ -12029,7 +12070,7 @@
       <c r="AD53" s="11"/>
       <c r="AE53" s="11"/>
       <c r="AF53" s="11" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AG53" s="11"/>
       <c r="AH53" s="11"/>
@@ -12067,7 +12108,7 @@
       <c r="AD54" s="11"/>
       <c r="AE54" s="11"/>
       <c r="AF54" s="11" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AG54" s="11"/>
       <c r="AH54" s="11"/>
@@ -12105,7 +12146,7 @@
       <c r="AD55" s="11"/>
       <c r="AE55" s="11"/>
       <c r="AF55" s="11" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="AG55" s="11"/>
       <c r="AH55" s="11"/>
@@ -12143,7 +12184,7 @@
       <c r="AD56" s="11"/>
       <c r="AE56" s="11"/>
       <c r="AF56" s="11" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="AG56" s="11"/>
       <c r="AH56" s="11"/>
@@ -12181,7 +12222,7 @@
       <c r="AD57" s="11"/>
       <c r="AE57" s="11"/>
       <c r="AF57" s="11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AG57" s="11"/>
       <c r="AH57" s="11"/>
@@ -12219,7 +12260,7 @@
       <c r="AD58" s="11"/>
       <c r="AE58" s="11"/>
       <c r="AF58" s="11" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AG58" s="11"/>
       <c r="AH58" s="11"/>
@@ -12257,7 +12298,7 @@
       <c r="AD59" s="11"/>
       <c r="AE59" s="11"/>
       <c r="AF59" s="11" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AG59" s="11"/>
       <c r="AH59" s="11"/>
@@ -12295,7 +12336,7 @@
       <c r="AD60" s="11"/>
       <c r="AE60" s="11"/>
       <c r="AF60" s="11" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AG60" s="11"/>
       <c r="AH60" s="11"/>
@@ -12333,7 +12374,7 @@
       <c r="AD61" s="11"/>
       <c r="AE61" s="11"/>
       <c r="AF61" s="11" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AG61" s="11"/>
       <c r="AH61" s="11"/>
@@ -12371,7 +12412,7 @@
       <c r="AD62" s="11"/>
       <c r="AE62" s="11"/>
       <c r="AF62" s="11" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="AG62" s="11"/>
       <c r="AH62" s="11"/>
@@ -12409,7 +12450,7 @@
       <c r="AD63" s="11"/>
       <c r="AE63" s="11"/>
       <c r="AF63" s="11" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AG63" s="11"/>
       <c r="AH63" s="11"/>
@@ -12447,7 +12488,7 @@
       <c r="AD64" s="11"/>
       <c r="AE64" s="11"/>
       <c r="AF64" s="11" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AG64" s="11"/>
       <c r="AH64" s="11"/>
@@ -12485,10 +12526,466 @@
       <c r="AD65" s="11"/>
       <c r="AE65" s="11"/>
       <c r="AF65" s="11" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="AG65" s="11"/>
       <c r="AH65" s="11"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="11"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11"/>
+      <c r="S66" s="11"/>
+      <c r="T66" s="11"/>
+      <c r="U66" s="11"/>
+      <c r="V66" s="11"/>
+      <c r="W66" s="11"/>
+      <c r="X66" s="11"/>
+      <c r="Y66" s="11"/>
+      <c r="Z66" s="11"/>
+      <c r="AA66" s="11"/>
+      <c r="AB66" s="11"/>
+      <c r="AC66" s="11"/>
+      <c r="AD66" s="11"/>
+      <c r="AE66" s="11"/>
+      <c r="AF66" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="AG66" s="11"/>
+      <c r="AH66" s="11"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="11"/>
+      <c r="O67" s="11"/>
+      <c r="P67" s="11"/>
+      <c r="Q67" s="11"/>
+      <c r="R67" s="11"/>
+      <c r="S67" s="11"/>
+      <c r="T67" s="11"/>
+      <c r="U67" s="11"/>
+      <c r="V67" s="11"/>
+      <c r="W67" s="11"/>
+      <c r="X67" s="11"/>
+      <c r="Y67" s="11"/>
+      <c r="Z67" s="11"/>
+      <c r="AA67" s="11"/>
+      <c r="AB67" s="11"/>
+      <c r="AC67" s="11"/>
+      <c r="AD67" s="11"/>
+      <c r="AE67" s="11"/>
+      <c r="AF67" s="11" t="s">
+        <v>984</v>
+      </c>
+      <c r="AG67" s="11"/>
+      <c r="AH67" s="11"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="11"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="11"/>
+      <c r="Q68" s="11"/>
+      <c r="R68" s="11"/>
+      <c r="S68" s="11"/>
+      <c r="T68" s="11"/>
+      <c r="U68" s="11"/>
+      <c r="V68" s="11"/>
+      <c r="W68" s="11"/>
+      <c r="X68" s="11"/>
+      <c r="Y68" s="11"/>
+      <c r="Z68" s="11"/>
+      <c r="AA68" s="11"/>
+      <c r="AB68" s="11"/>
+      <c r="AC68" s="11"/>
+      <c r="AD68" s="11"/>
+      <c r="AE68" s="11"/>
+      <c r="AF68" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="AG68" s="11"/>
+      <c r="AH68" s="11"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="11"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="11"/>
+      <c r="Q69" s="11"/>
+      <c r="R69" s="11"/>
+      <c r="S69" s="11"/>
+      <c r="T69" s="11"/>
+      <c r="U69" s="11"/>
+      <c r="V69" s="11"/>
+      <c r="W69" s="11"/>
+      <c r="X69" s="11"/>
+      <c r="Y69" s="11"/>
+      <c r="Z69" s="11"/>
+      <c r="AA69" s="11"/>
+      <c r="AB69" s="11"/>
+      <c r="AC69" s="11"/>
+      <c r="AD69" s="11"/>
+      <c r="AE69" s="11"/>
+      <c r="AF69" s="11" t="s">
+        <v>986</v>
+      </c>
+      <c r="AG69" s="11"/>
+      <c r="AH69" s="11"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="T70" s="11"/>
+      <c r="U70" s="11"/>
+      <c r="V70" s="11"/>
+      <c r="W70" s="11"/>
+      <c r="X70" s="11"/>
+      <c r="Y70" s="11"/>
+      <c r="Z70" s="11"/>
+      <c r="AA70" s="11"/>
+      <c r="AB70" s="11"/>
+      <c r="AC70" s="11"/>
+      <c r="AD70" s="11"/>
+      <c r="AE70" s="11"/>
+      <c r="AF70" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="AG70" s="11"/>
+      <c r="AH70" s="11"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11"/>
+      <c r="P71" s="11"/>
+      <c r="Q71" s="11"/>
+      <c r="R71" s="11"/>
+      <c r="S71" s="11"/>
+      <c r="T71" s="11"/>
+      <c r="U71" s="11"/>
+      <c r="V71" s="11"/>
+      <c r="W71" s="11"/>
+      <c r="X71" s="11"/>
+      <c r="Y71" s="11"/>
+      <c r="Z71" s="11"/>
+      <c r="AA71" s="11"/>
+      <c r="AB71" s="11"/>
+      <c r="AC71" s="11"/>
+      <c r="AD71" s="11"/>
+      <c r="AE71" s="11"/>
+      <c r="AF71" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="AG71" s="11"/>
+      <c r="AH71" s="11"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="11"/>
+      <c r="O72" s="11"/>
+      <c r="P72" s="11"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11"/>
+      <c r="S72" s="11"/>
+      <c r="T72" s="11"/>
+      <c r="U72" s="11"/>
+      <c r="V72" s="11"/>
+      <c r="W72" s="11"/>
+      <c r="X72" s="11"/>
+      <c r="Y72" s="11"/>
+      <c r="Z72" s="11"/>
+      <c r="AA72" s="11"/>
+      <c r="AB72" s="11"/>
+      <c r="AC72" s="11"/>
+      <c r="AD72" s="11"/>
+      <c r="AE72" s="11"/>
+      <c r="AF72" s="11" t="s">
+        <v>989</v>
+      </c>
+      <c r="AG72" s="11"/>
+      <c r="AH72" s="11"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="11"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="11"/>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="11"/>
+      <c r="S73" s="11"/>
+      <c r="T73" s="11"/>
+      <c r="U73" s="11"/>
+      <c r="V73" s="11"/>
+      <c r="W73" s="11"/>
+      <c r="X73" s="11"/>
+      <c r="Y73" s="11"/>
+      <c r="Z73" s="11"/>
+      <c r="AA73" s="11"/>
+      <c r="AB73" s="11"/>
+      <c r="AC73" s="11"/>
+      <c r="AD73" s="11"/>
+      <c r="AE73" s="11"/>
+      <c r="AF73" s="11" t="s">
+        <v>990</v>
+      </c>
+      <c r="AG73" s="11"/>
+      <c r="AH73" s="11"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="11"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="11"/>
+      <c r="S74" s="11"/>
+      <c r="T74" s="11"/>
+      <c r="U74" s="11"/>
+      <c r="V74" s="11"/>
+      <c r="W74" s="11"/>
+      <c r="X74" s="11"/>
+      <c r="Y74" s="11"/>
+      <c r="Z74" s="11"/>
+      <c r="AA74" s="11"/>
+      <c r="AB74" s="11"/>
+      <c r="AC74" s="11"/>
+      <c r="AD74" s="11"/>
+      <c r="AE74" s="11"/>
+      <c r="AF74" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="AG74" s="11"/>
+      <c r="AH74" s="11"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="11"/>
+      <c r="Q75" s="11"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="11"/>
+      <c r="T75" s="11"/>
+      <c r="U75" s="11"/>
+      <c r="V75" s="11"/>
+      <c r="W75" s="11"/>
+      <c r="X75" s="11"/>
+      <c r="Y75" s="11"/>
+      <c r="Z75" s="11"/>
+      <c r="AA75" s="11"/>
+      <c r="AB75" s="11"/>
+      <c r="AC75" s="11"/>
+      <c r="AD75" s="11"/>
+      <c r="AE75" s="11"/>
+      <c r="AF75" s="11" t="s">
+        <v>992</v>
+      </c>
+      <c r="AG75" s="11"/>
+      <c r="AH75" s="11"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="11"/>
+      <c r="Q76" s="11"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="11"/>
+      <c r="W76" s="11"/>
+      <c r="X76" s="11"/>
+      <c r="Y76" s="11"/>
+      <c r="Z76" s="11"/>
+      <c r="AA76" s="11"/>
+      <c r="AB76" s="11"/>
+      <c r="AC76" s="11"/>
+      <c r="AD76" s="11"/>
+      <c r="AE76" s="11"/>
+      <c r="AF76" s="11" t="s">
+        <v>993</v>
+      </c>
+      <c r="AG76" s="11"/>
+      <c r="AH76" s="11"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="11"/>
+      <c r="O77" s="11"/>
+      <c r="P77" s="11"/>
+      <c r="Q77" s="11"/>
+      <c r="R77" s="11"/>
+      <c r="S77" s="11"/>
+      <c r="T77" s="11"/>
+      <c r="U77" s="11"/>
+      <c r="V77" s="11"/>
+      <c r="W77" s="11"/>
+      <c r="X77" s="11"/>
+      <c r="Y77" s="11"/>
+      <c r="Z77" s="11"/>
+      <c r="AA77" s="11"/>
+      <c r="AB77" s="11"/>
+      <c r="AC77" s="11"/>
+      <c r="AD77" s="11"/>
+      <c r="AE77" s="11"/>
+      <c r="AF77" s="11" t="s">
+        <v>994</v>
+      </c>
+      <c r="AG77" s="11"/>
+      <c r="AH77" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12510,19 +13007,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>723</v>
@@ -12530,16 +13027,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -12577,43 +13074,43 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>723</v>
@@ -12621,36 +13118,36 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>808</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
@@ -12683,19 +13180,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>723</v>
@@ -12703,19 +13200,19 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -12760,67 +13257,67 @@
   <sheetData>
     <row r="1" spans="1:22" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>993</v>
+        <v>1006</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
       <c r="V1" s="8" t="s">
         <v>723</v>
@@ -12828,51 +13325,51 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1249</v>
+        <v>1262</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="R2" s="9" t="s">
         <v>777</v>
@@ -12911,13 +13408,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>723</v>
@@ -12925,13 +13422,13 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="D2" s="9"/>
     </row>
@@ -12963,28 +13460,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>723</v>
@@ -12992,16 +13489,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>779</v>
@@ -13046,16 +13543,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1271</v>
+        <v>1284</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -13063,13 +13560,13 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>865</v>
@@ -13100,16 +13597,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -13117,13 +13614,13 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -13152,7 +13649,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>723</v>
@@ -13160,7 +13657,7 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -13186,10 +13683,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>723</v>
@@ -13197,10 +13694,10 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="C2" s="9"/>
     </row>
@@ -13243,61 +13740,61 @@
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>983</v>
+        <v>996</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>986</v>
+        <v>999</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>987</v>
+        <v>1000</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>988</v>
+        <v>1001</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>989</v>
+        <v>1002</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>993</v>
+        <v>1006</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>994</v>
+        <v>1007</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>771</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>996</v>
+        <v>1009</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>999</v>
+        <v>1012</v>
       </c>
       <c r="T1" s="8" t="s">
         <v>723</v>
@@ -13305,49 +13802,49 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1002</v>
+        <v>1015</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1004</v>
+        <v>1017</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
-        <v>1005</v>
+        <v>1018</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1008</v>
+        <v>1021</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9" t="s">
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>1013</v>
+        <v>1026</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="9" t="s">
@@ -13379,16 +13876,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1288</v>
+        <v>1301</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -13396,16 +13893,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1291</v>
+        <v>1304</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1293</v>
+        <v>1306</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -13436,25 +13933,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1297</v>
+        <v>1310</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1298</v>
+        <v>1311</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1299</v>
+        <v>1312</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1300</v>
+        <v>1313</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1289</v>
+        <v>1302</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>723</v>
@@ -13462,25 +13959,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1302</v>
+        <v>1315</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1303</v>
+        <v>1316</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1304</v>
+        <v>1317</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1305</v>
+        <v>1318</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
       <c r="H2" s="9"/>
     </row>
@@ -13517,43 +14014,43 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1310</v>
+        <v>1323</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1311</v>
+        <v>1324</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1312</v>
+        <v>1325</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1313</v>
+        <v>1326</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1314</v>
+        <v>1327</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1315</v>
+        <v>1328</v>
       </c>
       <c r="N1" s="8" t="s">
         <v>723</v>
@@ -13561,43 +14058,43 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1316</v>
+        <v>1329</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1317</v>
+        <v>1330</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1318</v>
+        <v>1331</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1319</v>
+        <v>1332</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>756</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="N2" s="9"/>
     </row>
@@ -13629,28 +14126,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1327</v>
+        <v>1340</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1328</v>
+        <v>1341</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1330</v>
+        <v>1343</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1331</v>
+        <v>1344</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>723</v>
@@ -13658,25 +14155,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1332</v>
+        <v>1345</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1335</v>
+        <v>1348</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1336</v>
+        <v>1349</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1337</v>
+        <v>1350</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1338</v>
+        <v>1351</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -13705,16 +14202,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1339</v>
+        <v>1352</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1340</v>
+        <v>1353</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -13722,16 +14219,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1341</v>
+        <v>1354</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1342</v>
+        <v>1355</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1343</v>
+        <v>1356</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -13760,19 +14257,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1345</v>
+        <v>1358</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>723</v>
@@ -13780,10 +14277,10 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1347</v>
+        <v>1360</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1348</v>
+        <v>1361</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>814</v>
@@ -13792,7 +14289,7 @@
         <v>815</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -13829,25 +14326,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1350</v>
+        <v>1363</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1352</v>
+        <v>1365</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>628</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>723</v>
@@ -13855,22 +14352,22 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1353</v>
+        <v>1366</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>875</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1355</v>
+        <v>1368</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>756</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -13906,37 +14403,37 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1357</v>
+        <v>1370</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1359</v>
+        <v>1372</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1360</v>
+        <v>1373</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>723</v>
@@ -13944,37 +14441,37 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1362</v>
+        <v>1375</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1363</v>
+        <v>1376</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1366</v>
+        <v>1379</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>1369</v>
+        <v>1382</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>756</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
       <c r="L2" s="9"/>
     </row>
@@ -14005,25 +14502,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>723</v>
@@ -14031,19 +14528,19 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1378</v>
+        <v>1391</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1379</v>
+        <v>1392</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -14078,22 +14575,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1380</v>
+        <v>1393</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>723</v>
@@ -14101,10 +14598,10 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1383</v>
+        <v>1396</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>841</v>
@@ -14113,7 +14610,7 @@
         <v>756</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1384</v>
+        <v>1397</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -14121,7 +14618,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="C2:C5000">
-      <formula1>Lists!$AF$2:$AF$65</formula1>
+      <formula1>Lists!$AF$2:$AF$77</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G2:G5000">
       <formula1>Lists!$B$2:$B$3</formula1>
@@ -14143,24 +14640,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1014</v>
+        <v>1027</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1016</v>
+        <v>1029</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1018</v>
+        <v>1031</v>
       </c>
     </row>
   </sheetData>
@@ -14193,45 +14690,45 @@
         <v>786</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1385</v>
+        <v>1398</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>1386</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>1387</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1373</v>
-      </c>
       <c r="F1" s="8" t="s">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1389</v>
+        <v>1402</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1390</v>
+        <v>1403</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1391</v>
+        <v>1404</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>757</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1393</v>
+        <v>1406</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>865</v>
@@ -14245,23 +14742,23 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>1395</v>
+        <v>1408</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9" t="s">
         <v>756</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>1396</v>
+        <v>1409</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$7</formula1>
+      <formula1>Lists!$N$2:$N$8</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="B2:B5000">
       <formula1>Lists!$O$2:$O$9</formula1>
@@ -14302,60 +14799,60 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1397</v>
+        <v>1410</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1398</v>
+        <v>1411</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1399</v>
+        <v>1412</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1401</v>
+        <v>1414</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1402</v>
+        <v>1415</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>732</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1403</v>
+        <v>1416</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1404</v>
+        <v>1417</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1405</v>
+        <v>1418</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>757</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>1406</v>
+        <v>1419</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1407</v>
+        <v>1420</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1408</v>
+        <v>1421</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>872</v>
@@ -14365,7 +14862,7 @@
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>1379</v>
+        <v>1392</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
@@ -14377,7 +14874,7 @@
         <v>756</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>1395</v>
+        <v>1408</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -14419,51 +14916,51 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1397</v>
+        <v>1410</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>771</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1391</v>
+        <v>1404</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1406</v>
+        <v>1419</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>757</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1409</v>
+        <v>1422</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1410</v>
+        <v>1423</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1410</v>
+        <v>1423</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1411</v>
+        <v>1424</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1395</v>
+        <v>1408</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="9" t="s">
@@ -14494,30 +14991,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1412</v>
+        <v>1425</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1413</v>
+        <v>1426</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1414</v>
+        <v>1427</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1415</v>
+        <v>1428</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>873</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1417</v>
+        <v>1430</v>
       </c>
     </row>
   </sheetData>
@@ -14550,25 +15047,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1418</v>
+        <v>1431</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1419</v>
+        <v>1432</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1420</v>
+        <v>1433</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1421</v>
+        <v>1434</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1422</v>
+        <v>1435</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>733</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>757</v>
@@ -14576,25 +15073,25 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1424</v>
+        <v>1437</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1425</v>
+        <v>1438</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1426</v>
+        <v>1439</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1427</v>
+        <v>1440</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>766</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1428</v>
+        <v>1441</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>756</v>
@@ -14631,28 +15128,28 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1429</v>
+        <v>1442</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1430</v>
+        <v>1443</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>724</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1431</v>
+        <v>1444</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1432</v>
+        <v>1445</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>757</v>
@@ -14660,19 +15157,19 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1433</v>
+        <v>1446</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1434</v>
+        <v>1447</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1435</v>
+        <v>1448</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1436</v>
+        <v>1449</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>819</v>
@@ -14716,56 +15213,56 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1437</v>
+        <v>1450</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1420</v>
+        <v>1433</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1438</v>
+        <v>1451</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1439</v>
+        <v>1452</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1423</v>
+        <v>1436</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1440</v>
+        <v>1453</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1393</v>
+        <v>1406</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9" t="s">
-        <v>1441</v>
+        <v>1454</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1442</v>
+        <v>1455</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1443</v>
+        <v>1456</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1442</v>
+        <v>1455</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>1444</v>
+        <v>1457</v>
       </c>
       <c r="H2" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="0" errorStyle="information" sqref="A2:A5000">
-      <formula1>Lists!$N$2:$N$7</formula1>
+      <formula1>Lists!$N$2:$N$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14785,30 +15282,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1445</v>
+        <v>1458</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1446</v>
+        <v>1459</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1447</v>
+        <v>1460</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1448</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1449</v>
+        <v>1462</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1451</v>
+        <v>1464</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
     </row>
   </sheetData>
@@ -14830,36 +15327,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1453</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1454</v>
+        <v>1467</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1455</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1456</v>
+        <v>1469</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1457</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1458</v>
+        <v>1471</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1459</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1460</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6">
@@ -14867,20 +15364,20 @@
         <v>3</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1461</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1462</v>
+        <v>1475</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1464</v>
+        <v>1477</v>
       </c>
     </row>
   </sheetData>
@@ -14903,16 +15400,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -14920,16 +15417,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -14959,22 +15456,22 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>723</v>
@@ -14982,20 +15479,20 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1033</v>
+        <v>1046</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="G2" s="9"/>
     </row>
@@ -15026,25 +15523,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>723</v>
@@ -15052,19 +15549,19 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>851</v>
@@ -15104,31 +15601,31 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>994</v>
+        <v>1007</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>723</v>
@@ -15136,21 +15633,21 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1052</v>
+        <v>1065</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
       <c r="G2" s="9" t="s">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -15183,16 +15680,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1056</v>
+        <v>1069</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>994</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>723</v>
@@ -15200,16 +15697,16 @@
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="E2" s="9"/>
     </row>
